--- a/VerveStacks_MEX_grids_kan/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
+++ b/VerveStacks_MEX_grids_kan/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_MEX_grids_kan\SubRES_Tmpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{39CB0A6D-4822-40C2-83AA-1EAC12384B0A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{0AE486B5-72C0-44EE-92A1-5F21FA8298F4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="6" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1203,16 +1203,346 @@
     <t>pre</t>
   </si>
   <si>
+    <t>distr_solelc_spv_MEX_002</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 2</t>
+  </si>
+  <si>
+    <t>NRGI</t>
+  </si>
+  <si>
+    <t>daynite</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_MEX_014</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 14</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_MEX_022</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 22</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_MEX_031</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 31</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_MEX_040</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 40</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_MEX_001</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 1</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_MEX_011</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 11</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_MEX_019</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 19</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_MEX_021</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 21</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_MEX_027</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 27</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_MEX_044</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 44</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_MEX_039</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 39</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_MEX_033</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 33</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_MEX_008</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 8</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_MEX_050</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 50</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_MEX_034</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 34</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_MEX_024</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 24</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_MEX_043</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 43</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_MEX_006</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 6</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_MEX_045</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 45</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_MEX_035</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 35</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_MEX_016</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 16</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_MEX_017</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 17</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_MEX_049</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 49</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_MEX_042</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 42</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_MEX_003</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 3</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_MEX_058</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 58</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_MEX_036</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 36</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_MEX_023</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 23</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_MEX_059</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 59</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_MEX_048</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 48</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_MEX_028</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 28</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_MEX_047</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 47</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_MEX_005</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 5</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_MEX_020</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 20</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_MEX_046</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 46</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_MEX_010</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 10</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_MEX_013</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 13</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_MEX_056</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 56</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_MEX_051</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 51</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_MEX_054</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 54</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_MEX_004</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 4</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_MEX_009</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 9</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_MEX_018</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 18</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_MEX_057</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 57</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_MEX_055</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 55</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_MEX_029</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 29</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_MEX_032</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 32</t>
+  </si>
+  <si>
     <t>distr_solelc_spv_MEX_053</t>
   </si>
   <si>
     <t>connecting solar to buses in cluster 53</t>
   </si>
   <si>
-    <t>NRGI</t>
-  </si>
-  <si>
-    <t>daynite</t>
+    <t>distr_solelc_spv_MEX_007</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 7</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_MEX_015</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 15</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_MEX_026</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 26</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_MEX_012</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 12</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_MEX_030</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 30</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_MEX_037</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 37</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_MEX_038</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 38</t>
   </si>
   <si>
     <t>distr_solelc_spv_MEX_025</t>
@@ -1233,345 +1563,177 @@
     <t>connecting solar to buses in cluster 41</t>
   </si>
   <si>
-    <t>distr_solelc_spv_MEX_010</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 10</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_MEX_013</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 13</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_MEX_056</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 56</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_MEX_051</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 51</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_MEX_054</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 54</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_MEX_005</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 5</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_MEX_020</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 20</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_MEX_046</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 46</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_MEX_006</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 6</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_MEX_045</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 45</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_MEX_035</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 35</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_MEX_007</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 7</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_MEX_015</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 15</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_MEX_026</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 26</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_MEX_002</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 2</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_MEX_014</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 14</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_MEX_022</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 22</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_MEX_031</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 31</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_MEX_040</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 40</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_MEX_016</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 16</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_MEX_017</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 17</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_MEX_049</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 49</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_MEX_042</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 42</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_MEX_023</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 23</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_MEX_059</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 59</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_MEX_003</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 3</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_MEX_058</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 58</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_MEX_036</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 36</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_MEX_012</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 12</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_MEX_030</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 30</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_MEX_037</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 37</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_MEX_038</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 38</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_MEX_048</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 48</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_MEX_028</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 28</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_MEX_047</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 47</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_MEX_024</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 24</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_MEX_043</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 43</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_MEX_001</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 1</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_MEX_011</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 11</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_MEX_019</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 19</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_MEX_021</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 21</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_MEX_027</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 27</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_MEX_044</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 44</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_MEX_039</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 39</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_MEX_033</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 33</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_MEX_008</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 8</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_MEX_050</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 50</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_MEX_034</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 34</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_MEX_004</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 4</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_MEX_009</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 9</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_MEX_018</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 18</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_MEX_057</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 57</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_MEX_055</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 55</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_MEX_029</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 29</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_MEX_032</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 32</t>
-  </si>
-  <si>
     <t>comm-in</t>
   </si>
   <si>
     <t>ncap_cost~USD21_alt</t>
   </si>
   <si>
+    <t>e_w1377035989-400_MEX,e_w1376647652-400_MEX</t>
+  </si>
+  <si>
+    <t>e_w324339640-400_MEX,e_MX13-400_MEX,e_w382170046-400_MEX,e_w323989601-400_MEX</t>
+  </si>
+  <si>
+    <t>e_w193411905-400_MEX,e_MX1-400_MEX</t>
+  </si>
+  <si>
+    <t>e_w113005835-400_MEX,e_w112525248-400_MEX,e_MX47-400_MEX,e_MX66-400_MEX,e_w113005841-400_MEX,e_w1343929811-400_MEX</t>
+  </si>
+  <si>
+    <t>e_w334603451-400_MEX,e_MX68-400_MEX,e_w187401888-400_MEX</t>
+  </si>
+  <si>
+    <t>e_r16051214-400_MEX</t>
+  </si>
+  <si>
+    <t>e_w120340864-400_MEX,e_w323989601-400_MEX,e_w120212304-400_MEX,e_w1144358547-400_MEX</t>
+  </si>
+  <si>
+    <t>e_w1144358547-400_MEX,e_w120340864-400_MEX,e_w1144316290-400_MEX,e_w864230553-400_MEX,e_w328237829-400_MEX,e_w1144316288-400_MEX,e_MX12-400_MEX,e_w328234376-400_MEX</t>
+  </si>
+  <si>
+    <t>e_w335761046-400_MEX,e_w653400165-400_MEX,e_MX1-400_MEX,e_w329140644-400_MEX</t>
+  </si>
+  <si>
+    <t>e_MX62-400_MEX,e_w1185619636-400_MEX,e_w97343927-400_MEX,e_w113005835-400_MEX,e_w639158083-400_MEX,e_w112525248-400_MEX,e_w113005841-400_MEX,e_MX66-400_MEX</t>
+  </si>
+  <si>
+    <t>e_w317273421-400_MEX,e_w334603451-400_MEX,e_w187401888-400_MEX,e_MX60-400_MEX</t>
+  </si>
+  <si>
+    <t>e_MX49-400_MEX,e_MX43-400_MEX,e_w187401888-400_MEX,e_w370805988-400_MEX,e_MX36-400_MEX</t>
+  </si>
+  <si>
+    <t>e_w1376647652-400_MEX,e_w1013583868-400_MEX</t>
+  </si>
+  <si>
+    <t>e_MX26-400_MEX,e_w318396111-400_MEX,e_w318720928-400_MEX,e_w318721921-400_MEX,e_w302760278-400_MEX,e_w120212304-400_MEX,e_w1167512634-400_MEX,e_w1211021210-400_MEX,e_w120195768-400_MEX,e_w120197852-400_MEX,e_w1211041028-400_MEX,e_w318795296-400_MEX,e_w1211031755-400_MEX,e_MX17-400_MEX,e_MX35-400_MEX,e_w120217741-400_MEX,e_MX38-400_MEX</t>
+  </si>
+  <si>
+    <t>e_MX49-400_MEX,e_MX44-400_MEX,e_MX43-400_MEX,e_w370805988-400_MEX,e_MX41-400_MEX</t>
+  </si>
+  <si>
+    <t>e_w908223181-400_MEX,e_w193411905-400_MEX,e_w147507817-400_MEX</t>
+  </si>
+  <si>
+    <t>e_w381991692-400_MEX,e_MX62-400_MEX,e_w97343932-400_MEX,e_w316976706-400_MEX,e_w113005841-400_MEX,e_MX66-400_MEX</t>
+  </si>
+  <si>
+    <t>e_w119378437-400_MEX,e_w324339641-400_MEX</t>
+  </si>
+  <si>
+    <t>e_w108456470-400_MEX,e_MX58-400_MEX,e_w381991692-400_MEX,e_MX61-400_MEX,e_w97343932-400_MEX</t>
+  </si>
+  <si>
+    <t>e_MX36-400_MEX,e_w489433441-400_MEX,e_w764377660-400_MEX</t>
+  </si>
+  <si>
+    <t>e_w1020167966-400_MEX,e_w339029834-400_MEX,e_w908223181-400_MEX,e_w1122458623-400_MEX</t>
+  </si>
+  <si>
+    <t>e_w908223181-400_MEX</t>
+  </si>
+  <si>
+    <t>e_w318948686-400_MEX,e_MX20-400_MEX,e_w323989601-400_MEX,e_MX59-400_MEX,e_w318396111-400_MEX,e_w120139199-400_MEX,e_w320586165-400_MEX,e_w165130311-400_MEX,e_w221656033-400_MEX</t>
+  </si>
+  <si>
+    <t>e_w316976706-400_MEX,e_w156432250-400_MEX,e_w153402633-400_MEX</t>
+  </si>
+  <si>
+    <t>e_w1376647652-400_MEX,e_w1119978083-400_MEX,e_w1013583868-400_MEX</t>
+  </si>
+  <si>
+    <t>e_MX21-400_MEX,e_w325857132-400_MEX,e_MX46-400_MEX,e_MX31-400_MEX,e_MX42-400_MEX,e_w323682658-400_MEX,e_MX47-400_MEX,e_r16016425-400_MEX</t>
+  </si>
+  <si>
+    <t>e_w334603451-400_MEX,e_w156432250-400_MEX,e_w390018953-400_MEX</t>
+  </si>
+  <si>
+    <t>e_w703468573-400_MEX,e_w193411905-400_MEX,e_w335761046-400_MEX</t>
+  </si>
+  <si>
+    <t>e_MX18-400_MEX,e_MX15-400_MEX,e_MX16-400_MEX,e_MX24-400_MEX,e_w325974178-400_MEX,e_MX30-400_MEX,e_MX22-400_MEX,e_w325906414-400_MEX,e_w113005842-400_MEX,e_w1181050521-400_MEX</t>
+  </si>
+  <si>
+    <t>e_w320586165-400_MEX,e_w318811272-400_MEX,e_w322722579-400_MEX,e_w109684120-400_MEX,e_w1167512634-400_MEX,e_w318795296-400_MEX,e_MX64-400_MEX,e_MX63-400_MEX,e_w380654599-400_MEX,e_w187631617-400_MEX,e_MX38-400_MEX</t>
+  </si>
+  <si>
+    <t>e_w653400165-400_MEX,e_w335761046-400_MEX,e_w1135760619-400_MEX,e_w552409895-400_MEX,e_MX11-400_MEX,e_MX8-400_MEX,e_w124805240-400_MEX,e_w328371976-400_MEX,e_w1020056102-400_MEX,e_MX9-400_MEX</t>
+  </si>
+  <si>
+    <t>e_MX64-400_MEX,e_MX63-400_MEX,e_w380654599-400_MEX,e_w381991692-400_MEX,e_w108456470-400_MEX</t>
+  </si>
+  <si>
+    <t>e_w339029834-400_MEX,e_w324339641-400_MEX,e_w1020167966-400_MEX</t>
+  </si>
+  <si>
+    <t>e_w120340864-400_MEX,e_w147507817-400_MEX,e_w703468574-400_MEX,e_w1144316290-400_MEX,e_w703468573-400_MEX,e_w328237829-400_MEX,e_w1135760619-400_MEX</t>
+  </si>
+  <si>
+    <t>e_w1347720126-400_MEX,e_MX56-400_MEX,e_w1063163195-400_MEX,e_w1182315273-400_MEX,e_w108298346-400_MEX,e_MX51-400_MEX,e_w97173246-400_MEX,e_w1182379765-400_MEX,e_w31875861-400_MEX</t>
+  </si>
+  <si>
+    <t>e_w1013583868-400_MEX,e_w339029834-400_MEX,e_r16051214-400_MEX</t>
+  </si>
+  <si>
+    <t>e_r16051214-400_MEX,e_w908223181-400_MEX,e_w193411905-400_MEX</t>
+  </si>
+  <si>
+    <t>e_w864230553-400_MEX,e_w1211041028-400_MEX,e_w326213920-400_MEX,e_w120228114-400_MEX,e_MX34-400_MEX,e_w377881663-400_MEX</t>
+  </si>
+  <si>
+    <t>e_w327104799-400_MEX,e_w1128233586-400_MEX,e_w326794464-400_MEX,e_w1143875912-400_MEX,e_w1143875908-400_MEX</t>
+  </si>
+  <si>
+    <t>e_MX4-400_MEX,e_w1211132940-400_MEX,e_w100657593-400_MEX,e_w1137263496-400_MEX,e_w797709550-400_MEX</t>
+  </si>
+  <si>
+    <t>e_w1119978083-400_MEX,e_w1376647652-400_MEX,e_w1013583868-400_MEX</t>
+  </si>
+  <si>
+    <t>e_w1013583868-400_MEX,e_w1119978083-400_MEX,e_w339029834-400_MEX</t>
+  </si>
+  <si>
+    <t>e_w1122458623-400_MEX,e_w908223181-400_MEX,e_w120340864-400_MEX,e_w147507817-400_MEX,e_w193411905-400_MEX</t>
+  </si>
+  <si>
+    <t>e_w326213920-400_MEX,e_w1144316288-400_MEX,e_w931567937-400_MEX,e_w1143875912-400_MEX</t>
+  </si>
+  <si>
+    <t>e_w377881663-400_MEX,e_w326213920-400_MEX,e_MX32-400_MEX,e_MX23-400_MEX,e_MX21-400_MEX,e_MX15-400_MEX,e_w381587927-400_MEX</t>
+  </si>
+  <si>
+    <t>e_w244648181-400_MEX,e_w223990371-400_MEX,e_w316976706-400_MEX,e_w223990372-400_MEX,e_w686189325-400_MEX,e_w153402633-400_MEX</t>
+  </si>
+  <si>
+    <t>e_MX36-400_MEX,e_MX33-400_MEX,e_w489433441-400_MEX,e_w764377660-400_MEX</t>
+  </si>
+  <si>
     <t>e_w1137263495-400_MEX,e_w328454682-400_MEX,e_w970712564-400_MEX</t>
   </si>
   <si>
+    <t>e_w1119978083-400_MEX,e_w324339641-400_MEX,e_w339029834-400_MEX</t>
+  </si>
+  <si>
+    <t>e_w1122458623-400_MEX,e_w1020167966-400_MEX,e_w119378437-400_MEX,e_w324339640-400_MEX</t>
+  </si>
+  <si>
+    <t>e_w329140644-400_MEX,e_w101027471-400_MEX,e_w100657593-400_MEX,e_w101027476-400_MEX</t>
+  </si>
+  <si>
+    <t>e_r16051214-400_MEX,e_w908223181-400_MEX</t>
+  </si>
+  <si>
+    <t>e_MX66-400_MEX,e_w316976706-400_MEX,e_w244648181-400_MEX,e_w1343929811-400_MEX,e_w223990371-400_MEX</t>
+  </si>
+  <si>
+    <t>e_w156432250-400_MEX,e_w153402633-400_MEX,e_w317273421-400_MEX,e_w390018954-400_MEX</t>
+  </si>
+  <si>
+    <t>e_w187401888-400_MEX,e_MX60-400_MEX,e_MX49-400_MEX</t>
+  </si>
+  <si>
     <t>e_w101027476-400_MEX,e_MX1-400_MEX</t>
   </si>
   <si>
@@ -1581,168 +1743,6 @@
     <t>e_MX67-400_MEX,e_w334603451-400_MEX,e_w390018954-400_MEX,e_w390018953-400_MEX</t>
   </si>
   <si>
-    <t>e_w1013583868-400_MEX,e_w339029834-400_MEX,e_r16051214-400_MEX</t>
-  </si>
-  <si>
-    <t>e_r16051214-400_MEX,e_w908223181-400_MEX,e_w193411905-400_MEX</t>
-  </si>
-  <si>
-    <t>e_w864230553-400_MEX,e_w1211041028-400_MEX,e_w326213920-400_MEX,e_w120228114-400_MEX,e_MX34-400_MEX,e_w377881663-400_MEX</t>
-  </si>
-  <si>
-    <t>e_w327104799-400_MEX,e_w1128233586-400_MEX,e_w326794464-400_MEX,e_w1143875912-400_MEX,e_w1143875908-400_MEX</t>
-  </si>
-  <si>
-    <t>e_MX4-400_MEX,e_w1211132940-400_MEX,e_w100657593-400_MEX,e_w1137263496-400_MEX,e_w797709550-400_MEX</t>
-  </si>
-  <si>
-    <t>e_w339029834-400_MEX,e_w324339641-400_MEX,e_w1020167966-400_MEX</t>
-  </si>
-  <si>
-    <t>e_w120340864-400_MEX,e_w147507817-400_MEX,e_w703468574-400_MEX,e_w1144316290-400_MEX,e_w703468573-400_MEX,e_w328237829-400_MEX,e_w1135760619-400_MEX</t>
-  </si>
-  <si>
-    <t>e_w1347720126-400_MEX,e_MX56-400_MEX,e_w1063163195-400_MEX,e_w1182315273-400_MEX,e_w108298346-400_MEX,e_MX51-400_MEX,e_w97173246-400_MEX,e_w1182379765-400_MEX,e_w31875861-400_MEX</t>
-  </si>
-  <si>
-    <t>e_w119378437-400_MEX,e_w324339641-400_MEX</t>
-  </si>
-  <si>
-    <t>e_w108456470-400_MEX,e_MX58-400_MEX,e_w381991692-400_MEX,e_MX61-400_MEX,e_w97343932-400_MEX</t>
-  </si>
-  <si>
-    <t>e_MX36-400_MEX,e_w489433441-400_MEX,e_w764377660-400_MEX</t>
-  </si>
-  <si>
-    <t>e_w1119978083-400_MEX,e_w324339641-400_MEX,e_w339029834-400_MEX</t>
-  </si>
-  <si>
-    <t>e_w1122458623-400_MEX,e_w1020167966-400_MEX,e_w119378437-400_MEX,e_w324339640-400_MEX</t>
-  </si>
-  <si>
-    <t>e_w329140644-400_MEX,e_w101027471-400_MEX,e_w100657593-400_MEX,e_w101027476-400_MEX</t>
-  </si>
-  <si>
-    <t>e_w1377035989-400_MEX,e_w1376647652-400_MEX</t>
-  </si>
-  <si>
-    <t>e_w324339640-400_MEX,e_MX13-400_MEX,e_w382170046-400_MEX,e_w323989601-400_MEX</t>
-  </si>
-  <si>
-    <t>e_w193411905-400_MEX,e_MX1-400_MEX</t>
-  </si>
-  <si>
-    <t>e_w113005835-400_MEX,e_w112525248-400_MEX,e_MX47-400_MEX,e_MX66-400_MEX,e_w113005841-400_MEX,e_w1343929811-400_MEX</t>
-  </si>
-  <si>
-    <t>e_w334603451-400_MEX,e_MX68-400_MEX,e_w187401888-400_MEX</t>
-  </si>
-  <si>
-    <t>e_w1020167966-400_MEX,e_w339029834-400_MEX,e_w908223181-400_MEX,e_w1122458623-400_MEX</t>
-  </si>
-  <si>
-    <t>e_w908223181-400_MEX</t>
-  </si>
-  <si>
-    <t>e_w318948686-400_MEX,e_MX20-400_MEX,e_w323989601-400_MEX,e_MX59-400_MEX,e_w318396111-400_MEX,e_w120139199-400_MEX,e_w320586165-400_MEX,e_w165130311-400_MEX,e_w221656033-400_MEX</t>
-  </si>
-  <si>
-    <t>e_w316976706-400_MEX,e_w156432250-400_MEX,e_w153402633-400_MEX</t>
-  </si>
-  <si>
-    <t>e_w703468573-400_MEX,e_w193411905-400_MEX,e_w335761046-400_MEX</t>
-  </si>
-  <si>
-    <t>e_MX18-400_MEX,e_MX15-400_MEX,e_MX16-400_MEX,e_MX24-400_MEX,e_w325974178-400_MEX,e_MX30-400_MEX,e_MX22-400_MEX,e_w325906414-400_MEX,e_w113005842-400_MEX,e_w1181050521-400_MEX</t>
-  </si>
-  <si>
-    <t>e_w1376647652-400_MEX,e_w1119978083-400_MEX,e_w1013583868-400_MEX</t>
-  </si>
-  <si>
-    <t>e_MX21-400_MEX,e_w325857132-400_MEX,e_MX46-400_MEX,e_MX31-400_MEX,e_MX42-400_MEX,e_w323682658-400_MEX,e_MX47-400_MEX,e_r16016425-400_MEX</t>
-  </si>
-  <si>
-    <t>e_w334603451-400_MEX,e_w156432250-400_MEX,e_w390018953-400_MEX</t>
-  </si>
-  <si>
-    <t>e_r16051214-400_MEX,e_w908223181-400_MEX</t>
-  </si>
-  <si>
-    <t>e_MX66-400_MEX,e_w316976706-400_MEX,e_w244648181-400_MEX,e_w1343929811-400_MEX,e_w223990371-400_MEX</t>
-  </si>
-  <si>
-    <t>e_w156432250-400_MEX,e_w153402633-400_MEX,e_w317273421-400_MEX,e_w390018954-400_MEX</t>
-  </si>
-  <si>
-    <t>e_w187401888-400_MEX,e_MX60-400_MEX,e_MX49-400_MEX</t>
-  </si>
-  <si>
-    <t>e_w320586165-400_MEX,e_w318811272-400_MEX,e_w322722579-400_MEX,e_w109684120-400_MEX,e_w1167512634-400_MEX,e_w318795296-400_MEX,e_MX64-400_MEX,e_MX63-400_MEX,e_w380654599-400_MEX,e_w187631617-400_MEX,e_MX38-400_MEX</t>
-  </si>
-  <si>
-    <t>e_w653400165-400_MEX,e_w335761046-400_MEX,e_w1135760619-400_MEX,e_w552409895-400_MEX,e_MX11-400_MEX,e_MX8-400_MEX,e_w124805240-400_MEX,e_w328371976-400_MEX,e_w1020056102-400_MEX,e_MX9-400_MEX</t>
-  </si>
-  <si>
-    <t>e_MX64-400_MEX,e_MX63-400_MEX,e_w380654599-400_MEX,e_w381991692-400_MEX,e_w108456470-400_MEX</t>
-  </si>
-  <si>
-    <t>e_w908223181-400_MEX,e_w193411905-400_MEX,e_w147507817-400_MEX</t>
-  </si>
-  <si>
-    <t>e_w381991692-400_MEX,e_MX62-400_MEX,e_w97343932-400_MEX,e_w316976706-400_MEX,e_w113005841-400_MEX,e_MX66-400_MEX</t>
-  </si>
-  <si>
-    <t>e_r16051214-400_MEX</t>
-  </si>
-  <si>
-    <t>e_w120340864-400_MEX,e_w323989601-400_MEX,e_w120212304-400_MEX,e_w1144358547-400_MEX</t>
-  </si>
-  <si>
-    <t>e_w1144358547-400_MEX,e_w120340864-400_MEX,e_w1144316290-400_MEX,e_w864230553-400_MEX,e_w328237829-400_MEX,e_w1144316288-400_MEX,e_MX12-400_MEX,e_w328234376-400_MEX</t>
-  </si>
-  <si>
-    <t>e_w335761046-400_MEX,e_w653400165-400_MEX,e_MX1-400_MEX,e_w329140644-400_MEX</t>
-  </si>
-  <si>
-    <t>e_MX62-400_MEX,e_w1185619636-400_MEX,e_w97343927-400_MEX,e_w113005835-400_MEX,e_w639158083-400_MEX,e_w112525248-400_MEX,e_w113005841-400_MEX,e_MX66-400_MEX</t>
-  </si>
-  <si>
-    <t>e_w317273421-400_MEX,e_w334603451-400_MEX,e_w187401888-400_MEX,e_MX60-400_MEX</t>
-  </si>
-  <si>
-    <t>e_MX49-400_MEX,e_MX43-400_MEX,e_w187401888-400_MEX,e_w370805988-400_MEX,e_MX36-400_MEX</t>
-  </si>
-  <si>
-    <t>e_w1376647652-400_MEX,e_w1013583868-400_MEX</t>
-  </si>
-  <si>
-    <t>e_MX26-400_MEX,e_w318396111-400_MEX,e_w318720928-400_MEX,e_w318721921-400_MEX,e_w302760278-400_MEX,e_w120212304-400_MEX,e_w1167512634-400_MEX,e_w1211021210-400_MEX,e_w120195768-400_MEX,e_w120197852-400_MEX,e_w1211041028-400_MEX,e_w318795296-400_MEX,e_w1211031755-400_MEX,e_MX17-400_MEX,e_MX35-400_MEX,e_w120217741-400_MEX,e_MX38-400_MEX</t>
-  </si>
-  <si>
-    <t>e_MX49-400_MEX,e_MX44-400_MEX,e_MX43-400_MEX,e_w370805988-400_MEX,e_MX41-400_MEX</t>
-  </si>
-  <si>
-    <t>e_w1119978083-400_MEX,e_w1376647652-400_MEX,e_w1013583868-400_MEX</t>
-  </si>
-  <si>
-    <t>e_w1013583868-400_MEX,e_w1119978083-400_MEX,e_w339029834-400_MEX</t>
-  </si>
-  <si>
-    <t>e_w1122458623-400_MEX,e_w908223181-400_MEX,e_w120340864-400_MEX,e_w147507817-400_MEX,e_w193411905-400_MEX</t>
-  </si>
-  <si>
-    <t>e_w326213920-400_MEX,e_w1144316288-400_MEX,e_w931567937-400_MEX,e_w1143875912-400_MEX</t>
-  </si>
-  <si>
-    <t>e_w377881663-400_MEX,e_w326213920-400_MEX,e_MX32-400_MEX,e_MX23-400_MEX,e_MX21-400_MEX,e_MX15-400_MEX,e_w381587927-400_MEX</t>
-  </si>
-  <si>
-    <t>e_w244648181-400_MEX,e_w223990371-400_MEX,e_w316976706-400_MEX,e_w223990372-400_MEX,e_w686189325-400_MEX,e_w153402633-400_MEX</t>
-  </si>
-  <si>
-    <t>e_MX36-400_MEX,e_MX33-400_MEX,e_w489433441-400_MEX,e_w764377660-400_MEX</t>
-  </si>
-  <si>
     <t>distr_wonelc_won_MEX_027</t>
   </si>
   <si>
@@ -1755,6 +1755,186 @@
     <t>connecting wind onshore to buses in cluster 30</t>
   </si>
   <si>
+    <t>distr_wonelc_won_MEX_015</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 15</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_MEX_032</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 32</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_MEX_028</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 28</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_MEX_002</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 2</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_MEX_020</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 20</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_MEX_029</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 29</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_MEX_022</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 22</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_MEX_005</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 5</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_MEX_035</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 35</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_MEX_044</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 44</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_MEX_003</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 3</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_MEX_006</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 6</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_MEX_019</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 19</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_MEX_011</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 11</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_MEX_008</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 8</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_MEX_014</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 14</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_MEX_021</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 21</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_MEX_043</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 43</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_MEX_023</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 23</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_MEX_012</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 12</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_MEX_036</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 36</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_MEX_038</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 38</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_MEX_033</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 33</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_MEX_026</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 26</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_MEX_009</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 9</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_MEX_042</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 42</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_MEX_025</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 25</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_MEX_041</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 41</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_MEX_040</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 40</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_MEX_004</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 4</t>
+  </si>
+  <si>
     <t>distr_wonelc_won_MEX_007</t>
   </si>
   <si>
@@ -1767,76 +1947,40 @@
     <t>connecting wind onshore to buses in cluster 1</t>
   </si>
   <si>
-    <t>distr_wonelc_won_MEX_033</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 33</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_MEX_026</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 26</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_MEX_009</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 9</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_MEX_042</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 42</t>
-  </si>
-  <si>
     <t>distr_wonelc_won_MEX_018</t>
   </si>
   <si>
     <t>connecting wind onshore to buses in cluster 18</t>
   </si>
   <si>
-    <t>distr_wonelc_won_MEX_003</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 3</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_MEX_006</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 6</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_MEX_019</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 19</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_MEX_032</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 32</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_MEX_028</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 28</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_MEX_002</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 2</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_MEX_020</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 20</t>
+    <t>distr_wonelc_won_MEX_013</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 13</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_MEX_016</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 16</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_MEX_034</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 34</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_MEX_039</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 39</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_MEX_037</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 37</t>
   </si>
   <si>
     <t>distr_wonelc_won_MEX_031</t>
@@ -1863,150 +2007,6 @@
     <t>connecting wind onshore to buses in cluster 17</t>
   </si>
   <si>
-    <t>distr_wonelc_won_MEX_029</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 29</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_MEX_022</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 22</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_MEX_005</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 5</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_MEX_035</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 35</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_MEX_044</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 44</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_MEX_023</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 23</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_MEX_012</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 12</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_MEX_036</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 36</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_MEX_038</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 38</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_MEX_013</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 13</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_MEX_016</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 16</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_MEX_034</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 34</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_MEX_039</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 39</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_MEX_037</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 37</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_MEX_004</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 4</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_MEX_011</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 11</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_MEX_008</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 8</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_MEX_014</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 14</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_MEX_021</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 21</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_MEX_043</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 43</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_MEX_015</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 15</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_MEX_025</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 25</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_MEX_041</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 41</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_MEX_040</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 40</t>
-  </si>
-  <si>
     <t>elc_won_MEX_027</t>
   </si>
   <si>
@@ -2019,6 +2019,165 @@
     <t>e_w1376647652-400_MEX,e_w1013583868-400_MEX,e_w1119978083-400_MEX</t>
   </si>
   <si>
+    <t>elc_won_MEX_015</t>
+  </si>
+  <si>
+    <t>e_w908223181-400_MEX,e_w147507817-400_MEX,e_w193411905-400_MEX,e_w120340864-400_MEX,e_w1144358547-400_MEX</t>
+  </si>
+  <si>
+    <t>elc_won_MEX_032</t>
+  </si>
+  <si>
+    <t>e_w1377035989-400_MEX</t>
+  </si>
+  <si>
+    <t>elc_won_MEX_028</t>
+  </si>
+  <si>
+    <t>e_w1119978083-400_MEX,e_w324339641-400_MEX,e_w339029834-400_MEX,e_w119378437-400_MEX</t>
+  </si>
+  <si>
+    <t>elc_won_MEX_002</t>
+  </si>
+  <si>
+    <t>e_w1122458623-400_MEX,e_w908223181-400_MEX,e_w120340864-400_MEX</t>
+  </si>
+  <si>
+    <t>elc_won_MEX_020</t>
+  </si>
+  <si>
+    <t>e_w703468573-400_MEX,e_w1135760619-400_MEX,e_w653400165-400_MEX,e_w552409895-400_MEX,e_MX8-400_MEX</t>
+  </si>
+  <si>
+    <t>elc_won_MEX_029</t>
+  </si>
+  <si>
+    <t>e_w1119978083-400_MEX,e_w339029834-400_MEX,e_w324339641-400_MEX,e_w1020167966-400_MEX</t>
+  </si>
+  <si>
+    <t>elc_won_MEX_022</t>
+  </si>
+  <si>
+    <t>e_w1376647652-400_MEX,e_w1013583868-400_MEX,e_r16051214-400_MEX</t>
+  </si>
+  <si>
+    <t>elc_won_MEX_005</t>
+  </si>
+  <si>
+    <t>e_w908223181-400_MEX,e_w1122458623-400_MEX</t>
+  </si>
+  <si>
+    <t>elc_won_MEX_035</t>
+  </si>
+  <si>
+    <t>e_w327104799-400_MEX,e_w1211132940-400_MEX,e_w326794464-400_MEX,e_w1143875908-400_MEX,e_w100657593-400_MEX,e_w1137263496-400_MEX,e_w797709550-400_MEX</t>
+  </si>
+  <si>
+    <t>elc_won_MEX_044</t>
+  </si>
+  <si>
+    <t>e_MX22-400_MEX,e_w325974178-400_MEX,e_w325906414-400_MEX,e_w113005842-400_MEX,e_MX47-400_MEX,e_r16016425-400_MEX</t>
+  </si>
+  <si>
+    <t>elc_won_MEX_003</t>
+  </si>
+  <si>
+    <t>elc_won_MEX_006</t>
+  </si>
+  <si>
+    <t>elc_won_MEX_019</t>
+  </si>
+  <si>
+    <t>e_w302760278-400_MEX,e_w120197852-400_MEX,e_w1211041028-400_MEX,e_w120195768-400_MEX,e_w120212304-400_MEX,e_w1211031755-400_MEX,e_w120217741-400_MEX,e_w120228114-400_MEX,e_MX34-400_MEX,e_w377881663-400_MEX,e_w1347720126-400_MEX</t>
+  </si>
+  <si>
+    <t>elc_won_MEX_011</t>
+  </si>
+  <si>
+    <t>elc_won_MEX_008</t>
+  </si>
+  <si>
+    <t>e_w908223181-400_MEX,e_w193411905-400_MEX</t>
+  </si>
+  <si>
+    <t>elc_won_MEX_014</t>
+  </si>
+  <si>
+    <t>e_w193411905-400_MEX,e_w147507817-400_MEX,e_w703468573-400_MEX</t>
+  </si>
+  <si>
+    <t>elc_won_MEX_021</t>
+  </si>
+  <si>
+    <t>e_w326213920-400_MEX,e_w377881663-400_MEX</t>
+  </si>
+  <si>
+    <t>elc_won_MEX_043</t>
+  </si>
+  <si>
+    <t>e_w1343929811-400_MEX,e_MX66-400_MEX,e_w223990371-400_MEX</t>
+  </si>
+  <si>
+    <t>elc_won_MEX_023</t>
+  </si>
+  <si>
+    <t>e_w1013583868-400_MEX,e_w1119978083-400_MEX</t>
+  </si>
+  <si>
+    <t>elc_won_MEX_012</t>
+  </si>
+  <si>
+    <t>e_w193411905-400_MEX,e_w335761046-400_MEX,e_MX1-400_MEX</t>
+  </si>
+  <si>
+    <t>elc_won_MEX_036</t>
+  </si>
+  <si>
+    <t>e_w931567937-400_MEX,e_w1143989565-400_MEX,e_w785742675-400_MEX,e_w326794464-400_MEX,e_w1137263496-400_MEX,e_w1137263495-400_MEX,e_w328454682-400_MEX,e_w970712564-400_MEX</t>
+  </si>
+  <si>
+    <t>elc_won_MEX_038</t>
+  </si>
+  <si>
+    <t>e_MX41-400_MEX,e_w187401888-400_MEX,e_MX49-400_MEX,e_MX36-400_MEX,e_w489433441-400_MEX,e_MX33-400_MEX,e_w764377660-400_MEX</t>
+  </si>
+  <si>
+    <t>elc_won_MEX_033</t>
+  </si>
+  <si>
+    <t>e_w1376647652-400_MEX,e_w1377035989-400_MEX,e_w1119978083-400_MEX,e_w1013583868-400_MEX</t>
+  </si>
+  <si>
+    <t>elc_won_MEX_026</t>
+  </si>
+  <si>
+    <t>elc_won_MEX_009</t>
+  </si>
+  <si>
+    <t>elc_won_MEX_042</t>
+  </si>
+  <si>
+    <t>e_w316976706-400_MEX,e_w244648181-400_MEX,e_w223990371-400_MEX,e_w223990372-400_MEX,e_w686189325-400_MEX,e_w153402633-400_MEX</t>
+  </si>
+  <si>
+    <t>elc_won_MEX_025</t>
+  </si>
+  <si>
+    <t>elc_won_MEX_041</t>
+  </si>
+  <si>
+    <t>e_w97343932-400_MEX,e_MX62-400_MEX,e_w316976706-400_MEX,e_w156432250-400_MEX,e_w153402633-400_MEX,e_w334603451-400_MEX</t>
+  </si>
+  <si>
+    <t>elc_won_MEX_040</t>
+  </si>
+  <si>
+    <t>e_w223990372-400_MEX,e_w317273421-400_MEX</t>
+  </si>
+  <si>
+    <t>elc_won_MEX_004</t>
+  </si>
+  <si>
     <t>elc_won_MEX_007</t>
   </si>
   <si>
@@ -2028,64 +2187,40 @@
     <t>e_w120340864-400_MEX,e_w120212304-400_MEX,e_w1144358547-400_MEX</t>
   </si>
   <si>
-    <t>elc_won_MEX_033</t>
-  </si>
-  <si>
-    <t>e_w1376647652-400_MEX,e_w1377035989-400_MEX,e_w1119978083-400_MEX,e_w1013583868-400_MEX</t>
-  </si>
-  <si>
-    <t>elc_won_MEX_026</t>
-  </si>
-  <si>
-    <t>elc_won_MEX_009</t>
-  </si>
-  <si>
-    <t>elc_won_MEX_042</t>
-  </si>
-  <si>
-    <t>e_w316976706-400_MEX,e_w244648181-400_MEX,e_w223990371-400_MEX,e_w223990372-400_MEX,e_w686189325-400_MEX,e_w153402633-400_MEX</t>
-  </si>
-  <si>
     <t>elc_won_MEX_018</t>
   </si>
   <si>
     <t>e_w1144316290-400_MEX,e_w703468573-400_MEX,e_w1144358547-400_MEX,e_w328237829-400_MEX,e_w864230553-400_MEX,e_w1144316288-400_MEX</t>
   </si>
   <si>
-    <t>elc_won_MEX_003</t>
-  </si>
-  <si>
-    <t>elc_won_MEX_006</t>
-  </si>
-  <si>
-    <t>elc_won_MEX_019</t>
-  </si>
-  <si>
-    <t>e_w302760278-400_MEX,e_w120197852-400_MEX,e_w1211041028-400_MEX,e_w120195768-400_MEX,e_w120212304-400_MEX,e_w1211031755-400_MEX,e_w120217741-400_MEX,e_w120228114-400_MEX,e_MX34-400_MEX,e_w377881663-400_MEX,e_w1347720126-400_MEX</t>
-  </si>
-  <si>
-    <t>elc_won_MEX_032</t>
-  </si>
-  <si>
-    <t>e_w1377035989-400_MEX</t>
-  </si>
-  <si>
-    <t>elc_won_MEX_028</t>
-  </si>
-  <si>
-    <t>e_w1119978083-400_MEX,e_w324339641-400_MEX,e_w339029834-400_MEX,e_w119378437-400_MEX</t>
-  </si>
-  <si>
-    <t>elc_won_MEX_002</t>
-  </si>
-  <si>
-    <t>e_w1122458623-400_MEX,e_w908223181-400_MEX,e_w120340864-400_MEX</t>
-  </si>
-  <si>
-    <t>elc_won_MEX_020</t>
-  </si>
-  <si>
-    <t>e_w703468573-400_MEX,e_w1135760619-400_MEX,e_w653400165-400_MEX,e_w552409895-400_MEX,e_MX8-400_MEX</t>
+    <t>elc_won_MEX_013</t>
+  </si>
+  <si>
+    <t>e_w147507817-400_MEX,e_w703468574-400_MEX,e_w703468573-400_MEX</t>
+  </si>
+  <si>
+    <t>elc_won_MEX_016</t>
+  </si>
+  <si>
+    <t>e_w328237829-400_MEX,e_MX12-400_MEX,e_w328234376-400_MEX,e_w1135760619-400_MEX,e_w1144316288-400_MEX,e_MX11-400_MEX</t>
+  </si>
+  <si>
+    <t>elc_won_MEX_034</t>
+  </si>
+  <si>
+    <t>e_MX1-400_MEX,e_w335761046-400_MEX,e_w101027476-400_MEX,e_w329140644-400_MEX,e_w101027471-400_MEX,e_MX4-400_MEX,e_w100657593-400_MEX</t>
+  </si>
+  <si>
+    <t>elc_won_MEX_039</t>
+  </si>
+  <si>
+    <t>e_w317273421-400_MEX,e_w187401888-400_MEX,e_MX60-400_MEX</t>
+  </si>
+  <si>
+    <t>elc_won_MEX_037</t>
+  </si>
+  <si>
+    <t>e_MX60-400_MEX,e_MX49-400_MEX,e_MX44-400_MEX,e_MX43-400_MEX,e_w370805988-400_MEX,e_MX41-400_MEX</t>
   </si>
   <si>
     <t>elc_won_MEX_031</t>
@@ -2109,139 +2244,118 @@
     <t>e_w1144358547-400_MEX,e_w120212304-400_MEX,e_MX17-400_MEX,e_w864230553-400_MEX,e_w1211041028-400_MEX,e_w326213920-400_MEX</t>
   </si>
   <si>
-    <t>elc_won_MEX_029</t>
-  </si>
-  <si>
-    <t>e_w1119978083-400_MEX,e_w339029834-400_MEX,e_w324339641-400_MEX,e_w1020167966-400_MEX</t>
-  </si>
-  <si>
-    <t>elc_won_MEX_022</t>
-  </si>
-  <si>
-    <t>e_w1376647652-400_MEX,e_w1013583868-400_MEX,e_r16051214-400_MEX</t>
-  </si>
-  <si>
-    <t>elc_won_MEX_005</t>
-  </si>
-  <si>
-    <t>e_w908223181-400_MEX,e_w1122458623-400_MEX</t>
-  </si>
-  <si>
-    <t>elc_won_MEX_035</t>
-  </si>
-  <si>
-    <t>e_w327104799-400_MEX,e_w1211132940-400_MEX,e_w326794464-400_MEX,e_w1143875908-400_MEX,e_w100657593-400_MEX,e_w1137263496-400_MEX,e_w797709550-400_MEX</t>
-  </si>
-  <si>
-    <t>elc_won_MEX_044</t>
-  </si>
-  <si>
-    <t>e_MX22-400_MEX,e_w325974178-400_MEX,e_w325906414-400_MEX,e_w113005842-400_MEX,e_MX47-400_MEX,e_r16016425-400_MEX</t>
-  </si>
-  <si>
-    <t>elc_won_MEX_023</t>
-  </si>
-  <si>
-    <t>e_w1013583868-400_MEX,e_w1119978083-400_MEX</t>
-  </si>
-  <si>
-    <t>elc_won_MEX_012</t>
-  </si>
-  <si>
-    <t>e_w193411905-400_MEX,e_w335761046-400_MEX,e_MX1-400_MEX</t>
-  </si>
-  <si>
-    <t>elc_won_MEX_036</t>
-  </si>
-  <si>
-    <t>e_w931567937-400_MEX,e_w1143989565-400_MEX,e_w785742675-400_MEX,e_w326794464-400_MEX,e_w1137263496-400_MEX,e_w1137263495-400_MEX,e_w328454682-400_MEX,e_w970712564-400_MEX</t>
-  </si>
-  <si>
-    <t>elc_won_MEX_038</t>
-  </si>
-  <si>
-    <t>e_MX41-400_MEX,e_w187401888-400_MEX,e_MX49-400_MEX,e_MX36-400_MEX,e_w489433441-400_MEX,e_MX33-400_MEX,e_w764377660-400_MEX</t>
-  </si>
-  <si>
-    <t>elc_won_MEX_013</t>
-  </si>
-  <si>
-    <t>e_w147507817-400_MEX,e_w703468574-400_MEX,e_w703468573-400_MEX</t>
-  </si>
-  <si>
-    <t>elc_won_MEX_016</t>
-  </si>
-  <si>
-    <t>e_w328237829-400_MEX,e_MX12-400_MEX,e_w328234376-400_MEX,e_w1135760619-400_MEX,e_w1144316288-400_MEX,e_MX11-400_MEX</t>
-  </si>
-  <si>
-    <t>elc_won_MEX_034</t>
-  </si>
-  <si>
-    <t>e_MX1-400_MEX,e_w335761046-400_MEX,e_w101027476-400_MEX,e_w329140644-400_MEX,e_w101027471-400_MEX,e_MX4-400_MEX,e_w100657593-400_MEX</t>
-  </si>
-  <si>
-    <t>elc_won_MEX_039</t>
-  </si>
-  <si>
-    <t>e_w317273421-400_MEX,e_w187401888-400_MEX,e_MX60-400_MEX</t>
-  </si>
-  <si>
-    <t>elc_won_MEX_037</t>
-  </si>
-  <si>
-    <t>e_MX60-400_MEX,e_MX49-400_MEX,e_MX44-400_MEX,e_MX43-400_MEX,e_w370805988-400_MEX,e_MX41-400_MEX</t>
-  </si>
-  <si>
-    <t>elc_won_MEX_004</t>
-  </si>
-  <si>
-    <t>elc_won_MEX_011</t>
-  </si>
-  <si>
-    <t>elc_won_MEX_008</t>
-  </si>
-  <si>
-    <t>e_w908223181-400_MEX,e_w193411905-400_MEX</t>
-  </si>
-  <si>
-    <t>elc_won_MEX_014</t>
-  </si>
-  <si>
-    <t>e_w193411905-400_MEX,e_w147507817-400_MEX,e_w703468573-400_MEX</t>
-  </si>
-  <si>
-    <t>elc_won_MEX_021</t>
-  </si>
-  <si>
-    <t>e_w326213920-400_MEX,e_w377881663-400_MEX</t>
-  </si>
-  <si>
-    <t>elc_won_MEX_043</t>
-  </si>
-  <si>
-    <t>e_w1343929811-400_MEX,e_MX66-400_MEX,e_w223990371-400_MEX</t>
-  </si>
-  <si>
-    <t>elc_won_MEX_015</t>
-  </si>
-  <si>
-    <t>e_w908223181-400_MEX,e_w147507817-400_MEX,e_w193411905-400_MEX,e_w120340864-400_MEX,e_w1144358547-400_MEX</t>
-  </si>
-  <si>
-    <t>elc_won_MEX_025</t>
-  </si>
-  <si>
-    <t>elc_won_MEX_041</t>
-  </si>
-  <si>
-    <t>e_w97343932-400_MEX,e_MX62-400_MEX,e_w316976706-400_MEX,e_w156432250-400_MEX,e_w153402633-400_MEX,e_w334603451-400_MEX</t>
-  </si>
-  <si>
-    <t>elc_won_MEX_040</t>
-  </si>
-  <si>
-    <t>e_w223990372-400_MEX,e_w317273421-400_MEX</t>
+    <t>distr_wofelc_wof_MEX_014</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 14</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_MEX_022</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 22</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_MEX_015</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 15</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_MEX_011</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 11</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_MEX_001</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 1</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_MEX_008</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 8</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_MEX_007</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 7</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_MEX_029</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 29</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_MEX_010</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 10</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_MEX_009</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 9</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_MEX_021</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 21</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_MEX_002</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 2</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_MEX_003</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 3</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_MEX_026</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 26</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_MEX_012</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 12</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_MEX_019</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 19</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_MEX_020</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 20</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_MEX_027</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 27</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_MEX_017</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 17</t>
   </si>
   <si>
     <t>distr_wofelc_wof_MEX_030</t>
@@ -2262,76 +2376,40 @@
     <t>connecting wind offshore to buses in cluster 6</t>
   </si>
   <si>
-    <t>distr_wofelc_wof_MEX_011</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 11</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_MEX_015</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 15</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_MEX_002</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 2</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_MEX_003</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 3</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_MEX_026</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 26</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_MEX_020</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 20</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_MEX_001</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 1</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_MEX_008</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 8</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_MEX_007</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 7</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_MEX_029</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 29</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_MEX_027</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 27</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_MEX_017</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 17</t>
+    <t>distr_wofelc_wof_MEX_004</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 4</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_MEX_023</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 23</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_MEX_016</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 16</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_MEX_024</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 24</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_MEX_013</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 13</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_MEX_025</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 25</t>
   </si>
   <si>
     <t>distr_wofelc_wof_MEX_005</t>
@@ -2346,82 +2424,100 @@
     <t>connecting wind offshore to buses in cluster 28</t>
   </si>
   <si>
-    <t>distr_wofelc_wof_MEX_010</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 10</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_MEX_009</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 9</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_MEX_021</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 21</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_MEX_016</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 16</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_MEX_012</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 12</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_MEX_019</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 19</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_MEX_014</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 14</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_MEX_022</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 22</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_MEX_004</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 4</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_MEX_023</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 23</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_MEX_024</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 24</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_MEX_013</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 13</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_MEX_025</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 25</t>
+    <t>elc_wof_MEX_014</t>
+  </si>
+  <si>
+    <t>e_w1119978083-400_MEX,e_w339029834-400_MEX</t>
+  </si>
+  <si>
+    <t>elc_wof_MEX_022</t>
+  </si>
+  <si>
+    <t>e_r16016425-400_MEX,e_w113005842-400_MEX</t>
+  </si>
+  <si>
+    <t>elc_wof_MEX_015</t>
+  </si>
+  <si>
+    <t>e_w489433441-400_MEX,e_w764377660-400_MEX</t>
+  </si>
+  <si>
+    <t>elc_wof_MEX_011</t>
+  </si>
+  <si>
+    <t>elc_wof_MEX_001</t>
+  </si>
+  <si>
+    <t>elc_wof_MEX_008</t>
+  </si>
+  <si>
+    <t>elc_wof_MEX_007</t>
+  </si>
+  <si>
+    <t>e_w324339641-400_MEX,e_w1119978083-400_MEX</t>
+  </si>
+  <si>
+    <t>elc_wof_MEX_029</t>
+  </si>
+  <si>
+    <t>e_w1343929811-400_MEX,e_r16016425-400_MEX,e_w223990371-400_MEX</t>
+  </si>
+  <si>
+    <t>elc_wof_MEX_010</t>
+  </si>
+  <si>
+    <t>elc_wof_MEX_009</t>
+  </si>
+  <si>
+    <t>elc_wof_MEX_021</t>
+  </si>
+  <si>
+    <t>e_MX49-400_MEX,e_MX44-400_MEX</t>
+  </si>
+  <si>
+    <t>elc_wof_MEX_002</t>
+  </si>
+  <si>
+    <t>elc_wof_MEX_003</t>
+  </si>
+  <si>
+    <t>e_w1119978083-400_MEX</t>
+  </si>
+  <si>
+    <t>elc_wof_MEX_026</t>
+  </si>
+  <si>
+    <t>e_w325906414-400_MEX,e_w1143989565-400_MEX,e_w970712564-400_MEX</t>
+  </si>
+  <si>
+    <t>elc_wof_MEX_012</t>
+  </si>
+  <si>
+    <t>e_w324339641-400_MEX,e_w339029834-400_MEX</t>
+  </si>
+  <si>
+    <t>elc_wof_MEX_019</t>
+  </si>
+  <si>
+    <t>e_MX40-400_MEX,e_MX36-400_MEX,e_w489433441-400_MEX,e_w764377660-400_MEX</t>
+  </si>
+  <si>
+    <t>elc_wof_MEX_020</t>
+  </si>
+  <si>
+    <t>e_MX44-400_MEX,e_w370805988-400_MEX,e_MX40-400_MEX</t>
+  </si>
+  <si>
+    <t>elc_wof_MEX_027</t>
+  </si>
+  <si>
+    <t>e_w316976706-400_MEX</t>
+  </si>
+  <si>
+    <t>elc_wof_MEX_017</t>
+  </si>
+  <si>
+    <t>e_MX60-400_MEX,e_MX49-400_MEX,e_MX44-400_MEX</t>
   </si>
   <si>
     <t>elc_wof_MEX_030</t>
@@ -2439,64 +2535,34 @@
     <t>elc_wof_MEX_006</t>
   </si>
   <si>
-    <t>e_w1119978083-400_MEX</t>
-  </si>
-  <si>
-    <t>elc_wof_MEX_011</t>
-  </si>
-  <si>
-    <t>elc_wof_MEX_015</t>
-  </si>
-  <si>
-    <t>e_w489433441-400_MEX,e_w764377660-400_MEX</t>
-  </si>
-  <si>
-    <t>elc_wof_MEX_002</t>
-  </si>
-  <si>
-    <t>elc_wof_MEX_003</t>
-  </si>
-  <si>
-    <t>elc_wof_MEX_026</t>
-  </si>
-  <si>
-    <t>e_w325906414-400_MEX,e_w1143989565-400_MEX,e_w970712564-400_MEX</t>
-  </si>
-  <si>
-    <t>elc_wof_MEX_020</t>
-  </si>
-  <si>
-    <t>e_MX44-400_MEX,e_w370805988-400_MEX,e_MX40-400_MEX</t>
-  </si>
-  <si>
-    <t>elc_wof_MEX_001</t>
-  </si>
-  <si>
-    <t>elc_wof_MEX_008</t>
-  </si>
-  <si>
-    <t>elc_wof_MEX_007</t>
-  </si>
-  <si>
-    <t>e_w324339641-400_MEX,e_w1119978083-400_MEX</t>
-  </si>
-  <si>
-    <t>elc_wof_MEX_029</t>
-  </si>
-  <si>
-    <t>e_w1343929811-400_MEX,e_r16016425-400_MEX,e_w223990371-400_MEX</t>
-  </si>
-  <si>
-    <t>elc_wof_MEX_027</t>
-  </si>
-  <si>
-    <t>e_w316976706-400_MEX</t>
-  </si>
-  <si>
-    <t>elc_wof_MEX_017</t>
-  </si>
-  <si>
-    <t>e_MX60-400_MEX,e_MX49-400_MEX,e_MX44-400_MEX</t>
+    <t>elc_wof_MEX_004</t>
+  </si>
+  <si>
+    <t>elc_wof_MEX_023</t>
+  </si>
+  <si>
+    <t>e_w1181050521-400_MEX,e_w325974178-400_MEX,e_w325906414-400_MEX</t>
+  </si>
+  <si>
+    <t>elc_wof_MEX_016</t>
+  </si>
+  <si>
+    <t>e_MX33-400_MEX,e_w764377660-400_MEX</t>
+  </si>
+  <si>
+    <t>elc_wof_MEX_024</t>
+  </si>
+  <si>
+    <t>e_w324339640-400_MEX,e_w324339641-400_MEX</t>
+  </si>
+  <si>
+    <t>elc_wof_MEX_013</t>
+  </si>
+  <si>
+    <t>elc_wof_MEX_025</t>
+  </si>
+  <si>
+    <t>e_w1143989565-400_MEX,e_w326794464-400_MEX,e_w1137263495-400_MEX,e_w970712564-400_MEX</t>
   </si>
   <si>
     <t>elc_wof_MEX_005</t>
@@ -2509,72 +2575,6 @@
   </si>
   <si>
     <t>e_w316976706-400_MEX,e_w390018953-400_MEX</t>
-  </si>
-  <si>
-    <t>elc_wof_MEX_010</t>
-  </si>
-  <si>
-    <t>elc_wof_MEX_009</t>
-  </si>
-  <si>
-    <t>elc_wof_MEX_021</t>
-  </si>
-  <si>
-    <t>e_MX49-400_MEX,e_MX44-400_MEX</t>
-  </si>
-  <si>
-    <t>elc_wof_MEX_016</t>
-  </si>
-  <si>
-    <t>e_MX33-400_MEX,e_w764377660-400_MEX</t>
-  </si>
-  <si>
-    <t>elc_wof_MEX_012</t>
-  </si>
-  <si>
-    <t>e_w324339641-400_MEX,e_w339029834-400_MEX</t>
-  </si>
-  <si>
-    <t>elc_wof_MEX_019</t>
-  </si>
-  <si>
-    <t>e_MX40-400_MEX,e_MX36-400_MEX,e_w489433441-400_MEX,e_w764377660-400_MEX</t>
-  </si>
-  <si>
-    <t>elc_wof_MEX_014</t>
-  </si>
-  <si>
-    <t>e_w1119978083-400_MEX,e_w339029834-400_MEX</t>
-  </si>
-  <si>
-    <t>elc_wof_MEX_022</t>
-  </si>
-  <si>
-    <t>e_r16016425-400_MEX,e_w113005842-400_MEX</t>
-  </si>
-  <si>
-    <t>elc_wof_MEX_004</t>
-  </si>
-  <si>
-    <t>elc_wof_MEX_023</t>
-  </si>
-  <si>
-    <t>e_w1181050521-400_MEX,e_w325974178-400_MEX,e_w325906414-400_MEX</t>
-  </si>
-  <si>
-    <t>elc_wof_MEX_024</t>
-  </si>
-  <si>
-    <t>e_w324339640-400_MEX,e_w324339641-400_MEX</t>
-  </si>
-  <si>
-    <t>elc_wof_MEX_013</t>
-  </si>
-  <si>
-    <t>elc_wof_MEX_025</t>
-  </si>
-  <si>
-    <t>e_w1143989565-400_MEX,e_w326794464-400_MEX,e_w1137263495-400_MEX,e_w970712564-400_MEX</t>
   </si>
   <si>
     <t>e_won_MEX_001</t>
@@ -7825,7 +7825,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2EC6CDE6-2849-43F4-BA66-567F4BABC417}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D4A4F6D2-385E-48A6-8D7F-3109C70AA56B}">
   <dimension ref="B9:BD69"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -8063,16 +8063,16 @@
         <v>358</v>
       </c>
       <c r="Y11" t="s">
-        <v>349</v>
+        <v>298</v>
       </c>
       <c r="Z11" t="s">
         <v>480</v>
       </c>
       <c r="AA11">
-        <v>0.9962831220986742</v>
+        <v>0.99052534478032794</v>
       </c>
       <c r="AB11">
-        <v>68.14276152430682</v>
+        <v>173.702012360655</v>
       </c>
       <c r="AD11" t="s">
         <v>357</v>
@@ -8141,10 +8141,10 @@
         <v>766</v>
       </c>
       <c r="BC11">
-        <v>0.9941574321229002</v>
+        <v>0.99267872653249711</v>
       </c>
       <c r="BD11">
-        <v>107.1137444134967</v>
+        <v>134.22334690422022</v>
       </c>
     </row>
     <row r="12" spans="2:56">
@@ -8209,16 +8209,16 @@
         <v>362</v>
       </c>
       <c r="Y12" t="s">
-        <v>321</v>
+        <v>310</v>
       </c>
       <c r="Z12" t="s">
         <v>481</v>
       </c>
       <c r="AA12">
-        <v>0.99474921825793183</v>
+        <v>0.99533851522026684</v>
       </c>
       <c r="AB12">
-        <v>96.264331937916907</v>
+        <v>85.460554295108906</v>
       </c>
       <c r="AD12" t="s">
         <v>357</v>
@@ -8287,10 +8287,10 @@
         <v>768</v>
       </c>
       <c r="BC12">
-        <v>0.98902827014922345</v>
+        <v>0.99560935707608011</v>
       </c>
       <c r="BD12">
-        <v>201.14838059757037</v>
+        <v>80.495120271864536</v>
       </c>
     </row>
     <row r="13" spans="2:56">
@@ -8355,16 +8355,16 @@
         <v>364</v>
       </c>
       <c r="Y13" t="s">
-        <v>348</v>
+        <v>318</v>
       </c>
       <c r="Z13" t="s">
         <v>482</v>
       </c>
       <c r="AA13">
-        <v>0.99496672523274499</v>
+        <v>0.9910347770013892</v>
       </c>
       <c r="AB13">
-        <v>92.276704066342106</v>
+        <v>164.36242164119781</v>
       </c>
       <c r="AD13" t="s">
         <v>357</v>
@@ -8394,13 +8394,13 @@
         <v>630</v>
       </c>
       <c r="AN13" t="s">
-        <v>521</v>
+        <v>631</v>
       </c>
       <c r="AO13">
-        <v>0.99146458511356661</v>
+        <v>0.99166730629437405</v>
       </c>
       <c r="AP13">
-        <v>156.48260625127807</v>
+        <v>152.7660512698088</v>
       </c>
       <c r="AR13" t="s">
         <v>357</v>
@@ -8433,10 +8433,10 @@
         <v>770</v>
       </c>
       <c r="BC13">
-        <v>0.97887093776827594</v>
+        <v>0.98810956277351192</v>
       </c>
       <c r="BD13">
-        <v>387.36614091494118</v>
+        <v>217.99134915228177</v>
       </c>
     </row>
     <row r="14" spans="2:56">
@@ -8501,16 +8501,16 @@
         <v>366</v>
       </c>
       <c r="Y14" t="s">
-        <v>337</v>
+        <v>327</v>
       </c>
       <c r="Z14" t="s">
         <v>483</v>
       </c>
       <c r="AA14">
-        <v>0.99600522283071102</v>
+        <v>0.9980184525690815</v>
       </c>
       <c r="AB14">
-        <v>73.237581436964462</v>
+        <v>36.32836956683964</v>
       </c>
       <c r="AD14" t="s">
         <v>357</v>
@@ -8537,16 +8537,16 @@
         <v>544</v>
       </c>
       <c r="AM14" t="s">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="AN14" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="AO14">
-        <v>0.99549102504559717</v>
+        <v>0.98392602134528517</v>
       </c>
       <c r="AP14">
-        <v>82.664540830717883</v>
+        <v>294.6896086697721</v>
       </c>
       <c r="AR14" t="s">
         <v>357</v>
@@ -8576,7 +8576,7 @@
         <v>771</v>
       </c>
       <c r="BB14" t="s">
-        <v>655</v>
+        <v>700</v>
       </c>
       <c r="BC14">
         <v>0.99293011592915836</v>
@@ -8647,16 +8647,16 @@
         <v>368</v>
       </c>
       <c r="Y15" t="s">
-        <v>306</v>
+        <v>336</v>
       </c>
       <c r="Z15" t="s">
         <v>484</v>
       </c>
       <c r="AA15">
-        <v>0.98362146023706842</v>
+        <v>0.98650642341957129</v>
       </c>
       <c r="AB15">
-        <v>300.27322898707882</v>
+        <v>247.38223730786015</v>
       </c>
       <c r="AD15" t="s">
         <v>357</v>
@@ -8683,16 +8683,16 @@
         <v>546</v>
       </c>
       <c r="AM15" t="s">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="AN15" t="s">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="AO15">
-        <v>0.98007271259494255</v>
+        <v>0.98720186362781304</v>
       </c>
       <c r="AP15">
-        <v>365.33360242605363</v>
+        <v>234.63250015676121</v>
       </c>
       <c r="AR15" t="s">
         <v>357</v>
@@ -8722,13 +8722,13 @@
         <v>772</v>
       </c>
       <c r="BB15" t="s">
-        <v>773</v>
+        <v>633</v>
       </c>
       <c r="BC15">
-        <v>0.98810956277351192</v>
+        <v>0.97618766725836525</v>
       </c>
       <c r="BD15">
-        <v>217.99134915228177</v>
+        <v>436.55943359663644</v>
       </c>
     </row>
     <row r="16" spans="2:56">
@@ -8793,16 +8793,16 @@
         <v>370</v>
       </c>
       <c r="Y16" t="s">
-        <v>309</v>
+        <v>297</v>
       </c>
       <c r="Z16" t="s">
-        <v>485</v>
+        <v>480</v>
       </c>
       <c r="AA16">
-        <v>0.99264013999643841</v>
+        <v>0.99211999835767339</v>
       </c>
       <c r="AB16">
-        <v>134.93076673196322</v>
+        <v>144.46669677598709</v>
       </c>
       <c r="AD16" t="s">
         <v>357</v>
@@ -8829,16 +8829,16 @@
         <v>548</v>
       </c>
       <c r="AM16" t="s">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="AN16" t="s">
-        <v>498</v>
+        <v>637</v>
       </c>
       <c r="AO16">
-        <v>0.99276484208013105</v>
+        <v>0.99050084265243499</v>
       </c>
       <c r="AP16">
-        <v>132.64456186426332</v>
+        <v>174.15121803869192</v>
       </c>
       <c r="AR16" t="s">
         <v>357</v>
@@ -8865,16 +8865,16 @@
         <v>715</v>
       </c>
       <c r="BA16" t="s">
-        <v>774</v>
+        <v>773</v>
       </c>
       <c r="BB16" t="s">
-        <v>498</v>
+        <v>700</v>
       </c>
       <c r="BC16">
-        <v>0.97966892426826813</v>
+        <v>0.9941550644110243</v>
       </c>
       <c r="BD16">
-        <v>372.73638841508404</v>
+        <v>107.15715246455407</v>
       </c>
     </row>
     <row r="17" spans="2:56">
@@ -8939,16 +8939,16 @@
         <v>372</v>
       </c>
       <c r="Y17" t="s">
-        <v>352</v>
+        <v>307</v>
       </c>
       <c r="Z17" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="AA17">
-        <v>0.99665443666269515</v>
+        <v>0.98833460826933028</v>
       </c>
       <c r="AB17">
-        <v>61.335327850588769</v>
+        <v>213.86551506227875</v>
       </c>
       <c r="AD17" t="s">
         <v>357</v>
@@ -8975,16 +8975,16 @@
         <v>550</v>
       </c>
       <c r="AM17" t="s">
-        <v>636</v>
+        <v>638</v>
       </c>
       <c r="AN17" t="s">
-        <v>504</v>
+        <v>639</v>
       </c>
       <c r="AO17">
-        <v>0.9953231779810513</v>
+        <v>0.9955321750792081</v>
       </c>
       <c r="AP17">
-        <v>85.741737014060448</v>
+        <v>81.910123547850631</v>
       </c>
       <c r="AR17" t="s">
         <v>357</v>
@@ -9011,16 +9011,16 @@
         <v>717</v>
       </c>
       <c r="BA17" t="s">
+        <v>774</v>
+      </c>
+      <c r="BB17" t="s">
         <v>775</v>
       </c>
-      <c r="BB17" t="s">
-        <v>770</v>
-      </c>
       <c r="BC17">
-        <v>0.95949403051377602</v>
+        <v>0.97713203835019113</v>
       </c>
       <c r="BD17">
-        <v>742.60944058077234</v>
+        <v>419.24596357982909</v>
       </c>
     </row>
     <row r="18" spans="2:56">
@@ -9085,16 +9085,16 @@
         <v>374</v>
       </c>
       <c r="Y18" t="s">
-        <v>347</v>
+        <v>315</v>
       </c>
       <c r="Z18" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="AA18">
-        <v>0.99724701964333673</v>
+        <v>0.99382176509351161</v>
       </c>
       <c r="AB18">
-        <v>50.471306538827449</v>
+        <v>113.26763995228751</v>
       </c>
       <c r="AD18" t="s">
         <v>357</v>
@@ -9121,16 +9121,16 @@
         <v>552</v>
       </c>
       <c r="AM18" t="s">
-        <v>637</v>
+        <v>640</v>
       </c>
       <c r="AN18" t="s">
-        <v>638</v>
+        <v>641</v>
       </c>
       <c r="AO18">
-        <v>0.99784973993426285</v>
+        <v>0.99727438786147571</v>
       </c>
       <c r="AP18">
-        <v>39.4214345385139</v>
+        <v>49.969555872944532</v>
       </c>
       <c r="AR18" t="s">
         <v>357</v>
@@ -9163,10 +9163,10 @@
         <v>777</v>
       </c>
       <c r="BC18">
-        <v>0.99033461600205908</v>
+        <v>0.99576968882554151</v>
       </c>
       <c r="BD18">
-        <v>177.19870662891677</v>
+        <v>77.555704865071448</v>
       </c>
     </row>
     <row r="19" spans="2:56">
@@ -9231,16 +9231,16 @@
         <v>376</v>
       </c>
       <c r="Y19" t="s">
-        <v>350</v>
+        <v>317</v>
       </c>
       <c r="Z19" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="AA19">
-        <v>0.99698341997506779</v>
+        <v>0.99664712909564768</v>
       </c>
       <c r="AB19">
-        <v>55.30396712375795</v>
+        <v>61.46929991312588</v>
       </c>
       <c r="AD19" t="s">
         <v>357</v>
@@ -9267,16 +9267,16 @@
         <v>554</v>
       </c>
       <c r="AM19" t="s">
-        <v>639</v>
+        <v>642</v>
       </c>
       <c r="AN19" t="s">
-        <v>640</v>
+        <v>643</v>
       </c>
       <c r="AO19">
-        <v>0.99652238714397645</v>
+        <v>0.98300207162986786</v>
       </c>
       <c r="AP19">
-        <v>63.756235693765916</v>
+        <v>311.62868678575552</v>
       </c>
       <c r="AR19" t="s">
         <v>357</v>
@@ -9306,13 +9306,13 @@
         <v>778</v>
       </c>
       <c r="BB19" t="s">
-        <v>779</v>
+        <v>700</v>
       </c>
       <c r="BC19">
-        <v>0.9832797879436902</v>
+        <v>0.98933592887453392</v>
       </c>
       <c r="BD19">
-        <v>306.53722103234719</v>
+        <v>195.50797063354466</v>
       </c>
     </row>
     <row r="20" spans="2:56">
@@ -9377,16 +9377,16 @@
         <v>378</v>
       </c>
       <c r="Y20" t="s">
-        <v>301</v>
+        <v>323</v>
       </c>
       <c r="Z20" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="AA20">
-        <v>0.99655418190491885</v>
+        <v>0.99632613854098695</v>
       </c>
       <c r="AB20">
-        <v>63.173331743153703</v>
+        <v>67.354126748571815</v>
       </c>
       <c r="AD20" t="s">
         <v>357</v>
@@ -9413,16 +9413,16 @@
         <v>556</v>
       </c>
       <c r="AM20" t="s">
-        <v>641</v>
+        <v>644</v>
       </c>
       <c r="AN20" t="s">
-        <v>512</v>
+        <v>645</v>
       </c>
       <c r="AO20">
-        <v>0.99159807557278401</v>
+        <v>0.99075985723145521</v>
       </c>
       <c r="AP20">
-        <v>154.03528116562623</v>
+        <v>169.402617423321</v>
       </c>
       <c r="AR20" t="s">
         <v>357</v>
@@ -9449,16 +9449,16 @@
         <v>723</v>
       </c>
       <c r="BA20" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
       <c r="BB20" t="s">
-        <v>646</v>
+        <v>492</v>
       </c>
       <c r="BC20">
-        <v>0.97618766725836525</v>
+        <v>0.98910793924841989</v>
       </c>
       <c r="BD20">
-        <v>436.55943359663644</v>
+        <v>199.68778044563484</v>
       </c>
     </row>
     <row r="21" spans="2:56">
@@ -9523,16 +9523,16 @@
         <v>380</v>
       </c>
       <c r="Y21" t="s">
-        <v>316</v>
+        <v>340</v>
       </c>
       <c r="Z21" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="AA21">
-        <v>0.99532495664776788</v>
+        <v>0.99498089833731562</v>
       </c>
       <c r="AB21">
-        <v>85.709128124254633</v>
+        <v>92.016863815880541</v>
       </c>
       <c r="AD21" t="s">
         <v>357</v>
@@ -9559,16 +9559,16 @@
         <v>558</v>
       </c>
       <c r="AM21" t="s">
-        <v>642</v>
+        <v>646</v>
       </c>
       <c r="AN21" t="s">
-        <v>521</v>
+        <v>647</v>
       </c>
       <c r="AO21">
-        <v>0.98819864394083989</v>
+        <v>0.99719980724440771</v>
       </c>
       <c r="AP21">
-        <v>216.35819441793581</v>
+        <v>51.336867185859347</v>
       </c>
       <c r="AR21" t="s">
         <v>357</v>
@@ -9595,16 +9595,16 @@
         <v>725</v>
       </c>
       <c r="BA21" t="s">
+        <v>780</v>
+      </c>
+      <c r="BB21" t="s">
         <v>781</v>
       </c>
-      <c r="BB21" t="s">
-        <v>655</v>
-      </c>
       <c r="BC21">
-        <v>0.9941550644110243</v>
+        <v>0.98350082174829745</v>
       </c>
       <c r="BD21">
-        <v>107.15715246455407</v>
+        <v>302.48493461454615</v>
       </c>
     </row>
     <row r="22" spans="2:56">
@@ -9669,16 +9669,16 @@
         <v>382</v>
       </c>
       <c r="Y22" t="s">
-        <v>342</v>
+        <v>335</v>
       </c>
       <c r="Z22" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="AA22">
-        <v>0.99794405176225942</v>
+        <v>0.99367247562142269</v>
       </c>
       <c r="AB22">
-        <v>37.692384358577527</v>
+        <v>116.00461360725107</v>
       </c>
       <c r="AD22" t="s">
         <v>357</v>
@@ -9705,16 +9705,16 @@
         <v>560</v>
       </c>
       <c r="AM22" t="s">
-        <v>643</v>
+        <v>648</v>
       </c>
       <c r="AN22" t="s">
-        <v>644</v>
+        <v>649</v>
       </c>
       <c r="AO22">
-        <v>0.99783515171992265</v>
+        <v>0.99712587624395799</v>
       </c>
       <c r="AP22">
-        <v>39.688885134750748</v>
+        <v>52.69226886077093</v>
       </c>
       <c r="AR22" t="s">
         <v>357</v>
@@ -9744,13 +9744,13 @@
         <v>782</v>
       </c>
       <c r="BB22" t="s">
-        <v>783</v>
+        <v>480</v>
       </c>
       <c r="BC22">
-        <v>0.97713203835019113</v>
+        <v>0.97966892426826813</v>
       </c>
       <c r="BD22">
-        <v>419.24596357982909</v>
+        <v>372.73638841508404</v>
       </c>
     </row>
     <row r="23" spans="2:56">
@@ -9815,16 +9815,16 @@
         <v>384</v>
       </c>
       <c r="Y23" t="s">
-        <v>302</v>
+        <v>329</v>
       </c>
       <c r="Z23" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="AA23">
-        <v>0.98305355992983057</v>
+        <v>0.98962497706829622</v>
       </c>
       <c r="AB23">
-        <v>310.68473461977231</v>
+        <v>190.20875374790245</v>
       </c>
       <c r="AD23" t="s">
         <v>357</v>
@@ -9851,16 +9851,16 @@
         <v>562</v>
       </c>
       <c r="AM23" t="s">
-        <v>645</v>
+        <v>650</v>
       </c>
       <c r="AN23" t="s">
-        <v>646</v>
+        <v>531</v>
       </c>
       <c r="AO23">
-        <v>0.98392602134528517</v>
+        <v>0.99159807557278401</v>
       </c>
       <c r="AP23">
-        <v>294.6896086697721</v>
+        <v>154.03528116562623</v>
       </c>
       <c r="AR23" t="s">
         <v>357</v>
@@ -9887,16 +9887,16 @@
         <v>729</v>
       </c>
       <c r="BA23" t="s">
+        <v>783</v>
+      </c>
+      <c r="BB23" t="s">
         <v>784</v>
       </c>
-      <c r="BB23" t="s">
-        <v>785</v>
-      </c>
       <c r="BC23">
-        <v>0.99576968882554151</v>
+        <v>0.95949403051377602</v>
       </c>
       <c r="BD23">
-        <v>77.555704865071448</v>
+        <v>742.60944058077234</v>
       </c>
     </row>
     <row r="24" spans="2:56">
@@ -9961,16 +9961,16 @@
         <v>386</v>
       </c>
       <c r="Y24" t="s">
-        <v>341</v>
+        <v>304</v>
       </c>
       <c r="Z24" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="AA24">
-        <v>0.99526736010661099</v>
+        <v>0.99148269770211572</v>
       </c>
       <c r="AB24">
-        <v>86.765064712131235</v>
+        <v>156.15054212787871</v>
       </c>
       <c r="AD24" t="s">
         <v>357</v>
@@ -9997,16 +9997,16 @@
         <v>564</v>
       </c>
       <c r="AM24" t="s">
-        <v>647</v>
+        <v>651</v>
       </c>
       <c r="AN24" t="s">
-        <v>648</v>
+        <v>485</v>
       </c>
       <c r="AO24">
-        <v>0.98720186362781304</v>
+        <v>0.98819864394083989</v>
       </c>
       <c r="AP24">
-        <v>234.63250015676121</v>
+        <v>216.35819441793581</v>
       </c>
       <c r="AR24" t="s">
         <v>357</v>
@@ -10033,16 +10033,16 @@
         <v>731</v>
       </c>
       <c r="BA24" t="s">
+        <v>785</v>
+      </c>
+      <c r="BB24" t="s">
         <v>786</v>
       </c>
-      <c r="BB24" t="s">
-        <v>787</v>
-      </c>
       <c r="BC24">
-        <v>0.99342309909810012</v>
+        <v>0.99033461600205908</v>
       </c>
       <c r="BD24">
-        <v>120.57651653483084</v>
+        <v>177.19870662891677</v>
       </c>
     </row>
     <row r="25" spans="2:56">
@@ -10107,16 +10107,16 @@
         <v>388</v>
       </c>
       <c r="Y25" t="s">
-        <v>331</v>
+        <v>346</v>
       </c>
       <c r="Z25" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="AA25">
-        <v>0.99536018066282017</v>
+        <v>0.9970215739199545</v>
       </c>
       <c r="AB25">
-        <v>85.06335451496426</v>
+        <v>54.604478134167074</v>
       </c>
       <c r="AD25" t="s">
         <v>357</v>
@@ -10143,16 +10143,16 @@
         <v>566</v>
       </c>
       <c r="AM25" t="s">
-        <v>649</v>
+        <v>652</v>
       </c>
       <c r="AN25" t="s">
-        <v>650</v>
+        <v>653</v>
       </c>
       <c r="AO25">
-        <v>0.99050084265243499</v>
+        <v>0.99783515171992265</v>
       </c>
       <c r="AP25">
-        <v>174.15121803869192</v>
+        <v>39.688885134750748</v>
       </c>
       <c r="AR25" t="s">
         <v>357</v>
@@ -10179,16 +10179,16 @@
         <v>733</v>
       </c>
       <c r="BA25" t="s">
+        <v>787</v>
+      </c>
+      <c r="BB25" t="s">
         <v>788</v>
       </c>
-      <c r="BB25" t="s">
-        <v>789</v>
-      </c>
       <c r="BC25">
-        <v>0.9895689701647985</v>
+        <v>0.99176274648027563</v>
       </c>
       <c r="BD25">
-        <v>191.23554697869403</v>
+        <v>151.01631452828045</v>
       </c>
     </row>
     <row r="26" spans="2:56">
@@ -10253,16 +10253,16 @@
         <v>390</v>
       </c>
       <c r="Y26" t="s">
-        <v>303</v>
+        <v>330</v>
       </c>
       <c r="Z26" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="AA26">
-        <v>0.98327228856468729</v>
+        <v>0.9963692742640502</v>
       </c>
       <c r="AB26">
-        <v>306.67470964740028</v>
+        <v>66.563305159080301</v>
       </c>
       <c r="AD26" t="s">
         <v>357</v>
@@ -10289,16 +10289,16 @@
         <v>568</v>
       </c>
       <c r="AM26" t="s">
-        <v>651</v>
+        <v>654</v>
       </c>
       <c r="AN26" t="s">
-        <v>652</v>
+        <v>531</v>
       </c>
       <c r="AO26">
-        <v>0.9955321750792081</v>
+        <v>0.99142662212165156</v>
       </c>
       <c r="AP26">
-        <v>81.910123547850631</v>
+        <v>157.17859443638787</v>
       </c>
       <c r="AR26" t="s">
         <v>357</v>
@@ -10325,16 +10325,16 @@
         <v>735</v>
       </c>
       <c r="BA26" t="s">
+        <v>789</v>
+      </c>
+      <c r="BB26" t="s">
         <v>790</v>
       </c>
-      <c r="BB26" t="s">
-        <v>791</v>
-      </c>
       <c r="BC26">
-        <v>0.976919795397307</v>
+        <v>0.9835548687728024</v>
       </c>
       <c r="BD26">
-        <v>423.13708438270464</v>
+        <v>301.49407249862264</v>
       </c>
     </row>
     <row r="27" spans="2:56">
@@ -10399,16 +10399,16 @@
         <v>392</v>
       </c>
       <c r="Y27" t="s">
-        <v>311</v>
+        <v>320</v>
       </c>
       <c r="Z27" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="AA27">
-        <v>0.99608527259090462</v>
+        <v>0.9936042103238425</v>
       </c>
       <c r="AB27">
-        <v>71.770002500082597</v>
+        <v>117.25614406288832</v>
       </c>
       <c r="AD27" t="s">
         <v>357</v>
@@ -10435,16 +10435,16 @@
         <v>570</v>
       </c>
       <c r="AM27" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
       <c r="AN27" t="s">
-        <v>648</v>
+        <v>656</v>
       </c>
       <c r="AO27">
-        <v>0.98296108964477757</v>
+        <v>0.99234453653341004</v>
       </c>
       <c r="AP27">
-        <v>312.38002317907871</v>
+        <v>140.35016355414848</v>
       </c>
       <c r="AR27" t="s">
         <v>357</v>
@@ -10471,16 +10471,16 @@
         <v>737</v>
       </c>
       <c r="BA27" t="s">
+        <v>791</v>
+      </c>
+      <c r="BB27" t="s">
         <v>792</v>
       </c>
-      <c r="BB27" t="s">
-        <v>793</v>
-      </c>
       <c r="BC27">
-        <v>0.99088318071669168</v>
+        <v>0.9832797879436902</v>
       </c>
       <c r="BD27">
-        <v>167.14168686065315</v>
+        <v>306.53722103234719</v>
       </c>
     </row>
     <row r="28" spans="2:56">
@@ -10545,16 +10545,16 @@
         <v>394</v>
       </c>
       <c r="Y28" t="s">
-        <v>322</v>
+        <v>339</v>
       </c>
       <c r="Z28" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="AA28">
-        <v>0.99688420747686357</v>
+        <v>0.98700404273476772</v>
       </c>
       <c r="AB28">
-        <v>57.122862924167315</v>
+        <v>238.25921652925925</v>
       </c>
       <c r="AD28" t="s">
         <v>357</v>
@@ -10581,16 +10581,16 @@
         <v>572</v>
       </c>
       <c r="AM28" t="s">
-        <v>654</v>
+        <v>657</v>
       </c>
       <c r="AN28" t="s">
-        <v>655</v>
+        <v>658</v>
       </c>
       <c r="AO28">
-        <v>0.9963831774222891</v>
+        <v>0.99443256604953767</v>
       </c>
       <c r="AP28">
-        <v>66.308413924699082</v>
+        <v>102.0696224251428</v>
       </c>
       <c r="AR28" t="s">
         <v>357</v>
@@ -10617,16 +10617,16 @@
         <v>739</v>
       </c>
       <c r="BA28" t="s">
+        <v>793</v>
+      </c>
+      <c r="BB28" t="s">
         <v>794</v>
       </c>
-      <c r="BB28" t="s">
-        <v>655</v>
-      </c>
       <c r="BC28">
-        <v>0.98933592887453392</v>
+        <v>0.99342309909810012</v>
       </c>
       <c r="BD28">
-        <v>195.50797063354466</v>
+        <v>120.57651653483084</v>
       </c>
     </row>
     <row r="29" spans="2:56">
@@ -10691,16 +10691,16 @@
         <v>396</v>
       </c>
       <c r="Y29" t="s">
-        <v>298</v>
+        <v>302</v>
       </c>
       <c r="Z29" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="AA29">
-        <v>0.99052534478032794</v>
+        <v>0.98305355992983057</v>
       </c>
       <c r="AB29">
-        <v>173.702012360655</v>
+        <v>310.68473461977231</v>
       </c>
       <c r="AD29" t="s">
         <v>357</v>
@@ -10727,16 +10727,16 @@
         <v>574</v>
       </c>
       <c r="AM29" t="s">
-        <v>656</v>
+        <v>659</v>
       </c>
       <c r="AN29" t="s">
-        <v>657</v>
+        <v>660</v>
       </c>
       <c r="AO29">
-        <v>0.99380770610317104</v>
+        <v>0.99636332294747387</v>
       </c>
       <c r="AP29">
-        <v>113.52538810853157</v>
+        <v>66.672412629645152</v>
       </c>
       <c r="AR29" t="s">
         <v>357</v>
@@ -10766,13 +10766,13 @@
         <v>795</v>
       </c>
       <c r="BB29" t="s">
-        <v>528</v>
+        <v>796</v>
       </c>
       <c r="BC29">
-        <v>0.98910793924841989</v>
+        <v>0.9895689701647985</v>
       </c>
       <c r="BD29">
-        <v>199.68778044563484</v>
+        <v>191.23554697869403</v>
       </c>
     </row>
     <row r="30" spans="2:56">
@@ -10837,16 +10837,16 @@
         <v>398</v>
       </c>
       <c r="Y30" t="s">
-        <v>310</v>
+        <v>341</v>
       </c>
       <c r="Z30" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="AA30">
-        <v>0.99533851522026684</v>
+        <v>0.99526736010661099</v>
       </c>
       <c r="AB30">
-        <v>85.460554295108906</v>
+        <v>86.765064712131235</v>
       </c>
       <c r="AD30" t="s">
         <v>357</v>
@@ -10873,16 +10873,16 @@
         <v>576</v>
       </c>
       <c r="AM30" t="s">
-        <v>658</v>
+        <v>661</v>
       </c>
       <c r="AN30" t="s">
-        <v>659</v>
+        <v>662</v>
       </c>
       <c r="AO30">
-        <v>0.99679454360228514</v>
+        <v>0.99611299874662873</v>
       </c>
       <c r="AP30">
-        <v>58.766700624772731</v>
+        <v>71.261689645139711</v>
       </c>
       <c r="AR30" t="s">
         <v>357</v>
@@ -10909,16 +10909,16 @@
         <v>743</v>
       </c>
       <c r="BA30" t="s">
-        <v>796</v>
+        <v>797</v>
       </c>
       <c r="BB30" t="s">
-        <v>797</v>
+        <v>798</v>
       </c>
       <c r="BC30">
-        <v>0.98350082174829745</v>
+        <v>0.9941574321229002</v>
       </c>
       <c r="BD30">
-        <v>302.48493461454615</v>
+        <v>107.1137444134967</v>
       </c>
     </row>
     <row r="31" spans="2:56">
@@ -10983,16 +10983,16 @@
         <v>400</v>
       </c>
       <c r="Y31" t="s">
-        <v>318</v>
+        <v>331</v>
       </c>
       <c r="Z31" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="AA31">
-        <v>0.9910347770013892</v>
+        <v>0.99536018066282017</v>
       </c>
       <c r="AB31">
-        <v>164.36242164119781</v>
+        <v>85.06335451496426</v>
       </c>
       <c r="AD31" t="s">
         <v>357</v>
@@ -11019,16 +11019,16 @@
         <v>578</v>
       </c>
       <c r="AM31" t="s">
-        <v>660</v>
+        <v>663</v>
       </c>
       <c r="AN31" t="s">
-        <v>661</v>
+        <v>664</v>
       </c>
       <c r="AO31">
-        <v>0.99727438786147571</v>
+        <v>0.99410266459132846</v>
       </c>
       <c r="AP31">
-        <v>49.969555872944532</v>
+        <v>108.11781582564529</v>
       </c>
       <c r="AR31" t="s">
         <v>357</v>
@@ -11055,16 +11055,16 @@
         <v>745</v>
       </c>
       <c r="BA31" t="s">
-        <v>798</v>
+        <v>799</v>
       </c>
       <c r="BB31" t="s">
-        <v>799</v>
+        <v>800</v>
       </c>
       <c r="BC31">
-        <v>0.99085132728755021</v>
+        <v>0.98902827014922345</v>
       </c>
       <c r="BD31">
-        <v>167.72566639491282</v>
+        <v>201.14838059757037</v>
       </c>
     </row>
     <row r="32" spans="2:56">
@@ -11129,16 +11129,16 @@
         <v>402</v>
       </c>
       <c r="Y32" t="s">
-        <v>327</v>
+        <v>312</v>
       </c>
       <c r="Z32" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="AA32">
-        <v>0.9980184525690815</v>
+        <v>0.99092468152945157</v>
       </c>
       <c r="AB32">
-        <v>36.32836956683964</v>
+        <v>166.38083862672116</v>
       </c>
       <c r="AD32" t="s">
         <v>357</v>
@@ -11165,16 +11165,16 @@
         <v>580</v>
       </c>
       <c r="AM32" t="s">
-        <v>662</v>
+        <v>665</v>
       </c>
       <c r="AN32" t="s">
-        <v>663</v>
+        <v>666</v>
       </c>
       <c r="AO32">
-        <v>0.98300207162986786</v>
+        <v>0.99072079741836661</v>
       </c>
       <c r="AP32">
-        <v>311.62868678575552</v>
+        <v>170.11871399661308</v>
       </c>
       <c r="AR32" t="s">
         <v>357</v>
@@ -11201,16 +11201,16 @@
         <v>747</v>
       </c>
       <c r="BA32" t="s">
-        <v>800</v>
+        <v>801</v>
       </c>
       <c r="BB32" t="s">
-        <v>801</v>
+        <v>784</v>
       </c>
       <c r="BC32">
-        <v>0.99176274648027563</v>
+        <v>0.97887093776827594</v>
       </c>
       <c r="BD32">
-        <v>151.01631452828045</v>
+        <v>387.36614091494118</v>
       </c>
     </row>
     <row r="33" spans="2:56">
@@ -11275,16 +11275,16 @@
         <v>404</v>
       </c>
       <c r="Y33" t="s">
-        <v>336</v>
+        <v>313</v>
       </c>
       <c r="Z33" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="AA33">
-        <v>0.98650642341957129</v>
+        <v>0.99431419492629725</v>
       </c>
       <c r="AB33">
-        <v>247.38223730786015</v>
+        <v>104.23975968455018</v>
       </c>
       <c r="AD33" t="s">
         <v>357</v>
@@ -11311,16 +11311,16 @@
         <v>582</v>
       </c>
       <c r="AM33" t="s">
-        <v>664</v>
+        <v>667</v>
       </c>
       <c r="AN33" t="s">
-        <v>665</v>
+        <v>668</v>
       </c>
       <c r="AO33">
-        <v>0.99075985723145521</v>
+        <v>0.99501643023888209</v>
       </c>
       <c r="AP33">
-        <v>169.402617423321</v>
+        <v>91.36544562049427</v>
       </c>
       <c r="AR33" t="s">
         <v>357</v>
@@ -11350,13 +11350,13 @@
         <v>802</v>
       </c>
       <c r="BB33" t="s">
-        <v>803</v>
+        <v>520</v>
       </c>
       <c r="BC33">
-        <v>0.9835548687728024</v>
+        <v>0.97764590548227914</v>
       </c>
       <c r="BD33">
-        <v>301.49407249862264</v>
+        <v>409.8250661582149</v>
       </c>
     </row>
     <row r="34" spans="2:56">
@@ -11421,16 +11421,16 @@
         <v>406</v>
       </c>
       <c r="Y34" t="s">
-        <v>312</v>
+        <v>345</v>
       </c>
       <c r="Z34" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="AA34">
-        <v>0.99092468152945157</v>
+        <v>0.99627916803835959</v>
       </c>
       <c r="AB34">
-        <v>166.38083862672116</v>
+        <v>68.215252630073479</v>
       </c>
       <c r="AD34" t="s">
         <v>357</v>
@@ -11457,16 +11457,16 @@
         <v>584</v>
       </c>
       <c r="AM34" t="s">
-        <v>666</v>
+        <v>669</v>
       </c>
       <c r="AN34" t="s">
-        <v>667</v>
+        <v>670</v>
       </c>
       <c r="AO34">
-        <v>0.99719980724440771</v>
+        <v>0.99367595643491624</v>
       </c>
       <c r="AP34">
-        <v>51.336867185859347</v>
+        <v>115.94079869320176</v>
       </c>
       <c r="AR34" t="s">
         <v>357</v>
@@ -11493,16 +11493,16 @@
         <v>751</v>
       </c>
       <c r="BA34" t="s">
+        <v>803</v>
+      </c>
+      <c r="BB34" t="s">
         <v>804</v>
       </c>
-      <c r="BB34" t="s">
-        <v>805</v>
-      </c>
       <c r="BC34">
-        <v>0.99267872653249711</v>
+        <v>0.99603912935693217</v>
       </c>
       <c r="BD34">
-        <v>134.22334690422022</v>
+        <v>72.615961789576843</v>
       </c>
     </row>
     <row r="35" spans="2:56">
@@ -11567,16 +11567,16 @@
         <v>408</v>
       </c>
       <c r="Y35" t="s">
-        <v>313</v>
+        <v>338</v>
       </c>
       <c r="Z35" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="AA35">
-        <v>0.99431419492629725</v>
+        <v>0.99512875041881377</v>
       </c>
       <c r="AB35">
-        <v>104.23975968455018</v>
+        <v>89.306242321746609</v>
       </c>
       <c r="AD35" t="s">
         <v>357</v>
@@ -11603,16 +11603,16 @@
         <v>586</v>
       </c>
       <c r="AM35" t="s">
-        <v>668</v>
+        <v>671</v>
       </c>
       <c r="AN35" t="s">
-        <v>669</v>
+        <v>672</v>
       </c>
       <c r="AO35">
-        <v>0.99712587624395799</v>
+        <v>0.98007271259494255</v>
       </c>
       <c r="AP35">
-        <v>52.69226886077093</v>
+        <v>365.33360242605363</v>
       </c>
       <c r="AR35" t="s">
         <v>357</v>
@@ -11639,16 +11639,16 @@
         <v>753</v>
       </c>
       <c r="BA35" t="s">
+        <v>805</v>
+      </c>
+      <c r="BB35" t="s">
         <v>806</v>
       </c>
-      <c r="BB35" t="s">
-        <v>807</v>
-      </c>
       <c r="BC35">
-        <v>0.99560935707608011</v>
+        <v>0.99085132728755021</v>
       </c>
       <c r="BD35">
-        <v>80.495120271864536</v>
+        <v>167.72566639491282</v>
       </c>
     </row>
     <row r="36" spans="2:56">
@@ -11713,16 +11713,16 @@
         <v>410</v>
       </c>
       <c r="Y36" t="s">
-        <v>345</v>
+        <v>299</v>
       </c>
       <c r="Z36" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="AA36">
-        <v>0.99627916803835959</v>
+        <v>0.97936066022114188</v>
       </c>
       <c r="AB36">
-        <v>68.215252630073479</v>
+        <v>378.38789594573325</v>
       </c>
       <c r="AD36" t="s">
         <v>357</v>
@@ -11749,16 +11749,16 @@
         <v>588</v>
       </c>
       <c r="AM36" t="s">
-        <v>670</v>
+        <v>673</v>
       </c>
       <c r="AN36" t="s">
-        <v>671</v>
+        <v>480</v>
       </c>
       <c r="AO36">
-        <v>0.99410266459132846</v>
+        <v>0.99276484208013105</v>
       </c>
       <c r="AP36">
-        <v>108.11781582564529</v>
+        <v>132.64456186426332</v>
       </c>
       <c r="AR36" t="s">
         <v>357</v>
@@ -11785,16 +11785,16 @@
         <v>755</v>
       </c>
       <c r="BA36" t="s">
+        <v>807</v>
+      </c>
+      <c r="BB36" t="s">
         <v>808</v>
       </c>
-      <c r="BB36" t="s">
-        <v>531</v>
-      </c>
       <c r="BC36">
-        <v>0.97764590548227914</v>
+        <v>0.93550473459950212</v>
       </c>
       <c r="BD36">
-        <v>409.8250661582149</v>
+        <v>1182.4131990091278</v>
       </c>
     </row>
     <row r="37" spans="2:56">
@@ -11859,16 +11859,16 @@
         <v>412</v>
       </c>
       <c r="Y37" t="s">
-        <v>338</v>
+        <v>354</v>
       </c>
       <c r="Z37" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="AA37">
-        <v>0.99512875041881377</v>
+        <v>0.9979650023251263</v>
       </c>
       <c r="AB37">
-        <v>89.306242321746609</v>
+        <v>37.308290706018212</v>
       </c>
       <c r="AD37" t="s">
         <v>357</v>
@@ -11895,16 +11895,16 @@
         <v>590</v>
       </c>
       <c r="AM37" t="s">
-        <v>672</v>
+        <v>674</v>
       </c>
       <c r="AN37" t="s">
-        <v>673</v>
+        <v>501</v>
       </c>
       <c r="AO37">
-        <v>0.99072079741836661</v>
+        <v>0.9953231779810513</v>
       </c>
       <c r="AP37">
-        <v>170.11871399661308</v>
+        <v>85.741737014060448</v>
       </c>
       <c r="AR37" t="s">
         <v>357</v>
@@ -11934,13 +11934,13 @@
         <v>809</v>
       </c>
       <c r="BB37" t="s">
-        <v>810</v>
+        <v>664</v>
       </c>
       <c r="BC37">
-        <v>0.99603912935693217</v>
+        <v>0.99006235484112581</v>
       </c>
       <c r="BD37">
-        <v>72.615961789576843</v>
+        <v>182.19016124602703</v>
       </c>
     </row>
     <row r="38" spans="2:56">
@@ -12005,16 +12005,16 @@
         <v>414</v>
       </c>
       <c r="Y38" t="s">
-        <v>319</v>
+        <v>332</v>
       </c>
       <c r="Z38" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="AA38">
-        <v>0.99312342621982508</v>
+        <v>0.99672243529281113</v>
       </c>
       <c r="AB38">
-        <v>126.07051930320748</v>
+        <v>60.088686298463386</v>
       </c>
       <c r="AD38" t="s">
         <v>357</v>
@@ -12041,16 +12041,16 @@
         <v>592</v>
       </c>
       <c r="AM38" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="AN38" t="s">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="AO38">
-        <v>0.99501643023888209</v>
+        <v>0.99784973993426285</v>
       </c>
       <c r="AP38">
-        <v>91.36544562049427</v>
+        <v>39.4214345385139</v>
       </c>
       <c r="AR38" t="s">
         <v>357</v>
@@ -12077,16 +12077,16 @@
         <v>759</v>
       </c>
       <c r="BA38" t="s">
+        <v>810</v>
+      </c>
+      <c r="BB38" t="s">
         <v>811</v>
       </c>
-      <c r="BB38" t="s">
-        <v>812</v>
-      </c>
       <c r="BC38">
-        <v>0.93550473459950212</v>
+        <v>0.99266053819235223</v>
       </c>
       <c r="BD38">
-        <v>1182.4131990091278</v>
+        <v>134.55679980687663</v>
       </c>
     </row>
     <row r="39" spans="2:56">
@@ -12151,16 +12151,16 @@
         <v>416</v>
       </c>
       <c r="Y39" t="s">
-        <v>355</v>
+        <v>319</v>
       </c>
       <c r="Z39" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="AA39">
-        <v>0.99752287241357906</v>
+        <v>0.99312342621982508</v>
       </c>
       <c r="AB39">
-        <v>45.414005751051391</v>
+        <v>126.07051930320748</v>
       </c>
       <c r="AD39" t="s">
         <v>357</v>
@@ -12187,16 +12187,16 @@
         <v>594</v>
       </c>
       <c r="AM39" t="s">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="AN39" t="s">
-        <v>677</v>
+        <v>492</v>
       </c>
       <c r="AO39">
-        <v>0.99367595643491624</v>
+        <v>0.99089429663374551</v>
       </c>
       <c r="AP39">
-        <v>115.94079869320176</v>
+        <v>166.93789504799881</v>
       </c>
       <c r="AR39" t="s">
         <v>357</v>
@@ -12223,16 +12223,16 @@
         <v>761</v>
       </c>
       <c r="BA39" t="s">
+        <v>812</v>
+      </c>
+      <c r="BB39" t="s">
         <v>813</v>
       </c>
-      <c r="BB39" t="s">
-        <v>671</v>
-      </c>
       <c r="BC39">
-        <v>0.99006235484112581</v>
+        <v>0.976919795397307</v>
       </c>
       <c r="BD39">
-        <v>182.19016124602703</v>
+        <v>423.13708438270464</v>
       </c>
     </row>
     <row r="40" spans="2:56">
@@ -12297,16 +12297,16 @@
         <v>418</v>
       </c>
       <c r="Y40" t="s">
-        <v>299</v>
+        <v>355</v>
       </c>
       <c r="Z40" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="AA40">
-        <v>0.97936066022114188</v>
+        <v>0.99752287241357906</v>
       </c>
       <c r="AB40">
-        <v>378.38789594573325</v>
+        <v>45.414005751051391</v>
       </c>
       <c r="AD40" t="s">
         <v>357</v>
@@ -12339,10 +12339,10 @@
         <v>679</v>
       </c>
       <c r="AO40">
-        <v>0.99644445157760886</v>
+        <v>0.99724587877560378</v>
       </c>
       <c r="AP40">
-        <v>65.185054410503341</v>
+        <v>50.492222447263664</v>
       </c>
       <c r="AR40" t="s">
         <v>357</v>
@@ -12375,10 +12375,10 @@
         <v>815</v>
       </c>
       <c r="BC40">
-        <v>0.99266053819235223</v>
+        <v>0.99088318071669168</v>
       </c>
       <c r="BD40">
-        <v>134.55679980687663</v>
+        <v>167.14168686065315</v>
       </c>
     </row>
     <row r="41" spans="2:56">
@@ -12443,16 +12443,16 @@
         <v>420</v>
       </c>
       <c r="Y41" t="s">
-        <v>354</v>
+        <v>344</v>
       </c>
       <c r="Z41" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="AA41">
-        <v>0.9979650023251263</v>
+        <v>0.99634720436029245</v>
       </c>
       <c r="AB41">
-        <v>37.308290706018212</v>
+        <v>66.967920061305705</v>
       </c>
       <c r="AD41" t="s">
         <v>357</v>
@@ -12485,10 +12485,10 @@
         <v>681</v>
       </c>
       <c r="AO41">
-        <v>0.99593921525806983</v>
+        <v>0.99687395765771536</v>
       </c>
       <c r="AP41">
-        <v>74.447720268718882</v>
+        <v>57.310776275218892</v>
       </c>
     </row>
     <row r="42" spans="2:56">
@@ -12553,16 +12553,16 @@
         <v>422</v>
       </c>
       <c r="Y42" t="s">
-        <v>332</v>
+        <v>324</v>
       </c>
       <c r="Z42" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="AA42">
-        <v>0.99672243529281113</v>
+        <v>0.99690900069701904</v>
       </c>
       <c r="AB42">
-        <v>60.088686298463386</v>
+        <v>56.668320554651658</v>
       </c>
       <c r="AD42" t="s">
         <v>357</v>
@@ -12592,13 +12592,13 @@
         <v>682</v>
       </c>
       <c r="AN42" t="s">
-        <v>683</v>
+        <v>501</v>
       </c>
       <c r="AO42">
-        <v>0.99516270130765094</v>
+        <v>0.99336120165168273</v>
       </c>
       <c r="AP42">
-        <v>88.68380935973272</v>
+        <v>121.71130305248386</v>
       </c>
     </row>
     <row r="43" spans="2:56">
@@ -12663,16 +12663,16 @@
         <v>424</v>
       </c>
       <c r="Y43" t="s">
-        <v>308</v>
+        <v>343</v>
       </c>
       <c r="Z43" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="AA43">
-        <v>0.99468188905612376</v>
+        <v>0.98659243069702229</v>
       </c>
       <c r="AB43">
-        <v>97.498700637730266</v>
+        <v>245.80543722125813</v>
       </c>
       <c r="AD43" t="s">
         <v>357</v>
@@ -12699,16 +12699,16 @@
         <v>602</v>
       </c>
       <c r="AM43" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="AN43" t="s">
-        <v>685</v>
+        <v>485</v>
       </c>
       <c r="AO43">
-        <v>0.99373433598681304</v>
+        <v>0.99146458511356661</v>
       </c>
       <c r="AP43">
-        <v>114.8705069084281</v>
+        <v>156.48260625127807</v>
       </c>
     </row>
     <row r="44" spans="2:56">
@@ -12773,16 +12773,16 @@
         <v>426</v>
       </c>
       <c r="Y44" t="s">
-        <v>326</v>
+        <v>301</v>
       </c>
       <c r="Z44" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="AA44">
-        <v>0.99798506730783287</v>
+        <v>0.99655418190491885</v>
       </c>
       <c r="AB44">
-        <v>36.940432689730294</v>
+        <v>63.173331743153703</v>
       </c>
       <c r="AD44" t="s">
         <v>357</v>
@@ -12809,16 +12809,16 @@
         <v>604</v>
       </c>
       <c r="AM44" t="s">
-        <v>686</v>
+        <v>684</v>
       </c>
       <c r="AN44" t="s">
-        <v>687</v>
+        <v>685</v>
       </c>
       <c r="AO44">
-        <v>0.99674459930858406</v>
+        <v>0.99549102504559717</v>
       </c>
       <c r="AP44">
-        <v>59.682346009292083</v>
+        <v>82.664540830717883</v>
       </c>
     </row>
     <row r="45" spans="2:56">
@@ -12883,16 +12883,16 @@
         <v>428</v>
       </c>
       <c r="Y45" t="s">
-        <v>333</v>
+        <v>316</v>
       </c>
       <c r="Z45" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="AA45">
-        <v>0.99710009105712261</v>
+        <v>0.99532495664776788</v>
       </c>
       <c r="AB45">
-        <v>53.164997286085928</v>
+        <v>85.709128124254633</v>
       </c>
       <c r="AD45" t="s">
         <v>357</v>
@@ -12919,16 +12919,16 @@
         <v>606</v>
       </c>
       <c r="AM45" t="s">
-        <v>688</v>
+        <v>686</v>
       </c>
       <c r="AN45" t="s">
-        <v>504</v>
+        <v>687</v>
       </c>
       <c r="AO45">
-        <v>0.99336120165168273</v>
+        <v>0.99652238714397645</v>
       </c>
       <c r="AP45">
-        <v>121.71130305248386</v>
+        <v>63.756235693765916</v>
       </c>
     </row>
     <row r="46" spans="2:56">
@@ -12993,16 +12993,16 @@
         <v>430</v>
       </c>
       <c r="Y46" t="s">
-        <v>334</v>
+        <v>342</v>
       </c>
       <c r="Z46" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="AA46">
-        <v>0.99687437062079542</v>
+        <v>0.99794405176225942</v>
       </c>
       <c r="AB46">
-        <v>57.30320528541781</v>
+        <v>37.692384358577527</v>
       </c>
       <c r="AD46" t="s">
         <v>357</v>
@@ -13029,16 +13029,16 @@
         <v>608</v>
       </c>
       <c r="AM46" t="s">
+        <v>688</v>
+      </c>
+      <c r="AN46" t="s">
         <v>689</v>
       </c>
-      <c r="AN46" t="s">
-        <v>512</v>
-      </c>
       <c r="AO46">
-        <v>0.99142662212165156</v>
+        <v>0.99644445157760886</v>
       </c>
       <c r="AP46">
-        <v>157.17859443638787</v>
+        <v>65.185054410503341</v>
       </c>
     </row>
     <row r="47" spans="2:56">
@@ -13103,16 +13103,16 @@
         <v>432</v>
       </c>
       <c r="Y47" t="s">
-        <v>344</v>
+        <v>306</v>
       </c>
       <c r="Z47" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="AA47">
-        <v>0.99634720436029245</v>
+        <v>0.98362146023706842</v>
       </c>
       <c r="AB47">
-        <v>66.967920061305705</v>
+        <v>300.27322898707882</v>
       </c>
       <c r="AD47" t="s">
         <v>357</v>
@@ -13145,10 +13145,10 @@
         <v>691</v>
       </c>
       <c r="AO47">
-        <v>0.99234453653341004</v>
+        <v>0.99593921525806983</v>
       </c>
       <c r="AP47">
-        <v>140.35016355414848</v>
+        <v>74.447720268718882</v>
       </c>
     </row>
     <row r="48" spans="2:56">
@@ -13213,16 +13213,16 @@
         <v>434</v>
       </c>
       <c r="Y48" t="s">
-        <v>324</v>
+        <v>309</v>
       </c>
       <c r="Z48" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="AA48">
-        <v>0.99690900069701904</v>
+        <v>0.99264013999643841</v>
       </c>
       <c r="AB48">
-        <v>56.668320554651658</v>
+        <v>134.93076673196322</v>
       </c>
       <c r="AD48" t="s">
         <v>357</v>
@@ -13255,10 +13255,10 @@
         <v>693</v>
       </c>
       <c r="AO48">
-        <v>0.99443256604953767</v>
+        <v>0.99516270130765094</v>
       </c>
       <c r="AP48">
-        <v>102.0696224251428</v>
+        <v>88.68380935973272</v>
       </c>
     </row>
     <row r="49" spans="2:42">
@@ -13323,16 +13323,16 @@
         <v>436</v>
       </c>
       <c r="Y49" t="s">
-        <v>343</v>
+        <v>352</v>
       </c>
       <c r="Z49" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="AA49">
-        <v>0.98659243069702229</v>
+        <v>0.99665443666269515</v>
       </c>
       <c r="AB49">
-        <v>245.80543722125813</v>
+        <v>61.335327850588769</v>
       </c>
       <c r="AD49" t="s">
         <v>357</v>
@@ -13365,10 +13365,10 @@
         <v>695</v>
       </c>
       <c r="AO49">
-        <v>0.99636332294747387</v>
+        <v>0.99373433598681304</v>
       </c>
       <c r="AP49">
-        <v>66.672412629645152</v>
+        <v>114.8705069084281</v>
       </c>
     </row>
     <row r="50" spans="2:42">
@@ -13433,16 +13433,16 @@
         <v>438</v>
       </c>
       <c r="Y50" t="s">
-        <v>320</v>
+        <v>347</v>
       </c>
       <c r="Z50" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="AA50">
-        <v>0.9936042103238425</v>
+        <v>0.99724701964333673</v>
       </c>
       <c r="AB50">
-        <v>117.25614406288832</v>
+        <v>50.471306538827449</v>
       </c>
       <c r="AD50" t="s">
         <v>357</v>
@@ -13475,10 +13475,10 @@
         <v>697</v>
       </c>
       <c r="AO50">
-        <v>0.99611299874662873</v>
+        <v>0.99674459930858406</v>
       </c>
       <c r="AP50">
-        <v>71.261689645139711</v>
+        <v>59.682346009292083</v>
       </c>
     </row>
     <row r="51" spans="2:42">
@@ -13543,16 +13543,16 @@
         <v>440</v>
       </c>
       <c r="Y51" t="s">
-        <v>339</v>
+        <v>350</v>
       </c>
       <c r="Z51" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="AA51">
-        <v>0.98700404273476772</v>
+        <v>0.99698341997506779</v>
       </c>
       <c r="AB51">
-        <v>238.25921652925925</v>
+        <v>55.30396712375795</v>
       </c>
       <c r="AD51" t="s">
         <v>357</v>
@@ -13582,13 +13582,13 @@
         <v>698</v>
       </c>
       <c r="AN51" t="s">
-        <v>699</v>
+        <v>635</v>
       </c>
       <c r="AO51">
-        <v>0.99166730629437405</v>
+        <v>0.98296108964477757</v>
       </c>
       <c r="AP51">
-        <v>152.7660512698088</v>
+        <v>312.38002317907871</v>
       </c>
     </row>
     <row r="52" spans="2:42">
@@ -13653,16 +13653,16 @@
         <v>442</v>
       </c>
       <c r="Y52" t="s">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="Z52" t="s">
-        <v>498</v>
+        <v>520</v>
       </c>
       <c r="AA52">
-        <v>0.99211999835767339</v>
+        <v>0.98292551835825892</v>
       </c>
       <c r="AB52">
-        <v>144.46669677598709</v>
+        <v>313.03216343191991</v>
       </c>
       <c r="AD52" t="s">
         <v>357</v>
@@ -13689,16 +13689,16 @@
         <v>620</v>
       </c>
       <c r="AM52" t="s">
+        <v>699</v>
+      </c>
+      <c r="AN52" t="s">
         <v>700</v>
       </c>
-      <c r="AN52" t="s">
-        <v>528</v>
-      </c>
       <c r="AO52">
-        <v>0.99089429663374551</v>
+        <v>0.9963831774222891</v>
       </c>
       <c r="AP52">
-        <v>166.93789504799881</v>
+        <v>66.308413924699082</v>
       </c>
     </row>
     <row r="53" spans="2:42">
@@ -13763,16 +13763,16 @@
         <v>444</v>
       </c>
       <c r="Y53" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="Z53" t="s">
         <v>521</v>
       </c>
       <c r="AA53">
-        <v>0.98833460826933028</v>
+        <v>0.99614153666719696</v>
       </c>
       <c r="AB53">
-        <v>213.86551506227875</v>
+        <v>70.738494434723179</v>
       </c>
       <c r="AD53" t="s">
         <v>357</v>
@@ -13805,10 +13805,10 @@
         <v>702</v>
       </c>
       <c r="AO53">
-        <v>0.99724587877560378</v>
+        <v>0.99380770610317104</v>
       </c>
       <c r="AP53">
-        <v>50.492222447263664</v>
+        <v>113.52538810853157</v>
       </c>
     </row>
     <row r="54" spans="2:42">
@@ -13873,16 +13873,16 @@
         <v>446</v>
       </c>
       <c r="Y54" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="Z54" t="s">
         <v>522</v>
       </c>
       <c r="AA54">
-        <v>0.99382176509351161</v>
+        <v>0.98850654863880194</v>
       </c>
       <c r="AB54">
-        <v>113.26763995228751</v>
+        <v>210.71327495529766</v>
       </c>
       <c r="AD54" t="s">
         <v>357</v>
@@ -13915,10 +13915,10 @@
         <v>704</v>
       </c>
       <c r="AO54">
-        <v>0.99687395765771536</v>
+        <v>0.99679454360228514</v>
       </c>
       <c r="AP54">
-        <v>57.310776275218892</v>
+        <v>58.766700624772731</v>
       </c>
     </row>
     <row r="55" spans="2:42">
@@ -13983,16 +13983,16 @@
         <v>448</v>
       </c>
       <c r="Y55" t="s">
-        <v>317</v>
+        <v>353</v>
       </c>
       <c r="Z55" t="s">
         <v>523</v>
       </c>
       <c r="AA55">
-        <v>0.99664712909564768</v>
+        <v>0.99485294245609246</v>
       </c>
       <c r="AB55">
-        <v>61.46929991312588</v>
+        <v>94.362721638304791</v>
       </c>
     </row>
     <row r="56" spans="2:42">
@@ -14057,16 +14057,16 @@
         <v>450</v>
       </c>
       <c r="Y56" t="s">
-        <v>323</v>
+        <v>351</v>
       </c>
       <c r="Z56" t="s">
         <v>524</v>
       </c>
       <c r="AA56">
-        <v>0.99632613854098695</v>
+        <v>0.99404600424580258</v>
       </c>
       <c r="AB56">
-        <v>67.354126748571815</v>
+        <v>109.15658882695236</v>
       </c>
     </row>
     <row r="57" spans="2:42">
@@ -14131,16 +14131,16 @@
         <v>452</v>
       </c>
       <c r="Y57" t="s">
-        <v>340</v>
+        <v>325</v>
       </c>
       <c r="Z57" t="s">
         <v>525</v>
       </c>
       <c r="AA57">
-        <v>0.99498089833731562</v>
+        <v>0.99781526983247337</v>
       </c>
       <c r="AB57">
-        <v>92.016863815880541</v>
+        <v>40.053386404654447</v>
       </c>
     </row>
     <row r="58" spans="2:42">
@@ -14205,16 +14205,16 @@
         <v>454</v>
       </c>
       <c r="Y58" t="s">
-        <v>335</v>
+        <v>328</v>
       </c>
       <c r="Z58" t="s">
         <v>526</v>
       </c>
       <c r="AA58">
-        <v>0.99367247562142269</v>
+        <v>0.98875969313918877</v>
       </c>
       <c r="AB58">
-        <v>116.00461360725107</v>
+        <v>206.07229244820644</v>
       </c>
     </row>
     <row r="59" spans="2:42">
@@ -14279,16 +14279,16 @@
         <v>456</v>
       </c>
       <c r="Y59" t="s">
-        <v>329</v>
+        <v>349</v>
       </c>
       <c r="Z59" t="s">
         <v>527</v>
       </c>
       <c r="AA59">
-        <v>0.98962497706829622</v>
+        <v>0.9962831220986742</v>
       </c>
       <c r="AB59">
-        <v>190.20875374790245</v>
+        <v>68.14276152430682</v>
       </c>
     </row>
     <row r="60" spans="2:42">
@@ -14353,16 +14353,16 @@
         <v>458</v>
       </c>
       <c r="Y60" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="Z60" t="s">
         <v>528</v>
       </c>
       <c r="AA60">
-        <v>0.99148269770211572</v>
+        <v>0.98327228856468729</v>
       </c>
       <c r="AB60">
-        <v>156.15054212787871</v>
+        <v>306.67470964740028</v>
       </c>
     </row>
     <row r="61" spans="2:42">
@@ -14427,16 +14427,16 @@
         <v>460</v>
       </c>
       <c r="Y61" t="s">
-        <v>346</v>
+        <v>311</v>
       </c>
       <c r="Z61" t="s">
         <v>529</v>
       </c>
       <c r="AA61">
-        <v>0.9970215739199545</v>
+        <v>0.99608527259090462</v>
       </c>
       <c r="AB61">
-        <v>54.604478134167074</v>
+        <v>71.770002500082597</v>
       </c>
     </row>
     <row r="62" spans="2:42">
@@ -14501,16 +14501,16 @@
         <v>462</v>
       </c>
       <c r="Y62" t="s">
-        <v>330</v>
+        <v>322</v>
       </c>
       <c r="Z62" t="s">
         <v>530</v>
       </c>
       <c r="AA62">
-        <v>0.9963692742640502</v>
+        <v>0.99688420747686357</v>
       </c>
       <c r="AB62">
-        <v>66.563305159080301</v>
+        <v>57.122862924167315</v>
       </c>
     </row>
     <row r="63" spans="2:42">
@@ -14575,16 +14575,16 @@
         <v>464</v>
       </c>
       <c r="Y63" t="s">
-        <v>300</v>
+        <v>308</v>
       </c>
       <c r="Z63" t="s">
         <v>531</v>
       </c>
       <c r="AA63">
-        <v>0.98292551835825892</v>
+        <v>0.99468188905612376</v>
       </c>
       <c r="AB63">
-        <v>313.03216343191991</v>
+        <v>97.498700637730266</v>
       </c>
     </row>
     <row r="64" spans="2:42">
@@ -14649,16 +14649,16 @@
         <v>466</v>
       </c>
       <c r="Y64" t="s">
-        <v>305</v>
+        <v>326</v>
       </c>
       <c r="Z64" t="s">
         <v>532</v>
       </c>
       <c r="AA64">
-        <v>0.99614153666719696</v>
+        <v>0.99798506730783287</v>
       </c>
       <c r="AB64">
-        <v>70.738494434723179</v>
+        <v>36.940432689730294</v>
       </c>
     </row>
     <row r="65" spans="2:28">
@@ -14723,16 +14723,16 @@
         <v>468</v>
       </c>
       <c r="Y65" t="s">
-        <v>314</v>
+        <v>333</v>
       </c>
       <c r="Z65" t="s">
         <v>533</v>
       </c>
       <c r="AA65">
-        <v>0.98850654863880194</v>
+        <v>0.99710009105712261</v>
       </c>
       <c r="AB65">
-        <v>210.71327495529766</v>
+        <v>53.164997286085928</v>
       </c>
     </row>
     <row r="66" spans="2:28">
@@ -14797,16 +14797,16 @@
         <v>470</v>
       </c>
       <c r="Y66" t="s">
-        <v>353</v>
+        <v>334</v>
       </c>
       <c r="Z66" t="s">
         <v>534</v>
       </c>
       <c r="AA66">
-        <v>0.99485294245609246</v>
+        <v>0.99687437062079542</v>
       </c>
       <c r="AB66">
-        <v>94.362721638304791</v>
+        <v>57.30320528541781</v>
       </c>
     </row>
     <row r="67" spans="2:28">
@@ -14871,16 +14871,16 @@
         <v>472</v>
       </c>
       <c r="Y67" t="s">
-        <v>351</v>
+        <v>321</v>
       </c>
       <c r="Z67" t="s">
         <v>535</v>
       </c>
       <c r="AA67">
-        <v>0.99404600424580258</v>
+        <v>0.99474921825793183</v>
       </c>
       <c r="AB67">
-        <v>109.15658882695236</v>
+        <v>96.264331937916907</v>
       </c>
     </row>
     <row r="68" spans="2:28">
@@ -14945,16 +14945,16 @@
         <v>474</v>
       </c>
       <c r="Y68" t="s">
-        <v>325</v>
+        <v>348</v>
       </c>
       <c r="Z68" t="s">
         <v>536</v>
       </c>
       <c r="AA68">
-        <v>0.99781526983247337</v>
+        <v>0.99496672523274499</v>
       </c>
       <c r="AB68">
-        <v>40.053386404654447</v>
+        <v>92.276704066342106</v>
       </c>
     </row>
     <row r="69" spans="2:28">
@@ -15019,16 +15019,16 @@
         <v>476</v>
       </c>
       <c r="Y69" t="s">
-        <v>328</v>
+        <v>337</v>
       </c>
       <c r="Z69" t="s">
         <v>537</v>
       </c>
       <c r="AA69">
-        <v>0.98875969313918877</v>
+        <v>0.99600522283071102</v>
       </c>
       <c r="AB69">
-        <v>206.07229244820644</v>
+        <v>73.237581436964462</v>
       </c>
     </row>
   </sheetData>
@@ -15037,7 +15037,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D6600707-3CF4-4431-A3B4-EA31ECF6FB32}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{27F58468-D39C-41E2-915C-5D685B1ECEDE}">
   <dimension ref="B9:Z54"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -15149,7 +15149,7 @@
         <v>816</v>
       </c>
       <c r="K11" t="s">
-        <v>631</v>
+        <v>684</v>
       </c>
       <c r="L11">
         <v>2.8233593407936151</v>
@@ -15182,7 +15182,7 @@
         <v>904</v>
       </c>
       <c r="X11" t="s">
-        <v>780</v>
+        <v>772</v>
       </c>
       <c r="Y11">
         <v>3.4740000000000002</v>
@@ -15217,7 +15217,7 @@
         <v>818</v>
       </c>
       <c r="K12" t="s">
-        <v>649</v>
+        <v>636</v>
       </c>
       <c r="L12">
         <v>3.8142378644522381</v>
@@ -15250,7 +15250,7 @@
         <v>906</v>
       </c>
       <c r="X12" t="s">
-        <v>774</v>
+        <v>782</v>
       </c>
       <c r="Y12">
         <v>8.5649999999999995</v>
@@ -15285,7 +15285,7 @@
         <v>820</v>
       </c>
       <c r="K13" t="s">
-        <v>641</v>
+        <v>650</v>
       </c>
       <c r="L13">
         <v>9.4269786267192082</v>
@@ -15318,7 +15318,7 @@
         <v>908</v>
       </c>
       <c r="X13" t="s">
-        <v>775</v>
+        <v>783</v>
       </c>
       <c r="Y13">
         <v>1.0125</v>
@@ -15353,7 +15353,7 @@
         <v>822</v>
       </c>
       <c r="K14" t="s">
-        <v>688</v>
+        <v>682</v>
       </c>
       <c r="L14">
         <v>7.6140112878139474</v>
@@ -15386,7 +15386,7 @@
         <v>910</v>
       </c>
       <c r="X14" t="s">
-        <v>808</v>
+        <v>802</v>
       </c>
       <c r="Y14">
         <v>23.480250000000002</v>
@@ -15421,7 +15421,7 @@
         <v>824</v>
       </c>
       <c r="K15" t="s">
-        <v>664</v>
+        <v>644</v>
       </c>
       <c r="L15">
         <v>0.94579509370884995</v>
@@ -15454,7 +15454,7 @@
         <v>912</v>
       </c>
       <c r="X15" t="s">
-        <v>790</v>
+        <v>812</v>
       </c>
       <c r="Y15">
         <v>39.333750000000002</v>
@@ -15489,7 +15489,7 @@
         <v>826</v>
       </c>
       <c r="K16" t="s">
-        <v>642</v>
+        <v>651</v>
       </c>
       <c r="L16">
         <v>11.144960581876036</v>
@@ -15522,7 +15522,7 @@
         <v>914</v>
       </c>
       <c r="X16" t="s">
-        <v>769</v>
+        <v>801</v>
       </c>
       <c r="Y16">
         <v>38.395499999999998</v>
@@ -15557,7 +15557,7 @@
         <v>828</v>
       </c>
       <c r="K17" t="s">
-        <v>630</v>
+        <v>683</v>
       </c>
       <c r="L17">
         <v>33.533313348973216</v>
@@ -15590,7 +15590,7 @@
         <v>916</v>
       </c>
       <c r="X17" t="s">
-        <v>782</v>
+        <v>774</v>
       </c>
       <c r="Y17">
         <v>37.595999999999997</v>
@@ -15625,7 +15625,7 @@
         <v>830</v>
       </c>
       <c r="K18" t="s">
-        <v>690</v>
+        <v>655</v>
       </c>
       <c r="L18">
         <v>11.453245383033059</v>
@@ -15658,7 +15658,7 @@
         <v>918</v>
       </c>
       <c r="X18" t="s">
-        <v>781</v>
+        <v>773</v>
       </c>
       <c r="Y18">
         <v>14.10375</v>
@@ -15693,7 +15693,7 @@
         <v>832</v>
       </c>
       <c r="K19" t="s">
-        <v>636</v>
+        <v>674</v>
       </c>
       <c r="L19">
         <v>6.1833350114404624</v>
@@ -15726,7 +15726,7 @@
         <v>920</v>
       </c>
       <c r="X19" t="s">
-        <v>795</v>
+        <v>779</v>
       </c>
       <c r="Y19">
         <v>26.091750000000001</v>
@@ -15761,7 +15761,7 @@
         <v>834</v>
       </c>
       <c r="K20" t="s">
-        <v>656</v>
+        <v>701</v>
       </c>
       <c r="L20">
         <v>16.389672297202406</v>
@@ -15794,7 +15794,7 @@
         <v>922</v>
       </c>
       <c r="X20" t="s">
-        <v>794</v>
+        <v>778</v>
       </c>
       <c r="Y20">
         <v>12.781499999999999</v>
@@ -15829,7 +15829,7 @@
         <v>836</v>
       </c>
       <c r="K21" t="s">
-        <v>689</v>
+        <v>654</v>
       </c>
       <c r="L21">
         <v>20.286141920134732</v>
@@ -15897,7 +15897,7 @@
         <v>838</v>
       </c>
       <c r="K22" t="s">
-        <v>672</v>
+        <v>665</v>
       </c>
       <c r="L22">
         <v>32.012227177722089</v>
@@ -15930,7 +15930,7 @@
         <v>926</v>
       </c>
       <c r="X22" t="s">
-        <v>800</v>
+        <v>787</v>
       </c>
       <c r="Y22">
         <v>15.56025</v>
@@ -15965,7 +15965,7 @@
         <v>840</v>
       </c>
       <c r="K23" t="s">
-        <v>678</v>
+        <v>688</v>
       </c>
       <c r="L23">
         <v>7.7073299979921162</v>
@@ -15998,7 +15998,7 @@
         <v>928</v>
       </c>
       <c r="X23" t="s">
-        <v>813</v>
+        <v>809</v>
       </c>
       <c r="Y23">
         <v>19.391999999999999</v>
@@ -16033,7 +16033,7 @@
         <v>842</v>
       </c>
       <c r="K24" t="s">
-        <v>692</v>
+        <v>657</v>
       </c>
       <c r="L24">
         <v>10.94212775371234</v>
@@ -16066,7 +16066,7 @@
         <v>930</v>
       </c>
       <c r="X24" t="s">
-        <v>804</v>
+        <v>765</v>
       </c>
       <c r="Y24">
         <v>11.877750000000001</v>
@@ -16101,7 +16101,7 @@
         <v>844</v>
       </c>
       <c r="K25" t="s">
-        <v>698</v>
+        <v>630</v>
       </c>
       <c r="L25">
         <v>17.017572468804527</v>
@@ -16134,7 +16134,7 @@
         <v>932</v>
       </c>
       <c r="X25" t="s">
-        <v>772</v>
+        <v>769</v>
       </c>
       <c r="Y25">
         <v>58.667999999999999</v>
@@ -16169,7 +16169,7 @@
         <v>846</v>
       </c>
       <c r="K26" t="s">
-        <v>680</v>
+        <v>690</v>
       </c>
       <c r="L26">
         <v>10.044304280614389</v>
@@ -16202,7 +16202,7 @@
         <v>934</v>
       </c>
       <c r="X26" t="s">
-        <v>798</v>
+        <v>805</v>
       </c>
       <c r="Y26">
         <v>23.315249999999999</v>
@@ -16237,7 +16237,7 @@
         <v>848</v>
       </c>
       <c r="K27" t="s">
-        <v>658</v>
+        <v>703</v>
       </c>
       <c r="L27">
         <v>6.8208467347837738</v>
@@ -16270,7 +16270,7 @@
         <v>936</v>
       </c>
       <c r="X27" t="s">
-        <v>788</v>
+        <v>795</v>
       </c>
       <c r="Y27">
         <v>10.53525</v>
@@ -16305,7 +16305,7 @@
         <v>850</v>
       </c>
       <c r="K28" t="s">
-        <v>639</v>
+        <v>686</v>
       </c>
       <c r="L28">
         <v>21.882724350441411</v>
@@ -16338,7 +16338,7 @@
         <v>938</v>
       </c>
       <c r="X28" t="s">
-        <v>767</v>
+        <v>799</v>
       </c>
       <c r="Y28">
         <v>43.472250000000003</v>
@@ -16373,7 +16373,7 @@
         <v>852</v>
       </c>
       <c r="K29" t="s">
-        <v>643</v>
+        <v>652</v>
       </c>
       <c r="L29">
         <v>4.5283086408379516</v>
@@ -16406,7 +16406,7 @@
         <v>940</v>
       </c>
       <c r="X29" t="s">
-        <v>802</v>
+        <v>789</v>
       </c>
       <c r="Y29">
         <v>60.665999999999997</v>
@@ -16441,7 +16441,7 @@
         <v>854</v>
       </c>
       <c r="K30" t="s">
-        <v>651</v>
+        <v>638</v>
       </c>
       <c r="L30">
         <v>10.193964319177619</v>
@@ -16474,7 +16474,7 @@
         <v>942</v>
       </c>
       <c r="X30" t="s">
-        <v>778</v>
+        <v>791</v>
       </c>
       <c r="Y30">
         <v>38.461500000000001</v>
@@ -16509,7 +16509,7 @@
         <v>856</v>
       </c>
       <c r="K31" t="s">
-        <v>694</v>
+        <v>659</v>
       </c>
       <c r="L31">
         <v>4.0796933380077434</v>
@@ -16542,7 +16542,7 @@
         <v>944</v>
       </c>
       <c r="X31" t="s">
-        <v>796</v>
+        <v>780</v>
       </c>
       <c r="Y31">
         <v>29.377500000000001</v>
@@ -16577,7 +16577,7 @@
         <v>858</v>
       </c>
       <c r="K32" t="s">
-        <v>662</v>
+        <v>642</v>
       </c>
       <c r="L32">
         <v>12.26323880416394</v>
@@ -16610,7 +16610,7 @@
         <v>946</v>
       </c>
       <c r="X32" t="s">
-        <v>806</v>
+        <v>767</v>
       </c>
       <c r="Y32">
         <v>8.5395000000000003</v>
@@ -16645,7 +16645,7 @@
         <v>860</v>
       </c>
       <c r="K33" t="s">
-        <v>670</v>
+        <v>663</v>
       </c>
       <c r="L33">
         <v>0.6739114575585754</v>
@@ -16678,7 +16678,7 @@
         <v>948</v>
       </c>
       <c r="X33" t="s">
-        <v>809</v>
+        <v>803</v>
       </c>
       <c r="Y33">
         <v>22.296749999999999</v>
@@ -16713,7 +16713,7 @@
         <v>862</v>
       </c>
       <c r="K34" t="s">
-        <v>654</v>
+        <v>699</v>
       </c>
       <c r="L34">
         <v>9.9985592326291517</v>
@@ -16746,7 +16746,7 @@
         <v>950</v>
       </c>
       <c r="X34" t="s">
-        <v>811</v>
+        <v>807</v>
       </c>
       <c r="Y34">
         <v>0.45450000000000002</v>
@@ -16781,7 +16781,7 @@
         <v>864</v>
       </c>
       <c r="K35" t="s">
-        <v>700</v>
+        <v>677</v>
       </c>
       <c r="L35">
         <v>8.2027093455463351</v>
@@ -16814,7 +16814,7 @@
         <v>952</v>
       </c>
       <c r="X35" t="s">
-        <v>814</v>
+        <v>810</v>
       </c>
       <c r="Y35">
         <v>1.9215</v>
@@ -16849,7 +16849,7 @@
         <v>866</v>
       </c>
       <c r="K36" t="s">
-        <v>635</v>
+        <v>673</v>
       </c>
       <c r="L36">
         <v>14.077964934917114</v>
@@ -16882,7 +16882,7 @@
         <v>954</v>
       </c>
       <c r="X36" t="s">
-        <v>776</v>
+        <v>785</v>
       </c>
       <c r="Y36">
         <v>66.086250000000007</v>
@@ -16950,7 +16950,7 @@
         <v>956</v>
       </c>
       <c r="X37" t="s">
-        <v>786</v>
+        <v>793</v>
       </c>
       <c r="Y37">
         <v>17.88</v>
@@ -16985,7 +16985,7 @@
         <v>870</v>
       </c>
       <c r="K38" t="s">
-        <v>647</v>
+        <v>634</v>
       </c>
       <c r="L38">
         <v>5.7746901396817503</v>
@@ -17018,7 +17018,7 @@
         <v>958</v>
       </c>
       <c r="X38" t="s">
-        <v>792</v>
+        <v>814</v>
       </c>
       <c r="Y38">
         <v>15.9975</v>
@@ -17053,7 +17053,7 @@
         <v>872</v>
       </c>
       <c r="K39" t="s">
-        <v>660</v>
+        <v>640</v>
       </c>
       <c r="L39">
         <v>0.31034972419242446</v>
@@ -17086,7 +17086,7 @@
         <v>960</v>
       </c>
       <c r="X39" t="s">
-        <v>784</v>
+        <v>776</v>
       </c>
       <c r="Y39">
         <v>13.328250000000001</v>
@@ -17154,7 +17154,7 @@
         <v>962</v>
       </c>
       <c r="X40" t="s">
-        <v>765</v>
+        <v>797</v>
       </c>
       <c r="Y40">
         <v>20.887499999999999</v>
@@ -17189,7 +17189,7 @@
         <v>876</v>
       </c>
       <c r="K41" t="s">
-        <v>653</v>
+        <v>698</v>
       </c>
       <c r="L41">
         <v>12.07826101849572</v>
@@ -17224,7 +17224,7 @@
         <v>878</v>
       </c>
       <c r="K42" t="s">
-        <v>645</v>
+        <v>632</v>
       </c>
       <c r="L42">
         <v>1.2064770882628508</v>
@@ -17259,7 +17259,7 @@
         <v>880</v>
       </c>
       <c r="K43" t="s">
-        <v>633</v>
+        <v>671</v>
       </c>
       <c r="L43">
         <v>18.8349545412255</v>
@@ -17294,7 +17294,7 @@
         <v>882</v>
       </c>
       <c r="K44" t="s">
-        <v>682</v>
+        <v>692</v>
       </c>
       <c r="L44">
         <v>58.145469176630144</v>
@@ -17329,7 +17329,7 @@
         <v>884</v>
       </c>
       <c r="K45" t="s">
-        <v>666</v>
+        <v>646</v>
       </c>
       <c r="L45">
         <v>21.047598854439691</v>
@@ -17364,7 +17364,7 @@
         <v>886</v>
       </c>
       <c r="K46" t="s">
-        <v>674</v>
+        <v>667</v>
       </c>
       <c r="L46">
         <v>6.0945869574590601</v>
@@ -17399,7 +17399,7 @@
         <v>888</v>
       </c>
       <c r="K47" t="s">
-        <v>686</v>
+        <v>696</v>
       </c>
       <c r="L47">
         <v>0.52378718950160097</v>
@@ -17434,7 +17434,7 @@
         <v>890</v>
       </c>
       <c r="K48" t="s">
-        <v>676</v>
+        <v>669</v>
       </c>
       <c r="L48">
         <v>0.74417561246386832</v>
@@ -17469,7 +17469,7 @@
         <v>892</v>
       </c>
       <c r="K49" t="s">
-        <v>684</v>
+        <v>694</v>
       </c>
       <c r="L49">
         <v>1.2742474813759068</v>
@@ -17504,7 +17504,7 @@
         <v>894</v>
       </c>
       <c r="K50" t="s">
-        <v>703</v>
+        <v>680</v>
       </c>
       <c r="L50">
         <v>0.78634982125966435</v>
@@ -17539,7 +17539,7 @@
         <v>896</v>
       </c>
       <c r="K51" t="s">
-        <v>701</v>
+        <v>678</v>
       </c>
       <c r="L51">
         <v>2.1288097562409964</v>
@@ -17574,7 +17574,7 @@
         <v>898</v>
       </c>
       <c r="K52" t="s">
-        <v>637</v>
+        <v>675</v>
       </c>
       <c r="L52">
         <v>3.1509090152495176</v>
@@ -17609,7 +17609,7 @@
         <v>900</v>
       </c>
       <c r="K53" t="s">
-        <v>696</v>
+        <v>661</v>
       </c>
       <c r="L53">
         <v>1.0579993988849852</v>
@@ -17644,7 +17644,7 @@
         <v>902</v>
       </c>
       <c r="K54" t="s">
-        <v>668</v>
+        <v>648</v>
       </c>
       <c r="L54">
         <v>0.12383426416706249</v>
@@ -17659,7 +17659,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D6CCCE7C-00A8-46E2-BE8B-9E7AB42B53C9}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{30762AB5-3FB5-41C9-8E3B-6313BA37FB94}">
   <dimension ref="B9:P73"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>

--- a/VerveStacks_MEX_grids_kan/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
+++ b/VerveStacks_MEX_grids_kan/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_MEX_grids_kan\SubRES_Tmpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{0AE486B5-72C0-44EE-92A1-5F21FA8298F4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{5657CFA2-3FEA-4FCA-A6B4-1E4AF08EAE1E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="6" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1203,18 +1203,108 @@
     <t>pre</t>
   </si>
   <si>
+    <t>distr_solelc_spv_MEX_001</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 1</t>
+  </si>
+  <si>
+    <t>NRGI</t>
+  </si>
+  <si>
+    <t>daynite</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_MEX_011</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 11</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_MEX_019</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 19</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_MEX_021</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 21</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_MEX_027</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 27</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_MEX_044</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 44</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_MEX_039</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 39</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_MEX_033</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 33</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_MEX_004</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 4</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_MEX_009</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 9</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_MEX_018</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 18</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_MEX_057</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 57</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_MEX_055</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 55</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_MEX_029</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 29</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_MEX_032</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 32</t>
+  </si>
+  <si>
     <t>distr_solelc_spv_MEX_002</t>
   </si>
   <si>
     <t>connecting solar to buses in cluster 2</t>
   </si>
   <si>
-    <t>NRGI</t>
-  </si>
-  <si>
-    <t>daynite</t>
-  </si>
-  <si>
     <t>distr_solelc_spv_MEX_014</t>
   </si>
   <si>
@@ -1239,52 +1329,16 @@
     <t>connecting solar to buses in cluster 40</t>
   </si>
   <si>
-    <t>distr_solelc_spv_MEX_001</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 1</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_MEX_011</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 11</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_MEX_019</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 19</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_MEX_021</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 21</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_MEX_027</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 27</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_MEX_044</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 44</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_MEX_039</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 39</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_MEX_033</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 33</t>
+    <t>distr_solelc_spv_MEX_024</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 24</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_MEX_043</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 43</t>
   </si>
   <si>
     <t>distr_solelc_spv_MEX_008</t>
@@ -1305,16 +1359,70 @@
     <t>connecting solar to buses in cluster 34</t>
   </si>
   <si>
-    <t>distr_solelc_spv_MEX_024</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 24</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_MEX_043</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 43</t>
+    <t>distr_solelc_spv_MEX_023</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 23</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_MEX_059</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 59</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_MEX_025</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 25</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_MEX_052</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 52</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_MEX_041</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 41</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_MEX_007</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 7</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_MEX_015</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 15</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_MEX_026</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 26</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_MEX_005</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 5</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_MEX_020</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 20</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_MEX_046</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 46</t>
   </si>
   <si>
     <t>distr_solelc_spv_MEX_006</t>
@@ -1335,6 +1443,102 @@
     <t>connecting solar to buses in cluster 35</t>
   </si>
   <si>
+    <t>distr_solelc_spv_MEX_048</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 48</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_MEX_028</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 28</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_MEX_047</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 47</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_MEX_010</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 10</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_MEX_013</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 13</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_MEX_056</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 56</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_MEX_051</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 51</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_MEX_054</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 54</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_MEX_003</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 3</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_MEX_058</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 58</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_MEX_036</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 36</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_MEX_012</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 12</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_MEX_030</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 30</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_MEX_037</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 37</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_MEX_038</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 38</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_MEX_053</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 53</t>
+  </si>
+  <si>
     <t>distr_solelc_spv_MEX_016</t>
   </si>
   <si>
@@ -1359,210 +1563,6 @@
     <t>connecting solar to buses in cluster 42</t>
   </si>
   <si>
-    <t>distr_solelc_spv_MEX_003</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 3</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_MEX_058</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 58</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_MEX_036</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 36</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_MEX_023</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 23</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_MEX_059</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 59</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_MEX_048</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 48</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_MEX_028</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 28</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_MEX_047</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 47</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_MEX_005</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 5</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_MEX_020</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 20</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_MEX_046</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 46</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_MEX_010</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 10</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_MEX_013</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 13</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_MEX_056</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 56</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_MEX_051</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 51</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_MEX_054</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 54</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_MEX_004</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 4</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_MEX_009</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 9</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_MEX_018</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 18</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_MEX_057</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 57</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_MEX_055</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 55</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_MEX_029</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 29</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_MEX_032</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 32</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_MEX_053</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 53</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_MEX_007</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 7</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_MEX_015</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 15</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_MEX_026</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 26</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_MEX_012</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 12</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_MEX_030</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 30</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_MEX_037</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 37</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_MEX_038</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 38</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_MEX_025</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 25</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_MEX_052</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 52</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_MEX_041</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 41</t>
-  </si>
-  <si>
     <t>comm-in</t>
   </si>
   <si>
@@ -1572,6 +1572,48 @@
     <t>e_w1377035989-400_MEX,e_w1376647652-400_MEX</t>
   </si>
   <si>
+    <t>e_r16051214-400_MEX</t>
+  </si>
+  <si>
+    <t>e_w120340864-400_MEX,e_w323989601-400_MEX,e_w120212304-400_MEX,e_w1144358547-400_MEX</t>
+  </si>
+  <si>
+    <t>e_w1144358547-400_MEX,e_w120340864-400_MEX,e_w1144316290-400_MEX,e_w864230553-400_MEX,e_w328237829-400_MEX,e_w1144316288-400_MEX,e_MX12-400_MEX,e_w328234376-400_MEX</t>
+  </si>
+  <si>
+    <t>e_w335761046-400_MEX,e_w653400165-400_MEX,e_MX1-400_MEX,e_w329140644-400_MEX</t>
+  </si>
+  <si>
+    <t>e_MX62-400_MEX,e_w1185619636-400_MEX,e_w97343927-400_MEX,e_w113005835-400_MEX,e_w639158083-400_MEX,e_w112525248-400_MEX,e_w113005841-400_MEX,e_MX66-400_MEX</t>
+  </si>
+  <si>
+    <t>e_w317273421-400_MEX,e_w334603451-400_MEX,e_w187401888-400_MEX,e_MX60-400_MEX</t>
+  </si>
+  <si>
+    <t>e_MX49-400_MEX,e_MX43-400_MEX,e_w187401888-400_MEX,e_w370805988-400_MEX,e_MX36-400_MEX</t>
+  </si>
+  <si>
+    <t>e_w1119978083-400_MEX,e_w1376647652-400_MEX,e_w1013583868-400_MEX</t>
+  </si>
+  <si>
+    <t>e_w1013583868-400_MEX,e_w1119978083-400_MEX,e_w339029834-400_MEX</t>
+  </si>
+  <si>
+    <t>e_w1122458623-400_MEX,e_w908223181-400_MEX,e_w120340864-400_MEX,e_w147507817-400_MEX,e_w193411905-400_MEX</t>
+  </si>
+  <si>
+    <t>e_w326213920-400_MEX,e_w1144316288-400_MEX,e_w931567937-400_MEX,e_w1143875912-400_MEX</t>
+  </si>
+  <si>
+    <t>e_w377881663-400_MEX,e_w326213920-400_MEX,e_MX32-400_MEX,e_MX23-400_MEX,e_MX21-400_MEX,e_MX15-400_MEX,e_w381587927-400_MEX</t>
+  </si>
+  <si>
+    <t>e_w244648181-400_MEX,e_w223990371-400_MEX,e_w316976706-400_MEX,e_w223990372-400_MEX,e_w686189325-400_MEX,e_w153402633-400_MEX</t>
+  </si>
+  <si>
+    <t>e_MX36-400_MEX,e_MX33-400_MEX,e_w489433441-400_MEX,e_w764377660-400_MEX</t>
+  </si>
+  <si>
     <t>e_w324339640-400_MEX,e_MX13-400_MEX,e_w382170046-400_MEX,e_w323989601-400_MEX</t>
   </si>
   <si>
@@ -1584,25 +1626,10 @@
     <t>e_w334603451-400_MEX,e_MX68-400_MEX,e_w187401888-400_MEX</t>
   </si>
   <si>
-    <t>e_r16051214-400_MEX</t>
-  </si>
-  <si>
-    <t>e_w120340864-400_MEX,e_w323989601-400_MEX,e_w120212304-400_MEX,e_w1144358547-400_MEX</t>
-  </si>
-  <si>
-    <t>e_w1144358547-400_MEX,e_w120340864-400_MEX,e_w1144316290-400_MEX,e_w864230553-400_MEX,e_w328237829-400_MEX,e_w1144316288-400_MEX,e_MX12-400_MEX,e_w328234376-400_MEX</t>
-  </si>
-  <si>
-    <t>e_w335761046-400_MEX,e_w653400165-400_MEX,e_MX1-400_MEX,e_w329140644-400_MEX</t>
-  </si>
-  <si>
-    <t>e_MX62-400_MEX,e_w1185619636-400_MEX,e_w97343927-400_MEX,e_w113005835-400_MEX,e_w639158083-400_MEX,e_w112525248-400_MEX,e_w113005841-400_MEX,e_MX66-400_MEX</t>
-  </si>
-  <si>
-    <t>e_w317273421-400_MEX,e_w334603451-400_MEX,e_w187401888-400_MEX,e_MX60-400_MEX</t>
-  </si>
-  <si>
-    <t>e_MX49-400_MEX,e_MX43-400_MEX,e_w187401888-400_MEX,e_w370805988-400_MEX,e_MX36-400_MEX</t>
+    <t>e_w908223181-400_MEX,e_w193411905-400_MEX,e_w147507817-400_MEX</t>
+  </si>
+  <si>
+    <t>e_w381991692-400_MEX,e_MX62-400_MEX,e_w97343932-400_MEX,e_w316976706-400_MEX,e_w113005841-400_MEX,e_MX66-400_MEX</t>
   </si>
   <si>
     <t>e_w1376647652-400_MEX,e_w1013583868-400_MEX</t>
@@ -1614,10 +1641,37 @@
     <t>e_MX49-400_MEX,e_MX44-400_MEX,e_MX43-400_MEX,e_w370805988-400_MEX,e_MX41-400_MEX</t>
   </si>
   <si>
-    <t>e_w908223181-400_MEX,e_w193411905-400_MEX,e_w147507817-400_MEX</t>
-  </si>
-  <si>
-    <t>e_w381991692-400_MEX,e_MX62-400_MEX,e_w97343932-400_MEX,e_w316976706-400_MEX,e_w113005841-400_MEX,e_MX66-400_MEX</t>
+    <t>e_w703468573-400_MEX,e_w193411905-400_MEX,e_w335761046-400_MEX</t>
+  </si>
+  <si>
+    <t>e_MX18-400_MEX,e_MX15-400_MEX,e_MX16-400_MEX,e_MX24-400_MEX,e_w325974178-400_MEX,e_MX30-400_MEX,e_MX22-400_MEX,e_w325906414-400_MEX,e_w113005842-400_MEX,e_w1181050521-400_MEX</t>
+  </si>
+  <si>
+    <t>e_w101027476-400_MEX,e_MX1-400_MEX</t>
+  </si>
+  <si>
+    <t>e_w1143989567-400_MEX,e_w931567937-400_MEX,e_w326794464-400_MEX,e_w1143989565-400_MEX,e_w785742675-400_MEX,e_w1137263496-400_MEX</t>
+  </si>
+  <si>
+    <t>e_MX67-400_MEX,e_w334603451-400_MEX,e_w390018954-400_MEX,e_w390018953-400_MEX</t>
+  </si>
+  <si>
+    <t>e_w1119978083-400_MEX,e_w324339641-400_MEX,e_w339029834-400_MEX</t>
+  </si>
+  <si>
+    <t>e_w1122458623-400_MEX,e_w1020167966-400_MEX,e_w119378437-400_MEX,e_w324339640-400_MEX</t>
+  </si>
+  <si>
+    <t>e_w329140644-400_MEX,e_w101027471-400_MEX,e_w100657593-400_MEX,e_w101027476-400_MEX</t>
+  </si>
+  <si>
+    <t>e_w339029834-400_MEX,e_w324339641-400_MEX,e_w1020167966-400_MEX</t>
+  </si>
+  <si>
+    <t>e_w120340864-400_MEX,e_w147507817-400_MEX,e_w703468574-400_MEX,e_w1144316290-400_MEX,e_w703468573-400_MEX,e_w328237829-400_MEX,e_w1135760619-400_MEX</t>
+  </si>
+  <si>
+    <t>e_w1347720126-400_MEX,e_MX56-400_MEX,e_w1063163195-400_MEX,e_w1182315273-400_MEX,e_w108298346-400_MEX,e_MX51-400_MEX,e_w97173246-400_MEX,e_w1182379765-400_MEX,e_w31875861-400_MEX</t>
   </si>
   <si>
     <t>e_w119378437-400_MEX,e_w324339641-400_MEX</t>
@@ -1629,6 +1683,54 @@
     <t>e_MX36-400_MEX,e_w489433441-400_MEX,e_w764377660-400_MEX</t>
   </si>
   <si>
+    <t>e_w320586165-400_MEX,e_w318811272-400_MEX,e_w322722579-400_MEX,e_w109684120-400_MEX,e_w1167512634-400_MEX,e_w318795296-400_MEX,e_MX64-400_MEX,e_MX63-400_MEX,e_w380654599-400_MEX,e_w187631617-400_MEX,e_MX38-400_MEX</t>
+  </si>
+  <si>
+    <t>e_w653400165-400_MEX,e_w335761046-400_MEX,e_w1135760619-400_MEX,e_w552409895-400_MEX,e_MX11-400_MEX,e_MX8-400_MEX,e_w124805240-400_MEX,e_w328371976-400_MEX,e_w1020056102-400_MEX,e_MX9-400_MEX</t>
+  </si>
+  <si>
+    <t>e_MX64-400_MEX,e_MX63-400_MEX,e_w380654599-400_MEX,e_w381991692-400_MEX,e_w108456470-400_MEX</t>
+  </si>
+  <si>
+    <t>e_w1013583868-400_MEX,e_w339029834-400_MEX,e_r16051214-400_MEX</t>
+  </si>
+  <si>
+    <t>e_r16051214-400_MEX,e_w908223181-400_MEX,e_w193411905-400_MEX</t>
+  </si>
+  <si>
+    <t>e_w864230553-400_MEX,e_w1211041028-400_MEX,e_w326213920-400_MEX,e_w120228114-400_MEX,e_MX34-400_MEX,e_w377881663-400_MEX</t>
+  </si>
+  <si>
+    <t>e_w327104799-400_MEX,e_w1128233586-400_MEX,e_w326794464-400_MEX,e_w1143875912-400_MEX,e_w1143875908-400_MEX</t>
+  </si>
+  <si>
+    <t>e_MX4-400_MEX,e_w1211132940-400_MEX,e_w100657593-400_MEX,e_w1137263496-400_MEX,e_w797709550-400_MEX</t>
+  </si>
+  <si>
+    <t>e_w1376647652-400_MEX,e_w1119978083-400_MEX,e_w1013583868-400_MEX</t>
+  </si>
+  <si>
+    <t>e_MX21-400_MEX,e_w325857132-400_MEX,e_MX46-400_MEX,e_MX31-400_MEX,e_MX42-400_MEX,e_w323682658-400_MEX,e_MX47-400_MEX,e_r16016425-400_MEX</t>
+  </si>
+  <si>
+    <t>e_w334603451-400_MEX,e_w156432250-400_MEX,e_w390018953-400_MEX</t>
+  </si>
+  <si>
+    <t>e_r16051214-400_MEX,e_w908223181-400_MEX</t>
+  </si>
+  <si>
+    <t>e_MX66-400_MEX,e_w316976706-400_MEX,e_w244648181-400_MEX,e_w1343929811-400_MEX,e_w223990371-400_MEX</t>
+  </si>
+  <si>
+    <t>e_w156432250-400_MEX,e_w153402633-400_MEX,e_w317273421-400_MEX,e_w390018954-400_MEX</t>
+  </si>
+  <si>
+    <t>e_w187401888-400_MEX,e_MX60-400_MEX,e_MX49-400_MEX</t>
+  </si>
+  <si>
+    <t>e_w1137263495-400_MEX,e_w328454682-400_MEX,e_w970712564-400_MEX</t>
+  </si>
+  <si>
     <t>e_w1020167966-400_MEX,e_w339029834-400_MEX,e_w908223181-400_MEX,e_w1122458623-400_MEX</t>
   </si>
   <si>
@@ -1641,106 +1743,58 @@
     <t>e_w316976706-400_MEX,e_w156432250-400_MEX,e_w153402633-400_MEX</t>
   </si>
   <si>
-    <t>e_w1376647652-400_MEX,e_w1119978083-400_MEX,e_w1013583868-400_MEX</t>
-  </si>
-  <si>
-    <t>e_MX21-400_MEX,e_w325857132-400_MEX,e_MX46-400_MEX,e_MX31-400_MEX,e_MX42-400_MEX,e_w323682658-400_MEX,e_MX47-400_MEX,e_r16016425-400_MEX</t>
-  </si>
-  <si>
-    <t>e_w334603451-400_MEX,e_w156432250-400_MEX,e_w390018953-400_MEX</t>
-  </si>
-  <si>
-    <t>e_w703468573-400_MEX,e_w193411905-400_MEX,e_w335761046-400_MEX</t>
-  </si>
-  <si>
-    <t>e_MX18-400_MEX,e_MX15-400_MEX,e_MX16-400_MEX,e_MX24-400_MEX,e_w325974178-400_MEX,e_MX30-400_MEX,e_MX22-400_MEX,e_w325906414-400_MEX,e_w113005842-400_MEX,e_w1181050521-400_MEX</t>
-  </si>
-  <si>
-    <t>e_w320586165-400_MEX,e_w318811272-400_MEX,e_w322722579-400_MEX,e_w109684120-400_MEX,e_w1167512634-400_MEX,e_w318795296-400_MEX,e_MX64-400_MEX,e_MX63-400_MEX,e_w380654599-400_MEX,e_w187631617-400_MEX,e_MX38-400_MEX</t>
-  </si>
-  <si>
-    <t>e_w653400165-400_MEX,e_w335761046-400_MEX,e_w1135760619-400_MEX,e_w552409895-400_MEX,e_MX11-400_MEX,e_MX8-400_MEX,e_w124805240-400_MEX,e_w328371976-400_MEX,e_w1020056102-400_MEX,e_MX9-400_MEX</t>
-  </si>
-  <si>
-    <t>e_MX64-400_MEX,e_MX63-400_MEX,e_w380654599-400_MEX,e_w381991692-400_MEX,e_w108456470-400_MEX</t>
-  </si>
-  <si>
-    <t>e_w339029834-400_MEX,e_w324339641-400_MEX,e_w1020167966-400_MEX</t>
-  </si>
-  <si>
-    <t>e_w120340864-400_MEX,e_w147507817-400_MEX,e_w703468574-400_MEX,e_w1144316290-400_MEX,e_w703468573-400_MEX,e_w328237829-400_MEX,e_w1135760619-400_MEX</t>
-  </si>
-  <si>
-    <t>e_w1347720126-400_MEX,e_MX56-400_MEX,e_w1063163195-400_MEX,e_w1182315273-400_MEX,e_w108298346-400_MEX,e_MX51-400_MEX,e_w97173246-400_MEX,e_w1182379765-400_MEX,e_w31875861-400_MEX</t>
-  </si>
-  <si>
-    <t>e_w1013583868-400_MEX,e_w339029834-400_MEX,e_r16051214-400_MEX</t>
-  </si>
-  <si>
-    <t>e_r16051214-400_MEX,e_w908223181-400_MEX,e_w193411905-400_MEX</t>
-  </si>
-  <si>
-    <t>e_w864230553-400_MEX,e_w1211041028-400_MEX,e_w326213920-400_MEX,e_w120228114-400_MEX,e_MX34-400_MEX,e_w377881663-400_MEX</t>
-  </si>
-  <si>
-    <t>e_w327104799-400_MEX,e_w1128233586-400_MEX,e_w326794464-400_MEX,e_w1143875912-400_MEX,e_w1143875908-400_MEX</t>
-  </si>
-  <si>
-    <t>e_MX4-400_MEX,e_w1211132940-400_MEX,e_w100657593-400_MEX,e_w1137263496-400_MEX,e_w797709550-400_MEX</t>
-  </si>
-  <si>
-    <t>e_w1119978083-400_MEX,e_w1376647652-400_MEX,e_w1013583868-400_MEX</t>
-  </si>
-  <si>
-    <t>e_w1013583868-400_MEX,e_w1119978083-400_MEX,e_w339029834-400_MEX</t>
-  </si>
-  <si>
-    <t>e_w1122458623-400_MEX,e_w908223181-400_MEX,e_w120340864-400_MEX,e_w147507817-400_MEX,e_w193411905-400_MEX</t>
-  </si>
-  <si>
-    <t>e_w326213920-400_MEX,e_w1144316288-400_MEX,e_w931567937-400_MEX,e_w1143875912-400_MEX</t>
-  </si>
-  <si>
-    <t>e_w377881663-400_MEX,e_w326213920-400_MEX,e_MX32-400_MEX,e_MX23-400_MEX,e_MX21-400_MEX,e_MX15-400_MEX,e_w381587927-400_MEX</t>
-  </si>
-  <si>
-    <t>e_w244648181-400_MEX,e_w223990371-400_MEX,e_w316976706-400_MEX,e_w223990372-400_MEX,e_w686189325-400_MEX,e_w153402633-400_MEX</t>
-  </si>
-  <si>
-    <t>e_MX36-400_MEX,e_MX33-400_MEX,e_w489433441-400_MEX,e_w764377660-400_MEX</t>
-  </si>
-  <si>
-    <t>e_w1137263495-400_MEX,e_w328454682-400_MEX,e_w970712564-400_MEX</t>
-  </si>
-  <si>
-    <t>e_w1119978083-400_MEX,e_w324339641-400_MEX,e_w339029834-400_MEX</t>
-  </si>
-  <si>
-    <t>e_w1122458623-400_MEX,e_w1020167966-400_MEX,e_w119378437-400_MEX,e_w324339640-400_MEX</t>
-  </si>
-  <si>
-    <t>e_w329140644-400_MEX,e_w101027471-400_MEX,e_w100657593-400_MEX,e_w101027476-400_MEX</t>
-  </si>
-  <si>
-    <t>e_r16051214-400_MEX,e_w908223181-400_MEX</t>
-  </si>
-  <si>
-    <t>e_MX66-400_MEX,e_w316976706-400_MEX,e_w244648181-400_MEX,e_w1343929811-400_MEX,e_w223990371-400_MEX</t>
-  </si>
-  <si>
-    <t>e_w156432250-400_MEX,e_w153402633-400_MEX,e_w317273421-400_MEX,e_w390018954-400_MEX</t>
-  </si>
-  <si>
-    <t>e_w187401888-400_MEX,e_MX60-400_MEX,e_MX49-400_MEX</t>
-  </si>
-  <si>
-    <t>e_w101027476-400_MEX,e_MX1-400_MEX</t>
-  </si>
-  <si>
-    <t>e_w1143989567-400_MEX,e_w931567937-400_MEX,e_w326794464-400_MEX,e_w1143989565-400_MEX,e_w785742675-400_MEX,e_w1137263496-400_MEX</t>
-  </si>
-  <si>
-    <t>e_MX67-400_MEX,e_w334603451-400_MEX,e_w390018954-400_MEX,e_w390018953-400_MEX</t>
+    <t>distr_wonelc_won_MEX_011</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 11</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_MEX_008</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 8</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_MEX_014</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 14</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_MEX_021</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 21</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_MEX_043</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 43</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_MEX_032</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 32</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_MEX_028</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 28</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_MEX_002</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 2</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_MEX_020</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 20</t>
   </si>
   <si>
     <t>distr_wonelc_won_MEX_027</t>
@@ -1755,64 +1809,154 @@
     <t>connecting wind onshore to buses in cluster 30</t>
   </si>
   <si>
+    <t>distr_wonelc_won_MEX_004</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 4</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_MEX_029</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 29</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_MEX_022</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 22</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_MEX_005</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 5</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_MEX_035</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 35</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_MEX_044</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 44</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_MEX_033</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 33</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_MEX_026</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 26</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_MEX_009</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 9</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_MEX_042</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 42</t>
+  </si>
+  <si>
     <t>distr_wonelc_won_MEX_015</t>
   </si>
   <si>
     <t>connecting wind onshore to buses in cluster 15</t>
   </si>
   <si>
-    <t>distr_wonelc_won_MEX_032</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 32</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_MEX_028</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 28</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_MEX_002</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 2</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_MEX_020</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 20</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_MEX_029</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 29</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_MEX_022</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 22</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_MEX_005</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 5</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_MEX_035</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 35</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_MEX_044</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 44</t>
+    <t>distr_wonelc_won_MEX_007</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 7</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_MEX_001</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 1</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_MEX_025</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 25</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_MEX_041</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 41</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_MEX_040</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 40</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_MEX_023</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 23</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_MEX_012</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 12</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_MEX_036</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 36</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_MEX_038</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 38</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_MEX_013</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 13</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_MEX_016</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 16</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_MEX_034</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 34</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_MEX_039</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 39</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_MEX_037</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 37</t>
   </si>
   <si>
     <t>distr_wonelc_won_MEX_003</t>
@@ -1833,156 +1977,12 @@
     <t>connecting wind onshore to buses in cluster 19</t>
   </si>
   <si>
-    <t>distr_wonelc_won_MEX_011</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 11</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_MEX_008</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 8</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_MEX_014</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 14</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_MEX_021</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 21</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_MEX_043</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 43</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_MEX_023</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 23</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_MEX_012</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 12</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_MEX_036</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 36</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_MEX_038</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 38</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_MEX_033</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 33</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_MEX_026</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 26</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_MEX_009</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 9</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_MEX_042</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 42</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_MEX_025</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 25</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_MEX_041</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 41</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_MEX_040</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 40</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_MEX_004</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 4</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_MEX_007</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 7</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_MEX_001</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 1</t>
-  </si>
-  <si>
     <t>distr_wonelc_won_MEX_018</t>
   </si>
   <si>
     <t>connecting wind onshore to buses in cluster 18</t>
   </si>
   <si>
-    <t>distr_wonelc_won_MEX_013</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 13</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_MEX_016</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 16</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_MEX_034</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 34</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_MEX_039</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 39</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_MEX_037</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 37</t>
-  </si>
-  <si>
     <t>distr_wonelc_won_MEX_031</t>
   </si>
   <si>
@@ -2007,6 +2007,57 @@
     <t>connecting wind onshore to buses in cluster 17</t>
   </si>
   <si>
+    <t>elc_won_MEX_011</t>
+  </si>
+  <si>
+    <t>elc_won_MEX_008</t>
+  </si>
+  <si>
+    <t>e_w908223181-400_MEX,e_w193411905-400_MEX</t>
+  </si>
+  <si>
+    <t>elc_won_MEX_014</t>
+  </si>
+  <si>
+    <t>e_w193411905-400_MEX,e_w147507817-400_MEX,e_w703468573-400_MEX</t>
+  </si>
+  <si>
+    <t>elc_won_MEX_021</t>
+  </si>
+  <si>
+    <t>e_w326213920-400_MEX,e_w377881663-400_MEX</t>
+  </si>
+  <si>
+    <t>elc_won_MEX_043</t>
+  </si>
+  <si>
+    <t>e_w1343929811-400_MEX,e_MX66-400_MEX,e_w223990371-400_MEX</t>
+  </si>
+  <si>
+    <t>elc_won_MEX_032</t>
+  </si>
+  <si>
+    <t>e_w1377035989-400_MEX</t>
+  </si>
+  <si>
+    <t>elc_won_MEX_028</t>
+  </si>
+  <si>
+    <t>e_w1119978083-400_MEX,e_w324339641-400_MEX,e_w339029834-400_MEX,e_w119378437-400_MEX</t>
+  </si>
+  <si>
+    <t>elc_won_MEX_002</t>
+  </si>
+  <si>
+    <t>e_w1122458623-400_MEX,e_w908223181-400_MEX,e_w120340864-400_MEX</t>
+  </si>
+  <si>
+    <t>elc_won_MEX_020</t>
+  </si>
+  <si>
+    <t>e_w703468573-400_MEX,e_w1135760619-400_MEX,e_w653400165-400_MEX,e_w552409895-400_MEX,e_MX8-400_MEX</t>
+  </si>
+  <si>
     <t>elc_won_MEX_027</t>
   </si>
   <si>
@@ -2019,64 +2070,139 @@
     <t>e_w1376647652-400_MEX,e_w1013583868-400_MEX,e_w1119978083-400_MEX</t>
   </si>
   <si>
+    <t>elc_won_MEX_004</t>
+  </si>
+  <si>
+    <t>elc_won_MEX_029</t>
+  </si>
+  <si>
+    <t>e_w1119978083-400_MEX,e_w339029834-400_MEX,e_w324339641-400_MEX,e_w1020167966-400_MEX</t>
+  </si>
+  <si>
+    <t>elc_won_MEX_022</t>
+  </si>
+  <si>
+    <t>e_w1376647652-400_MEX,e_w1013583868-400_MEX,e_r16051214-400_MEX</t>
+  </si>
+  <si>
+    <t>elc_won_MEX_005</t>
+  </si>
+  <si>
+    <t>e_w908223181-400_MEX,e_w1122458623-400_MEX</t>
+  </si>
+  <si>
+    <t>elc_won_MEX_035</t>
+  </si>
+  <si>
+    <t>e_w327104799-400_MEX,e_w1211132940-400_MEX,e_w326794464-400_MEX,e_w1143875908-400_MEX,e_w100657593-400_MEX,e_w1137263496-400_MEX,e_w797709550-400_MEX</t>
+  </si>
+  <si>
+    <t>elc_won_MEX_044</t>
+  </si>
+  <si>
+    <t>e_MX22-400_MEX,e_w325974178-400_MEX,e_w325906414-400_MEX,e_w113005842-400_MEX,e_MX47-400_MEX,e_r16016425-400_MEX</t>
+  </si>
+  <si>
+    <t>elc_won_MEX_033</t>
+  </si>
+  <si>
+    <t>e_w1376647652-400_MEX,e_w1377035989-400_MEX,e_w1119978083-400_MEX,e_w1013583868-400_MEX</t>
+  </si>
+  <si>
+    <t>elc_won_MEX_026</t>
+  </si>
+  <si>
+    <t>elc_won_MEX_009</t>
+  </si>
+  <si>
+    <t>elc_won_MEX_042</t>
+  </si>
+  <si>
+    <t>e_w316976706-400_MEX,e_w244648181-400_MEX,e_w223990371-400_MEX,e_w223990372-400_MEX,e_w686189325-400_MEX,e_w153402633-400_MEX</t>
+  </si>
+  <si>
     <t>elc_won_MEX_015</t>
   </si>
   <si>
     <t>e_w908223181-400_MEX,e_w147507817-400_MEX,e_w193411905-400_MEX,e_w120340864-400_MEX,e_w1144358547-400_MEX</t>
   </si>
   <si>
-    <t>elc_won_MEX_032</t>
-  </si>
-  <si>
-    <t>e_w1377035989-400_MEX</t>
-  </si>
-  <si>
-    <t>elc_won_MEX_028</t>
-  </si>
-  <si>
-    <t>e_w1119978083-400_MEX,e_w324339641-400_MEX,e_w339029834-400_MEX,e_w119378437-400_MEX</t>
-  </si>
-  <si>
-    <t>elc_won_MEX_002</t>
-  </si>
-  <si>
-    <t>e_w1122458623-400_MEX,e_w908223181-400_MEX,e_w120340864-400_MEX</t>
-  </si>
-  <si>
-    <t>elc_won_MEX_020</t>
-  </si>
-  <si>
-    <t>e_w703468573-400_MEX,e_w1135760619-400_MEX,e_w653400165-400_MEX,e_w552409895-400_MEX,e_MX8-400_MEX</t>
-  </si>
-  <si>
-    <t>elc_won_MEX_029</t>
-  </si>
-  <si>
-    <t>e_w1119978083-400_MEX,e_w339029834-400_MEX,e_w324339641-400_MEX,e_w1020167966-400_MEX</t>
-  </si>
-  <si>
-    <t>elc_won_MEX_022</t>
-  </si>
-  <si>
-    <t>e_w1376647652-400_MEX,e_w1013583868-400_MEX,e_r16051214-400_MEX</t>
-  </si>
-  <si>
-    <t>elc_won_MEX_005</t>
-  </si>
-  <si>
-    <t>e_w908223181-400_MEX,e_w1122458623-400_MEX</t>
-  </si>
-  <si>
-    <t>elc_won_MEX_035</t>
-  </si>
-  <si>
-    <t>e_w327104799-400_MEX,e_w1211132940-400_MEX,e_w326794464-400_MEX,e_w1143875908-400_MEX,e_w100657593-400_MEX,e_w1137263496-400_MEX,e_w797709550-400_MEX</t>
-  </si>
-  <si>
-    <t>elc_won_MEX_044</t>
-  </si>
-  <si>
-    <t>e_MX22-400_MEX,e_w325974178-400_MEX,e_w325906414-400_MEX,e_w113005842-400_MEX,e_MX47-400_MEX,e_r16016425-400_MEX</t>
+    <t>elc_won_MEX_007</t>
+  </si>
+  <si>
+    <t>elc_won_MEX_001</t>
+  </si>
+  <si>
+    <t>e_w120340864-400_MEX,e_w120212304-400_MEX,e_w1144358547-400_MEX</t>
+  </si>
+  <si>
+    <t>elc_won_MEX_025</t>
+  </si>
+  <si>
+    <t>elc_won_MEX_041</t>
+  </si>
+  <si>
+    <t>e_w97343932-400_MEX,e_MX62-400_MEX,e_w316976706-400_MEX,e_w156432250-400_MEX,e_w153402633-400_MEX,e_w334603451-400_MEX</t>
+  </si>
+  <si>
+    <t>elc_won_MEX_040</t>
+  </si>
+  <si>
+    <t>e_w223990372-400_MEX,e_w317273421-400_MEX</t>
+  </si>
+  <si>
+    <t>elc_won_MEX_023</t>
+  </si>
+  <si>
+    <t>e_w1013583868-400_MEX,e_w1119978083-400_MEX</t>
+  </si>
+  <si>
+    <t>elc_won_MEX_012</t>
+  </si>
+  <si>
+    <t>e_w193411905-400_MEX,e_w335761046-400_MEX,e_MX1-400_MEX</t>
+  </si>
+  <si>
+    <t>elc_won_MEX_036</t>
+  </si>
+  <si>
+    <t>e_w931567937-400_MEX,e_w1143989565-400_MEX,e_w785742675-400_MEX,e_w326794464-400_MEX,e_w1137263496-400_MEX,e_w1137263495-400_MEX,e_w328454682-400_MEX,e_w970712564-400_MEX</t>
+  </si>
+  <si>
+    <t>elc_won_MEX_038</t>
+  </si>
+  <si>
+    <t>e_MX41-400_MEX,e_w187401888-400_MEX,e_MX49-400_MEX,e_MX36-400_MEX,e_w489433441-400_MEX,e_MX33-400_MEX,e_w764377660-400_MEX</t>
+  </si>
+  <si>
+    <t>elc_won_MEX_013</t>
+  </si>
+  <si>
+    <t>e_w147507817-400_MEX,e_w703468574-400_MEX,e_w703468573-400_MEX</t>
+  </si>
+  <si>
+    <t>elc_won_MEX_016</t>
+  </si>
+  <si>
+    <t>e_w328237829-400_MEX,e_MX12-400_MEX,e_w328234376-400_MEX,e_w1135760619-400_MEX,e_w1144316288-400_MEX,e_MX11-400_MEX</t>
+  </si>
+  <si>
+    <t>elc_won_MEX_034</t>
+  </si>
+  <si>
+    <t>e_MX1-400_MEX,e_w335761046-400_MEX,e_w101027476-400_MEX,e_w329140644-400_MEX,e_w101027471-400_MEX,e_MX4-400_MEX,e_w100657593-400_MEX</t>
+  </si>
+  <si>
+    <t>elc_won_MEX_039</t>
+  </si>
+  <si>
+    <t>e_w317273421-400_MEX,e_w187401888-400_MEX,e_MX60-400_MEX</t>
+  </si>
+  <si>
+    <t>elc_won_MEX_037</t>
+  </si>
+  <si>
+    <t>e_MX60-400_MEX,e_MX49-400_MEX,e_MX44-400_MEX,e_MX43-400_MEX,e_w370805988-400_MEX,e_MX41-400_MEX</t>
   </si>
   <si>
     <t>elc_won_MEX_003</t>
@@ -2091,138 +2217,12 @@
     <t>e_w302760278-400_MEX,e_w120197852-400_MEX,e_w1211041028-400_MEX,e_w120195768-400_MEX,e_w120212304-400_MEX,e_w1211031755-400_MEX,e_w120217741-400_MEX,e_w120228114-400_MEX,e_MX34-400_MEX,e_w377881663-400_MEX,e_w1347720126-400_MEX</t>
   </si>
   <si>
-    <t>elc_won_MEX_011</t>
-  </si>
-  <si>
-    <t>elc_won_MEX_008</t>
-  </si>
-  <si>
-    <t>e_w908223181-400_MEX,e_w193411905-400_MEX</t>
-  </si>
-  <si>
-    <t>elc_won_MEX_014</t>
-  </si>
-  <si>
-    <t>e_w193411905-400_MEX,e_w147507817-400_MEX,e_w703468573-400_MEX</t>
-  </si>
-  <si>
-    <t>elc_won_MEX_021</t>
-  </si>
-  <si>
-    <t>e_w326213920-400_MEX,e_w377881663-400_MEX</t>
-  </si>
-  <si>
-    <t>elc_won_MEX_043</t>
-  </si>
-  <si>
-    <t>e_w1343929811-400_MEX,e_MX66-400_MEX,e_w223990371-400_MEX</t>
-  </si>
-  <si>
-    <t>elc_won_MEX_023</t>
-  </si>
-  <si>
-    <t>e_w1013583868-400_MEX,e_w1119978083-400_MEX</t>
-  </si>
-  <si>
-    <t>elc_won_MEX_012</t>
-  </si>
-  <si>
-    <t>e_w193411905-400_MEX,e_w335761046-400_MEX,e_MX1-400_MEX</t>
-  </si>
-  <si>
-    <t>elc_won_MEX_036</t>
-  </si>
-  <si>
-    <t>e_w931567937-400_MEX,e_w1143989565-400_MEX,e_w785742675-400_MEX,e_w326794464-400_MEX,e_w1137263496-400_MEX,e_w1137263495-400_MEX,e_w328454682-400_MEX,e_w970712564-400_MEX</t>
-  </si>
-  <si>
-    <t>elc_won_MEX_038</t>
-  </si>
-  <si>
-    <t>e_MX41-400_MEX,e_w187401888-400_MEX,e_MX49-400_MEX,e_MX36-400_MEX,e_w489433441-400_MEX,e_MX33-400_MEX,e_w764377660-400_MEX</t>
-  </si>
-  <si>
-    <t>elc_won_MEX_033</t>
-  </si>
-  <si>
-    <t>e_w1376647652-400_MEX,e_w1377035989-400_MEX,e_w1119978083-400_MEX,e_w1013583868-400_MEX</t>
-  </si>
-  <si>
-    <t>elc_won_MEX_026</t>
-  </si>
-  <si>
-    <t>elc_won_MEX_009</t>
-  </si>
-  <si>
-    <t>elc_won_MEX_042</t>
-  </si>
-  <si>
-    <t>e_w316976706-400_MEX,e_w244648181-400_MEX,e_w223990371-400_MEX,e_w223990372-400_MEX,e_w686189325-400_MEX,e_w153402633-400_MEX</t>
-  </si>
-  <si>
-    <t>elc_won_MEX_025</t>
-  </si>
-  <si>
-    <t>elc_won_MEX_041</t>
-  </si>
-  <si>
-    <t>e_w97343932-400_MEX,e_MX62-400_MEX,e_w316976706-400_MEX,e_w156432250-400_MEX,e_w153402633-400_MEX,e_w334603451-400_MEX</t>
-  </si>
-  <si>
-    <t>elc_won_MEX_040</t>
-  </si>
-  <si>
-    <t>e_w223990372-400_MEX,e_w317273421-400_MEX</t>
-  </si>
-  <si>
-    <t>elc_won_MEX_004</t>
-  </si>
-  <si>
-    <t>elc_won_MEX_007</t>
-  </si>
-  <si>
-    <t>elc_won_MEX_001</t>
-  </si>
-  <si>
-    <t>e_w120340864-400_MEX,e_w120212304-400_MEX,e_w1144358547-400_MEX</t>
-  </si>
-  <si>
     <t>elc_won_MEX_018</t>
   </si>
   <si>
     <t>e_w1144316290-400_MEX,e_w703468573-400_MEX,e_w1144358547-400_MEX,e_w328237829-400_MEX,e_w864230553-400_MEX,e_w1144316288-400_MEX</t>
   </si>
   <si>
-    <t>elc_won_MEX_013</t>
-  </si>
-  <si>
-    <t>e_w147507817-400_MEX,e_w703468574-400_MEX,e_w703468573-400_MEX</t>
-  </si>
-  <si>
-    <t>elc_won_MEX_016</t>
-  </si>
-  <si>
-    <t>e_w328237829-400_MEX,e_MX12-400_MEX,e_w328234376-400_MEX,e_w1135760619-400_MEX,e_w1144316288-400_MEX,e_MX11-400_MEX</t>
-  </si>
-  <si>
-    <t>elc_won_MEX_034</t>
-  </si>
-  <si>
-    <t>e_MX1-400_MEX,e_w335761046-400_MEX,e_w101027476-400_MEX,e_w329140644-400_MEX,e_w101027471-400_MEX,e_MX4-400_MEX,e_w100657593-400_MEX</t>
-  </si>
-  <si>
-    <t>elc_won_MEX_039</t>
-  </si>
-  <si>
-    <t>e_w317273421-400_MEX,e_w187401888-400_MEX,e_MX60-400_MEX</t>
-  </si>
-  <si>
-    <t>elc_won_MEX_037</t>
-  </si>
-  <si>
-    <t>e_MX60-400_MEX,e_MX49-400_MEX,e_MX44-400_MEX,e_MX43-400_MEX,e_w370805988-400_MEX,e_MX41-400_MEX</t>
-  </si>
-  <si>
     <t>elc_won_MEX_031</t>
   </si>
   <si>
@@ -2244,6 +2244,162 @@
     <t>e_w1144358547-400_MEX,e_w120212304-400_MEX,e_MX17-400_MEX,e_w864230553-400_MEX,e_w1211041028-400_MEX,e_w326213920-400_MEX</t>
   </si>
   <si>
+    <t>distr_wofelc_wof_MEX_006</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 6</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_MEX_020</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 20</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_MEX_012</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 12</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_MEX_019</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 19</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_MEX_002</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 2</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_MEX_003</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 3</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_MEX_026</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 26</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_MEX_011</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 11</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_MEX_027</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 27</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_MEX_017</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 17</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_MEX_024</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 24</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_MEX_013</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 13</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_MEX_025</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 25</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_MEX_010</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 10</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_MEX_009</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 9</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_MEX_021</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 21</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_MEX_030</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 30</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_MEX_018</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 18</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_MEX_001</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 1</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_MEX_008</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 8</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_MEX_007</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 7</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_MEX_029</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 29</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_MEX_016</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 16</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_MEX_015</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 15</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_MEX_005</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 5</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_MEX_028</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 28</t>
+  </si>
+  <si>
     <t>distr_wofelc_wof_MEX_014</t>
   </si>
   <si>
@@ -2256,126 +2412,6 @@
     <t>connecting wind offshore to buses in cluster 22</t>
   </si>
   <si>
-    <t>distr_wofelc_wof_MEX_015</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 15</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_MEX_011</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 11</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_MEX_001</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 1</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_MEX_008</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 8</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_MEX_007</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 7</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_MEX_029</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 29</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_MEX_010</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 10</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_MEX_009</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 9</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_MEX_021</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 21</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_MEX_002</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 2</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_MEX_003</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 3</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_MEX_026</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 26</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_MEX_012</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 12</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_MEX_019</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 19</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_MEX_020</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 20</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_MEX_027</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 27</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_MEX_017</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 17</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_MEX_030</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 30</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_MEX_018</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 18</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_MEX_006</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 6</t>
-  </si>
-  <si>
     <t>distr_wofelc_wof_MEX_004</t>
   </si>
   <si>
@@ -2388,40 +2424,136 @@
     <t>connecting wind offshore to buses in cluster 23</t>
   </si>
   <si>
-    <t>distr_wofelc_wof_MEX_016</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 16</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_MEX_024</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 24</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_MEX_013</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 13</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_MEX_025</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 25</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_MEX_005</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 5</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_MEX_028</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 28</t>
+    <t>elc_wof_MEX_006</t>
+  </si>
+  <si>
+    <t>e_w1119978083-400_MEX</t>
+  </si>
+  <si>
+    <t>elc_wof_MEX_020</t>
+  </si>
+  <si>
+    <t>e_MX44-400_MEX,e_w370805988-400_MEX,e_MX40-400_MEX</t>
+  </si>
+  <si>
+    <t>elc_wof_MEX_012</t>
+  </si>
+  <si>
+    <t>e_w324339641-400_MEX,e_w339029834-400_MEX</t>
+  </si>
+  <si>
+    <t>elc_wof_MEX_019</t>
+  </si>
+  <si>
+    <t>e_MX40-400_MEX,e_MX36-400_MEX,e_w489433441-400_MEX,e_w764377660-400_MEX</t>
+  </si>
+  <si>
+    <t>elc_wof_MEX_002</t>
+  </si>
+  <si>
+    <t>elc_wof_MEX_003</t>
+  </si>
+  <si>
+    <t>elc_wof_MEX_026</t>
+  </si>
+  <si>
+    <t>e_w325906414-400_MEX,e_w1143989565-400_MEX,e_w970712564-400_MEX</t>
+  </si>
+  <si>
+    <t>elc_wof_MEX_011</t>
+  </si>
+  <si>
+    <t>elc_wof_MEX_027</t>
+  </si>
+  <si>
+    <t>e_w316976706-400_MEX</t>
+  </si>
+  <si>
+    <t>elc_wof_MEX_017</t>
+  </si>
+  <si>
+    <t>e_MX60-400_MEX,e_MX49-400_MEX,e_MX44-400_MEX</t>
+  </si>
+  <si>
+    <t>elc_wof_MEX_024</t>
+  </si>
+  <si>
+    <t>e_w324339640-400_MEX,e_w324339641-400_MEX</t>
+  </si>
+  <si>
+    <t>elc_wof_MEX_013</t>
+  </si>
+  <si>
+    <t>elc_wof_MEX_025</t>
+  </si>
+  <si>
+    <t>e_w1143989565-400_MEX,e_w326794464-400_MEX,e_w1137263495-400_MEX,e_w970712564-400_MEX</t>
+  </si>
+  <si>
+    <t>elc_wof_MEX_010</t>
+  </si>
+  <si>
+    <t>elc_wof_MEX_009</t>
+  </si>
+  <si>
+    <t>elc_wof_MEX_021</t>
+  </si>
+  <si>
+    <t>e_MX49-400_MEX,e_MX44-400_MEX</t>
+  </si>
+  <si>
+    <t>elc_wof_MEX_030</t>
+  </si>
+  <si>
+    <t>e_w223990371-400_MEX,e_w1181045739-400_MEX,e_w223990372-400_MEX</t>
+  </si>
+  <si>
+    <t>elc_wof_MEX_018</t>
+  </si>
+  <si>
+    <t>e_w1181045739-400_MEX,e_w317273421-400_MEX,e_MX60-400_MEX</t>
+  </si>
+  <si>
+    <t>elc_wof_MEX_001</t>
+  </si>
+  <si>
+    <t>elc_wof_MEX_008</t>
+  </si>
+  <si>
+    <t>elc_wof_MEX_007</t>
+  </si>
+  <si>
+    <t>e_w324339641-400_MEX,e_w1119978083-400_MEX</t>
+  </si>
+  <si>
+    <t>elc_wof_MEX_029</t>
+  </si>
+  <si>
+    <t>e_w1343929811-400_MEX,e_r16016425-400_MEX,e_w223990371-400_MEX</t>
+  </si>
+  <si>
+    <t>elc_wof_MEX_016</t>
+  </si>
+  <si>
+    <t>e_MX33-400_MEX,e_w764377660-400_MEX</t>
+  </si>
+  <si>
+    <t>elc_wof_MEX_015</t>
+  </si>
+  <si>
+    <t>e_w489433441-400_MEX,e_w764377660-400_MEX</t>
+  </si>
+  <si>
+    <t>elc_wof_MEX_005</t>
+  </si>
+  <si>
+    <t>e_w1376647652-400_MEX,e_w1119978083-400_MEX</t>
+  </si>
+  <si>
+    <t>elc_wof_MEX_028</t>
+  </si>
+  <si>
+    <t>e_w316976706-400_MEX,e_w390018953-400_MEX</t>
   </si>
   <si>
     <t>elc_wof_MEX_014</t>
@@ -2436,105 +2568,6 @@
     <t>e_r16016425-400_MEX,e_w113005842-400_MEX</t>
   </si>
   <si>
-    <t>elc_wof_MEX_015</t>
-  </si>
-  <si>
-    <t>e_w489433441-400_MEX,e_w764377660-400_MEX</t>
-  </si>
-  <si>
-    <t>elc_wof_MEX_011</t>
-  </si>
-  <si>
-    <t>elc_wof_MEX_001</t>
-  </si>
-  <si>
-    <t>elc_wof_MEX_008</t>
-  </si>
-  <si>
-    <t>elc_wof_MEX_007</t>
-  </si>
-  <si>
-    <t>e_w324339641-400_MEX,e_w1119978083-400_MEX</t>
-  </si>
-  <si>
-    <t>elc_wof_MEX_029</t>
-  </si>
-  <si>
-    <t>e_w1343929811-400_MEX,e_r16016425-400_MEX,e_w223990371-400_MEX</t>
-  </si>
-  <si>
-    <t>elc_wof_MEX_010</t>
-  </si>
-  <si>
-    <t>elc_wof_MEX_009</t>
-  </si>
-  <si>
-    <t>elc_wof_MEX_021</t>
-  </si>
-  <si>
-    <t>e_MX49-400_MEX,e_MX44-400_MEX</t>
-  </si>
-  <si>
-    <t>elc_wof_MEX_002</t>
-  </si>
-  <si>
-    <t>elc_wof_MEX_003</t>
-  </si>
-  <si>
-    <t>e_w1119978083-400_MEX</t>
-  </si>
-  <si>
-    <t>elc_wof_MEX_026</t>
-  </si>
-  <si>
-    <t>e_w325906414-400_MEX,e_w1143989565-400_MEX,e_w970712564-400_MEX</t>
-  </si>
-  <si>
-    <t>elc_wof_MEX_012</t>
-  </si>
-  <si>
-    <t>e_w324339641-400_MEX,e_w339029834-400_MEX</t>
-  </si>
-  <si>
-    <t>elc_wof_MEX_019</t>
-  </si>
-  <si>
-    <t>e_MX40-400_MEX,e_MX36-400_MEX,e_w489433441-400_MEX,e_w764377660-400_MEX</t>
-  </si>
-  <si>
-    <t>elc_wof_MEX_020</t>
-  </si>
-  <si>
-    <t>e_MX44-400_MEX,e_w370805988-400_MEX,e_MX40-400_MEX</t>
-  </si>
-  <si>
-    <t>elc_wof_MEX_027</t>
-  </si>
-  <si>
-    <t>e_w316976706-400_MEX</t>
-  </si>
-  <si>
-    <t>elc_wof_MEX_017</t>
-  </si>
-  <si>
-    <t>e_MX60-400_MEX,e_MX49-400_MEX,e_MX44-400_MEX</t>
-  </si>
-  <si>
-    <t>elc_wof_MEX_030</t>
-  </si>
-  <si>
-    <t>e_w223990371-400_MEX,e_w1181045739-400_MEX,e_w223990372-400_MEX</t>
-  </si>
-  <si>
-    <t>elc_wof_MEX_018</t>
-  </si>
-  <si>
-    <t>e_w1181045739-400_MEX,e_w317273421-400_MEX,e_MX60-400_MEX</t>
-  </si>
-  <si>
-    <t>elc_wof_MEX_006</t>
-  </si>
-  <si>
     <t>elc_wof_MEX_004</t>
   </si>
   <si>
@@ -2542,39 +2575,6 @@
   </si>
   <si>
     <t>e_w1181050521-400_MEX,e_w325974178-400_MEX,e_w325906414-400_MEX</t>
-  </si>
-  <si>
-    <t>elc_wof_MEX_016</t>
-  </si>
-  <si>
-    <t>e_MX33-400_MEX,e_w764377660-400_MEX</t>
-  </si>
-  <si>
-    <t>elc_wof_MEX_024</t>
-  </si>
-  <si>
-    <t>e_w324339640-400_MEX,e_w324339641-400_MEX</t>
-  </si>
-  <si>
-    <t>elc_wof_MEX_013</t>
-  </si>
-  <si>
-    <t>elc_wof_MEX_025</t>
-  </si>
-  <si>
-    <t>e_w1143989565-400_MEX,e_w326794464-400_MEX,e_w1137263495-400_MEX,e_w970712564-400_MEX</t>
-  </si>
-  <si>
-    <t>elc_wof_MEX_005</t>
-  </si>
-  <si>
-    <t>e_w1376647652-400_MEX,e_w1119978083-400_MEX</t>
-  </si>
-  <si>
-    <t>elc_wof_MEX_028</t>
-  </si>
-  <si>
-    <t>e_w316976706-400_MEX,e_w390018953-400_MEX</t>
   </si>
   <si>
     <t>e_won_MEX_001</t>
@@ -7825,7 +7825,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D4A4F6D2-385E-48A6-8D7F-3109C70AA56B}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{42B05BEF-8C75-4DEA-839A-2D3AD07A16AF}">
   <dimension ref="B9:BD69"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -8063,16 +8063,16 @@
         <v>358</v>
       </c>
       <c r="Y11" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="Z11" t="s">
         <v>480</v>
       </c>
       <c r="AA11">
-        <v>0.99052534478032794</v>
+        <v>0.99211999835767339</v>
       </c>
       <c r="AB11">
-        <v>173.702012360655</v>
+        <v>144.46669677598709</v>
       </c>
       <c r="AD11" t="s">
         <v>357</v>
@@ -8102,13 +8102,13 @@
         <v>626</v>
       </c>
       <c r="AN11" t="s">
-        <v>627</v>
+        <v>529</v>
       </c>
       <c r="AO11">
-        <v>0.98617803880332466</v>
+        <v>0.99142662212165156</v>
       </c>
       <c r="AP11">
-        <v>253.40262193904815</v>
+        <v>157.17859443638787</v>
       </c>
       <c r="AR11" t="s">
         <v>357</v>
@@ -8141,10 +8141,10 @@
         <v>766</v>
       </c>
       <c r="BC11">
-        <v>0.99267872653249711</v>
+        <v>0.97887093776827594</v>
       </c>
       <c r="BD11">
-        <v>134.22334690422022</v>
+        <v>387.36614091494118</v>
       </c>
     </row>
     <row r="12" spans="2:56">
@@ -8209,16 +8209,16 @@
         <v>362</v>
       </c>
       <c r="Y12" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
       <c r="Z12" t="s">
         <v>481</v>
       </c>
       <c r="AA12">
-        <v>0.99533851522026684</v>
+        <v>0.98833460826933028</v>
       </c>
       <c r="AB12">
-        <v>85.460554295108906</v>
+        <v>213.86551506227875</v>
       </c>
       <c r="AD12" t="s">
         <v>357</v>
@@ -8245,16 +8245,16 @@
         <v>540</v>
       </c>
       <c r="AM12" t="s">
+        <v>627</v>
+      </c>
+      <c r="AN12" t="s">
         <v>628</v>
       </c>
-      <c r="AN12" t="s">
-        <v>629</v>
-      </c>
       <c r="AO12">
-        <v>0.9886447874534503</v>
+        <v>0.99234453653341004</v>
       </c>
       <c r="AP12">
-        <v>208.17889668674354</v>
+        <v>140.35016355414848</v>
       </c>
       <c r="AR12" t="s">
         <v>357</v>
@@ -8287,10 +8287,10 @@
         <v>768</v>
       </c>
       <c r="BC12">
-        <v>0.99560935707608011</v>
+        <v>0.9832797879436902</v>
       </c>
       <c r="BD12">
-        <v>80.495120271864536</v>
+        <v>306.53722103234719</v>
       </c>
     </row>
     <row r="13" spans="2:56">
@@ -8355,16 +8355,16 @@
         <v>364</v>
       </c>
       <c r="Y13" t="s">
-        <v>318</v>
+        <v>315</v>
       </c>
       <c r="Z13" t="s">
         <v>482</v>
       </c>
       <c r="AA13">
-        <v>0.9910347770013892</v>
+        <v>0.99382176509351161</v>
       </c>
       <c r="AB13">
-        <v>164.36242164119781</v>
+        <v>113.26763995228751</v>
       </c>
       <c r="AD13" t="s">
         <v>357</v>
@@ -8391,16 +8391,16 @@
         <v>542</v>
       </c>
       <c r="AM13" t="s">
+        <v>629</v>
+      </c>
+      <c r="AN13" t="s">
         <v>630</v>
       </c>
-      <c r="AN13" t="s">
-        <v>631</v>
-      </c>
       <c r="AO13">
-        <v>0.99166730629437405</v>
+        <v>0.99443256604953767</v>
       </c>
       <c r="AP13">
-        <v>152.7660512698088</v>
+        <v>102.0696224251428</v>
       </c>
       <c r="AR13" t="s">
         <v>357</v>
@@ -8433,10 +8433,10 @@
         <v>770</v>
       </c>
       <c r="BC13">
-        <v>0.98810956277351192</v>
+        <v>0.99176274648027563</v>
       </c>
       <c r="BD13">
-        <v>217.99134915228177</v>
+        <v>151.01631452828045</v>
       </c>
     </row>
     <row r="14" spans="2:56">
@@ -8501,16 +8501,16 @@
         <v>366</v>
       </c>
       <c r="Y14" t="s">
-        <v>327</v>
+        <v>317</v>
       </c>
       <c r="Z14" t="s">
         <v>483</v>
       </c>
       <c r="AA14">
-        <v>0.9980184525690815</v>
+        <v>0.99664712909564768</v>
       </c>
       <c r="AB14">
-        <v>36.32836956683964</v>
+        <v>61.46929991312588</v>
       </c>
       <c r="AD14" t="s">
         <v>357</v>
@@ -8537,16 +8537,16 @@
         <v>544</v>
       </c>
       <c r="AM14" t="s">
+        <v>631</v>
+      </c>
+      <c r="AN14" t="s">
         <v>632</v>
       </c>
-      <c r="AN14" t="s">
-        <v>633</v>
-      </c>
       <c r="AO14">
-        <v>0.98392602134528517</v>
+        <v>0.99636332294747387</v>
       </c>
       <c r="AP14">
-        <v>294.6896086697721</v>
+        <v>66.672412629645152</v>
       </c>
       <c r="AR14" t="s">
         <v>357</v>
@@ -8576,13 +8576,13 @@
         <v>771</v>
       </c>
       <c r="BB14" t="s">
-        <v>700</v>
+        <v>772</v>
       </c>
       <c r="BC14">
-        <v>0.99293011592915836</v>
+        <v>0.9835548687728024</v>
       </c>
       <c r="BD14">
-        <v>129.61454129876253</v>
+        <v>301.49407249862264</v>
       </c>
     </row>
     <row r="15" spans="2:56">
@@ -8647,16 +8647,16 @@
         <v>368</v>
       </c>
       <c r="Y15" t="s">
-        <v>336</v>
+        <v>323</v>
       </c>
       <c r="Z15" t="s">
         <v>484</v>
       </c>
       <c r="AA15">
-        <v>0.98650642341957129</v>
+        <v>0.99632613854098695</v>
       </c>
       <c r="AB15">
-        <v>247.38223730786015</v>
+        <v>67.354126748571815</v>
       </c>
       <c r="AD15" t="s">
         <v>357</v>
@@ -8683,16 +8683,16 @@
         <v>546</v>
       </c>
       <c r="AM15" t="s">
+        <v>633</v>
+      </c>
+      <c r="AN15" t="s">
         <v>634</v>
       </c>
-      <c r="AN15" t="s">
-        <v>635</v>
-      </c>
       <c r="AO15">
-        <v>0.98720186362781304</v>
+        <v>0.99611299874662873</v>
       </c>
       <c r="AP15">
-        <v>234.63250015676121</v>
+        <v>71.261689645139711</v>
       </c>
       <c r="AR15" t="s">
         <v>357</v>
@@ -8719,16 +8719,16 @@
         <v>713</v>
       </c>
       <c r="BA15" t="s">
-        <v>772</v>
+        <v>773</v>
       </c>
       <c r="BB15" t="s">
-        <v>633</v>
+        <v>480</v>
       </c>
       <c r="BC15">
-        <v>0.97618766725836525</v>
+        <v>0.97966892426826813</v>
       </c>
       <c r="BD15">
-        <v>436.55943359663644</v>
+        <v>372.73638841508404</v>
       </c>
     </row>
     <row r="16" spans="2:56">
@@ -8793,16 +8793,16 @@
         <v>370</v>
       </c>
       <c r="Y16" t="s">
-        <v>297</v>
+        <v>340</v>
       </c>
       <c r="Z16" t="s">
-        <v>480</v>
+        <v>485</v>
       </c>
       <c r="AA16">
-        <v>0.99211999835767339</v>
+        <v>0.99498089833731562</v>
       </c>
       <c r="AB16">
-        <v>144.46669677598709</v>
+        <v>92.016863815880541</v>
       </c>
       <c r="AD16" t="s">
         <v>357</v>
@@ -8829,16 +8829,16 @@
         <v>548</v>
       </c>
       <c r="AM16" t="s">
+        <v>635</v>
+      </c>
+      <c r="AN16" t="s">
         <v>636</v>
       </c>
-      <c r="AN16" t="s">
-        <v>637</v>
-      </c>
       <c r="AO16">
-        <v>0.99050084265243499</v>
+        <v>0.98392602134528517</v>
       </c>
       <c r="AP16">
-        <v>174.15121803869192</v>
+        <v>294.6896086697721</v>
       </c>
       <c r="AR16" t="s">
         <v>357</v>
@@ -8865,16 +8865,16 @@
         <v>715</v>
       </c>
       <c r="BA16" t="s">
-        <v>773</v>
+        <v>774</v>
       </c>
       <c r="BB16" t="s">
-        <v>700</v>
+        <v>766</v>
       </c>
       <c r="BC16">
-        <v>0.9941550644110243</v>
+        <v>0.95949403051377602</v>
       </c>
       <c r="BD16">
-        <v>107.15715246455407</v>
+        <v>742.60944058077234</v>
       </c>
     </row>
     <row r="17" spans="2:56">
@@ -8939,16 +8939,16 @@
         <v>372</v>
       </c>
       <c r="Y17" t="s">
-        <v>307</v>
+        <v>335</v>
       </c>
       <c r="Z17" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="AA17">
-        <v>0.98833460826933028</v>
+        <v>0.99367247562142269</v>
       </c>
       <c r="AB17">
-        <v>213.86551506227875</v>
+        <v>116.00461360725107</v>
       </c>
       <c r="AD17" t="s">
         <v>357</v>
@@ -8975,16 +8975,16 @@
         <v>550</v>
       </c>
       <c r="AM17" t="s">
+        <v>637</v>
+      </c>
+      <c r="AN17" t="s">
         <v>638</v>
       </c>
-      <c r="AN17" t="s">
-        <v>639</v>
-      </c>
       <c r="AO17">
-        <v>0.9955321750792081</v>
+        <v>0.98720186362781304</v>
       </c>
       <c r="AP17">
-        <v>81.910123547850631</v>
+        <v>234.63250015676121</v>
       </c>
       <c r="AR17" t="s">
         <v>357</v>
@@ -9011,16 +9011,16 @@
         <v>717</v>
       </c>
       <c r="BA17" t="s">
-        <v>774</v>
+        <v>775</v>
       </c>
       <c r="BB17" t="s">
-        <v>775</v>
+        <v>776</v>
       </c>
       <c r="BC17">
-        <v>0.97713203835019113</v>
+        <v>0.99033461600205908</v>
       </c>
       <c r="BD17">
-        <v>419.24596357982909</v>
+        <v>177.19870662891677</v>
       </c>
     </row>
     <row r="18" spans="2:56">
@@ -9085,16 +9085,16 @@
         <v>374</v>
       </c>
       <c r="Y18" t="s">
-        <v>315</v>
+        <v>329</v>
       </c>
       <c r="Z18" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="AA18">
-        <v>0.99382176509351161</v>
+        <v>0.98962497706829622</v>
       </c>
       <c r="AB18">
-        <v>113.26763995228751</v>
+        <v>190.20875374790245</v>
       </c>
       <c r="AD18" t="s">
         <v>357</v>
@@ -9121,16 +9121,16 @@
         <v>552</v>
       </c>
       <c r="AM18" t="s">
+        <v>639</v>
+      </c>
+      <c r="AN18" t="s">
         <v>640</v>
       </c>
-      <c r="AN18" t="s">
-        <v>641</v>
-      </c>
       <c r="AO18">
-        <v>0.99727438786147571</v>
+        <v>0.99050084265243499</v>
       </c>
       <c r="AP18">
-        <v>49.969555872944532</v>
+        <v>174.15121803869192</v>
       </c>
       <c r="AR18" t="s">
         <v>357</v>
@@ -9157,16 +9157,16 @@
         <v>719</v>
       </c>
       <c r="BA18" t="s">
-        <v>776</v>
+        <v>777</v>
       </c>
       <c r="BB18" t="s">
-        <v>777</v>
+        <v>700</v>
       </c>
       <c r="BC18">
-        <v>0.99576968882554151</v>
+        <v>0.99293011592915836</v>
       </c>
       <c r="BD18">
-        <v>77.555704865071448</v>
+        <v>129.61454129876253</v>
       </c>
     </row>
     <row r="19" spans="2:56">
@@ -9231,16 +9231,16 @@
         <v>376</v>
       </c>
       <c r="Y19" t="s">
-        <v>317</v>
+        <v>300</v>
       </c>
       <c r="Z19" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="AA19">
-        <v>0.99664712909564768</v>
+        <v>0.98292551835825892</v>
       </c>
       <c r="AB19">
-        <v>61.46929991312588</v>
+        <v>313.03216343191991</v>
       </c>
       <c r="AD19" t="s">
         <v>357</v>
@@ -9267,16 +9267,16 @@
         <v>554</v>
       </c>
       <c r="AM19" t="s">
+        <v>641</v>
+      </c>
+      <c r="AN19" t="s">
         <v>642</v>
       </c>
-      <c r="AN19" t="s">
-        <v>643</v>
-      </c>
       <c r="AO19">
-        <v>0.98300207162986786</v>
+        <v>0.9955321750792081</v>
       </c>
       <c r="AP19">
-        <v>311.62868678575552</v>
+        <v>81.910123547850631</v>
       </c>
       <c r="AR19" t="s">
         <v>357</v>
@@ -9306,13 +9306,13 @@
         <v>778</v>
       </c>
       <c r="BB19" t="s">
-        <v>700</v>
+        <v>779</v>
       </c>
       <c r="BC19">
-        <v>0.98933592887453392</v>
+        <v>0.99342309909810012</v>
       </c>
       <c r="BD19">
-        <v>195.50797063354466</v>
+        <v>120.57651653483084</v>
       </c>
     </row>
     <row r="20" spans="2:56">
@@ -9377,16 +9377,16 @@
         <v>378</v>
       </c>
       <c r="Y20" t="s">
-        <v>323</v>
+        <v>305</v>
       </c>
       <c r="Z20" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="AA20">
-        <v>0.99632613854098695</v>
+        <v>0.99614153666719696</v>
       </c>
       <c r="AB20">
-        <v>67.354126748571815</v>
+        <v>70.738494434723179</v>
       </c>
       <c r="AD20" t="s">
         <v>357</v>
@@ -9413,16 +9413,16 @@
         <v>556</v>
       </c>
       <c r="AM20" t="s">
+        <v>643</v>
+      </c>
+      <c r="AN20" t="s">
         <v>644</v>
       </c>
-      <c r="AN20" t="s">
-        <v>645</v>
-      </c>
       <c r="AO20">
-        <v>0.99075985723145521</v>
+        <v>0.98617803880332466</v>
       </c>
       <c r="AP20">
-        <v>169.402617423321</v>
+        <v>253.40262193904815</v>
       </c>
       <c r="AR20" t="s">
         <v>357</v>
@@ -9449,16 +9449,16 @@
         <v>723</v>
       </c>
       <c r="BA20" t="s">
-        <v>779</v>
+        <v>780</v>
       </c>
       <c r="BB20" t="s">
-        <v>492</v>
+        <v>781</v>
       </c>
       <c r="BC20">
-        <v>0.98910793924841989</v>
+        <v>0.9895689701647985</v>
       </c>
       <c r="BD20">
-        <v>199.68778044563484</v>
+        <v>191.23554697869403</v>
       </c>
     </row>
     <row r="21" spans="2:56">
@@ -9523,16 +9523,16 @@
         <v>380</v>
       </c>
       <c r="Y21" t="s">
-        <v>340</v>
+        <v>314</v>
       </c>
       <c r="Z21" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="AA21">
-        <v>0.99498089833731562</v>
+        <v>0.98850654863880194</v>
       </c>
       <c r="AB21">
-        <v>92.016863815880541</v>
+        <v>210.71327495529766</v>
       </c>
       <c r="AD21" t="s">
         <v>357</v>
@@ -9559,16 +9559,16 @@
         <v>558</v>
       </c>
       <c r="AM21" t="s">
+        <v>645</v>
+      </c>
+      <c r="AN21" t="s">
         <v>646</v>
       </c>
-      <c r="AN21" t="s">
-        <v>647</v>
-      </c>
       <c r="AO21">
-        <v>0.99719980724440771</v>
+        <v>0.9886447874534503</v>
       </c>
       <c r="AP21">
-        <v>51.336867185859347</v>
+        <v>208.17889668674354</v>
       </c>
       <c r="AR21" t="s">
         <v>357</v>
@@ -9595,16 +9595,16 @@
         <v>725</v>
       </c>
       <c r="BA21" t="s">
-        <v>780</v>
+        <v>782</v>
       </c>
       <c r="BB21" t="s">
-        <v>781</v>
+        <v>783</v>
       </c>
       <c r="BC21">
-        <v>0.98350082174829745</v>
+        <v>0.93550473459950212</v>
       </c>
       <c r="BD21">
-        <v>302.48493461454615</v>
+        <v>1182.4131990091278</v>
       </c>
     </row>
     <row r="22" spans="2:56">
@@ -9669,16 +9669,16 @@
         <v>382</v>
       </c>
       <c r="Y22" t="s">
-        <v>335</v>
+        <v>353</v>
       </c>
       <c r="Z22" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="AA22">
-        <v>0.99367247562142269</v>
+        <v>0.99485294245609246</v>
       </c>
       <c r="AB22">
-        <v>116.00461360725107</v>
+        <v>94.362721638304791</v>
       </c>
       <c r="AD22" t="s">
         <v>357</v>
@@ -9705,16 +9705,16 @@
         <v>560</v>
       </c>
       <c r="AM22" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="AN22" t="s">
-        <v>649</v>
+        <v>535</v>
       </c>
       <c r="AO22">
-        <v>0.99712587624395799</v>
+        <v>0.99336120165168273</v>
       </c>
       <c r="AP22">
-        <v>52.69226886077093</v>
+        <v>121.71130305248386</v>
       </c>
       <c r="AR22" t="s">
         <v>357</v>
@@ -9741,16 +9741,16 @@
         <v>727</v>
       </c>
       <c r="BA22" t="s">
-        <v>782</v>
+        <v>784</v>
       </c>
       <c r="BB22" t="s">
-        <v>480</v>
+        <v>675</v>
       </c>
       <c r="BC22">
-        <v>0.97966892426826813</v>
+        <v>0.99006235484112581</v>
       </c>
       <c r="BD22">
-        <v>372.73638841508404</v>
+        <v>182.19016124602703</v>
       </c>
     </row>
     <row r="23" spans="2:56">
@@ -9815,16 +9815,16 @@
         <v>384</v>
       </c>
       <c r="Y23" t="s">
-        <v>329</v>
+        <v>351</v>
       </c>
       <c r="Z23" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="AA23">
-        <v>0.98962497706829622</v>
+        <v>0.99404600424580258</v>
       </c>
       <c r="AB23">
-        <v>190.20875374790245</v>
+        <v>109.15658882695236</v>
       </c>
       <c r="AD23" t="s">
         <v>357</v>
@@ -9851,16 +9851,16 @@
         <v>562</v>
       </c>
       <c r="AM23" t="s">
-        <v>650</v>
+        <v>648</v>
       </c>
       <c r="AN23" t="s">
-        <v>531</v>
+        <v>649</v>
       </c>
       <c r="AO23">
-        <v>0.99159807557278401</v>
+        <v>0.99727438786147571</v>
       </c>
       <c r="AP23">
-        <v>154.03528116562623</v>
+        <v>49.969555872944532</v>
       </c>
       <c r="AR23" t="s">
         <v>357</v>
@@ -9887,16 +9887,16 @@
         <v>729</v>
       </c>
       <c r="BA23" t="s">
-        <v>783</v>
+        <v>785</v>
       </c>
       <c r="BB23" t="s">
-        <v>784</v>
+        <v>786</v>
       </c>
       <c r="BC23">
-        <v>0.95949403051377602</v>
+        <v>0.99266053819235223</v>
       </c>
       <c r="BD23">
-        <v>742.60944058077234</v>
+        <v>134.55679980687663</v>
       </c>
     </row>
     <row r="24" spans="2:56">
@@ -9961,16 +9961,16 @@
         <v>386</v>
       </c>
       <c r="Y24" t="s">
-        <v>304</v>
+        <v>325</v>
       </c>
       <c r="Z24" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="AA24">
-        <v>0.99148269770211572</v>
+        <v>0.99781526983247337</v>
       </c>
       <c r="AB24">
-        <v>156.15054212787871</v>
+        <v>40.053386404654447</v>
       </c>
       <c r="AD24" t="s">
         <v>357</v>
@@ -9997,16 +9997,16 @@
         <v>564</v>
       </c>
       <c r="AM24" t="s">
+        <v>650</v>
+      </c>
+      <c r="AN24" t="s">
         <v>651</v>
       </c>
-      <c r="AN24" t="s">
-        <v>485</v>
-      </c>
       <c r="AO24">
-        <v>0.98819864394083989</v>
+        <v>0.98300207162986786</v>
       </c>
       <c r="AP24">
-        <v>216.35819441793581</v>
+        <v>311.62868678575552</v>
       </c>
       <c r="AR24" t="s">
         <v>357</v>
@@ -10033,16 +10033,16 @@
         <v>731</v>
       </c>
       <c r="BA24" t="s">
-        <v>785</v>
+        <v>787</v>
       </c>
       <c r="BB24" t="s">
-        <v>786</v>
+        <v>700</v>
       </c>
       <c r="BC24">
-        <v>0.99033461600205908</v>
+        <v>0.98933592887453392</v>
       </c>
       <c r="BD24">
-        <v>177.19870662891677</v>
+        <v>195.50797063354466</v>
       </c>
     </row>
     <row r="25" spans="2:56">
@@ -10107,16 +10107,16 @@
         <v>388</v>
       </c>
       <c r="Y25" t="s">
-        <v>346</v>
+        <v>328</v>
       </c>
       <c r="Z25" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="AA25">
-        <v>0.9970215739199545</v>
+        <v>0.98875969313918877</v>
       </c>
       <c r="AB25">
-        <v>54.604478134167074</v>
+        <v>206.07229244820644</v>
       </c>
       <c r="AD25" t="s">
         <v>357</v>
@@ -10149,10 +10149,10 @@
         <v>653</v>
       </c>
       <c r="AO25">
-        <v>0.99783515171992265</v>
+        <v>0.99075985723145521</v>
       </c>
       <c r="AP25">
-        <v>39.688885134750748</v>
+        <v>169.402617423321</v>
       </c>
       <c r="AR25" t="s">
         <v>357</v>
@@ -10179,16 +10179,16 @@
         <v>733</v>
       </c>
       <c r="BA25" t="s">
-        <v>787</v>
+        <v>788</v>
       </c>
       <c r="BB25" t="s">
-        <v>788</v>
+        <v>501</v>
       </c>
       <c r="BC25">
-        <v>0.99176274648027563</v>
+        <v>0.98910793924841989</v>
       </c>
       <c r="BD25">
-        <v>151.01631452828045</v>
+        <v>199.68778044563484</v>
       </c>
     </row>
     <row r="26" spans="2:56">
@@ -10253,16 +10253,16 @@
         <v>390</v>
       </c>
       <c r="Y26" t="s">
-        <v>330</v>
+        <v>298</v>
       </c>
       <c r="Z26" t="s">
-        <v>494</v>
+        <v>480</v>
       </c>
       <c r="AA26">
-        <v>0.9963692742640502</v>
+        <v>0.99052534478032794</v>
       </c>
       <c r="AB26">
-        <v>66.563305159080301</v>
+        <v>173.702012360655</v>
       </c>
       <c r="AD26" t="s">
         <v>357</v>
@@ -10292,13 +10292,13 @@
         <v>654</v>
       </c>
       <c r="AN26" t="s">
-        <v>531</v>
+        <v>655</v>
       </c>
       <c r="AO26">
-        <v>0.99142662212165156</v>
+        <v>0.99719980724440771</v>
       </c>
       <c r="AP26">
-        <v>157.17859443638787</v>
+        <v>51.336867185859347</v>
       </c>
       <c r="AR26" t="s">
         <v>357</v>
@@ -10331,10 +10331,10 @@
         <v>790</v>
       </c>
       <c r="BC26">
-        <v>0.9835548687728024</v>
+        <v>0.98350082174829745</v>
       </c>
       <c r="BD26">
-        <v>301.49407249862264</v>
+        <v>302.48493461454615</v>
       </c>
     </row>
     <row r="27" spans="2:56">
@@ -10399,16 +10399,16 @@
         <v>392</v>
       </c>
       <c r="Y27" t="s">
-        <v>320</v>
+        <v>310</v>
       </c>
       <c r="Z27" t="s">
         <v>495</v>
       </c>
       <c r="AA27">
-        <v>0.9936042103238425</v>
+        <v>0.99533851522026684</v>
       </c>
       <c r="AB27">
-        <v>117.25614406288832</v>
+        <v>85.460554295108906</v>
       </c>
       <c r="AD27" t="s">
         <v>357</v>
@@ -10435,16 +10435,16 @@
         <v>570</v>
       </c>
       <c r="AM27" t="s">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="AN27" t="s">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="AO27">
-        <v>0.99234453653341004</v>
+        <v>0.99712587624395799</v>
       </c>
       <c r="AP27">
-        <v>140.35016355414848</v>
+        <v>52.69226886077093</v>
       </c>
       <c r="AR27" t="s">
         <v>357</v>
@@ -10477,10 +10477,10 @@
         <v>792</v>
       </c>
       <c r="BC27">
-        <v>0.9832797879436902</v>
+        <v>0.9941574321229002</v>
       </c>
       <c r="BD27">
-        <v>306.53722103234719</v>
+        <v>107.1137444134967</v>
       </c>
     </row>
     <row r="28" spans="2:56">
@@ -10545,16 +10545,16 @@
         <v>394</v>
       </c>
       <c r="Y28" t="s">
-        <v>339</v>
+        <v>318</v>
       </c>
       <c r="Z28" t="s">
         <v>496</v>
       </c>
       <c r="AA28">
-        <v>0.98700404273476772</v>
+        <v>0.9910347770013892</v>
       </c>
       <c r="AB28">
-        <v>238.25921652925925</v>
+        <v>164.36242164119781</v>
       </c>
       <c r="AD28" t="s">
         <v>357</v>
@@ -10581,16 +10581,16 @@
         <v>572</v>
       </c>
       <c r="AM28" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="AN28" t="s">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="AO28">
-        <v>0.99443256604953767</v>
+        <v>0.98007271259494255</v>
       </c>
       <c r="AP28">
-        <v>102.0696224251428</v>
+        <v>365.33360242605363</v>
       </c>
       <c r="AR28" t="s">
         <v>357</v>
@@ -10623,10 +10623,10 @@
         <v>794</v>
       </c>
       <c r="BC28">
-        <v>0.99342309909810012</v>
+        <v>0.98902827014922345</v>
       </c>
       <c r="BD28">
-        <v>120.57651653483084</v>
+        <v>201.14838059757037</v>
       </c>
     </row>
     <row r="29" spans="2:56">
@@ -10691,16 +10691,16 @@
         <v>396</v>
       </c>
       <c r="Y29" t="s">
-        <v>302</v>
+        <v>327</v>
       </c>
       <c r="Z29" t="s">
         <v>497</v>
       </c>
       <c r="AA29">
-        <v>0.98305355992983057</v>
+        <v>0.9980184525690815</v>
       </c>
       <c r="AB29">
-        <v>310.68473461977231</v>
+        <v>36.32836956683964</v>
       </c>
       <c r="AD29" t="s">
         <v>357</v>
@@ -10727,16 +10727,16 @@
         <v>574</v>
       </c>
       <c r="AM29" t="s">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="AN29" t="s">
-        <v>660</v>
+        <v>480</v>
       </c>
       <c r="AO29">
-        <v>0.99636332294747387</v>
+        <v>0.99276484208013105</v>
       </c>
       <c r="AP29">
-        <v>66.672412629645152</v>
+        <v>132.64456186426332</v>
       </c>
       <c r="AR29" t="s">
         <v>357</v>
@@ -10766,13 +10766,13 @@
         <v>795</v>
       </c>
       <c r="BB29" t="s">
-        <v>796</v>
+        <v>636</v>
       </c>
       <c r="BC29">
-        <v>0.9895689701647985</v>
+        <v>0.97618766725836525</v>
       </c>
       <c r="BD29">
-        <v>191.23554697869403</v>
+        <v>436.55943359663644</v>
       </c>
     </row>
     <row r="30" spans="2:56">
@@ -10837,16 +10837,16 @@
         <v>398</v>
       </c>
       <c r="Y30" t="s">
-        <v>341</v>
+        <v>336</v>
       </c>
       <c r="Z30" t="s">
         <v>498</v>
       </c>
       <c r="AA30">
-        <v>0.99526736010661099</v>
+        <v>0.98650642341957129</v>
       </c>
       <c r="AB30">
-        <v>86.765064712131235</v>
+        <v>247.38223730786015</v>
       </c>
       <c r="AD30" t="s">
         <v>357</v>
@@ -10876,13 +10876,13 @@
         <v>661</v>
       </c>
       <c r="AN30" t="s">
-        <v>662</v>
+        <v>535</v>
       </c>
       <c r="AO30">
-        <v>0.99611299874662873</v>
+        <v>0.9953231779810513</v>
       </c>
       <c r="AP30">
-        <v>71.261689645139711</v>
+        <v>85.741737014060448</v>
       </c>
       <c r="AR30" t="s">
         <v>357</v>
@@ -10909,16 +10909,16 @@
         <v>743</v>
       </c>
       <c r="BA30" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="BB30" t="s">
-        <v>798</v>
+        <v>700</v>
       </c>
       <c r="BC30">
-        <v>0.9941574321229002</v>
+        <v>0.9941550644110243</v>
       </c>
       <c r="BD30">
-        <v>107.1137444134967</v>
+        <v>107.15715246455407</v>
       </c>
     </row>
     <row r="31" spans="2:56">
@@ -10983,16 +10983,16 @@
         <v>400</v>
       </c>
       <c r="Y31" t="s">
-        <v>331</v>
+        <v>320</v>
       </c>
       <c r="Z31" t="s">
         <v>499</v>
       </c>
       <c r="AA31">
-        <v>0.99536018066282017</v>
+        <v>0.9936042103238425</v>
       </c>
       <c r="AB31">
-        <v>85.06335451496426</v>
+        <v>117.25614406288832</v>
       </c>
       <c r="AD31" t="s">
         <v>357</v>
@@ -11019,16 +11019,16 @@
         <v>578</v>
       </c>
       <c r="AM31" t="s">
+        <v>662</v>
+      </c>
+      <c r="AN31" t="s">
         <v>663</v>
       </c>
-      <c r="AN31" t="s">
-        <v>664</v>
-      </c>
       <c r="AO31">
-        <v>0.99410266459132846</v>
+        <v>0.99784973993426285</v>
       </c>
       <c r="AP31">
-        <v>108.11781582564529</v>
+        <v>39.4214345385139</v>
       </c>
       <c r="AR31" t="s">
         <v>357</v>
@@ -11055,16 +11055,16 @@
         <v>745</v>
       </c>
       <c r="BA31" t="s">
-        <v>799</v>
+        <v>797</v>
       </c>
       <c r="BB31" t="s">
-        <v>800</v>
+        <v>798</v>
       </c>
       <c r="BC31">
-        <v>0.98902827014922345</v>
+        <v>0.97713203835019113</v>
       </c>
       <c r="BD31">
-        <v>201.14838059757037</v>
+        <v>419.24596357982909</v>
       </c>
     </row>
     <row r="32" spans="2:56">
@@ -11129,16 +11129,16 @@
         <v>402</v>
       </c>
       <c r="Y32" t="s">
-        <v>312</v>
+        <v>339</v>
       </c>
       <c r="Z32" t="s">
         <v>500</v>
       </c>
       <c r="AA32">
-        <v>0.99092468152945157</v>
+        <v>0.98700404273476772</v>
       </c>
       <c r="AB32">
-        <v>166.38083862672116</v>
+        <v>238.25921652925925</v>
       </c>
       <c r="AD32" t="s">
         <v>357</v>
@@ -11165,16 +11165,16 @@
         <v>580</v>
       </c>
       <c r="AM32" t="s">
+        <v>664</v>
+      </c>
+      <c r="AN32" t="s">
         <v>665</v>
       </c>
-      <c r="AN32" t="s">
-        <v>666</v>
-      </c>
       <c r="AO32">
-        <v>0.99072079741836661</v>
+        <v>0.99166730629437405</v>
       </c>
       <c r="AP32">
-        <v>170.11871399661308</v>
+        <v>152.7660512698088</v>
       </c>
       <c r="AR32" t="s">
         <v>357</v>
@@ -11201,16 +11201,16 @@
         <v>747</v>
       </c>
       <c r="BA32" t="s">
-        <v>801</v>
+        <v>799</v>
       </c>
       <c r="BB32" t="s">
-        <v>784</v>
+        <v>800</v>
       </c>
       <c r="BC32">
-        <v>0.97887093776827594</v>
+        <v>0.99576968882554151</v>
       </c>
       <c r="BD32">
-        <v>387.36614091494118</v>
+        <v>77.555704865071448</v>
       </c>
     </row>
     <row r="33" spans="2:56">
@@ -11275,16 +11275,16 @@
         <v>404</v>
       </c>
       <c r="Y33" t="s">
-        <v>313</v>
+        <v>304</v>
       </c>
       <c r="Z33" t="s">
         <v>501</v>
       </c>
       <c r="AA33">
-        <v>0.99431419492629725</v>
+        <v>0.99148269770211572</v>
       </c>
       <c r="AB33">
-        <v>104.23975968455018</v>
+        <v>156.15054212787871</v>
       </c>
       <c r="AD33" t="s">
         <v>357</v>
@@ -11311,16 +11311,16 @@
         <v>582</v>
       </c>
       <c r="AM33" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="AN33" t="s">
-        <v>668</v>
+        <v>481</v>
       </c>
       <c r="AO33">
-        <v>0.99501643023888209</v>
+        <v>0.99146458511356661</v>
       </c>
       <c r="AP33">
-        <v>91.36544562049427</v>
+        <v>156.48260625127807</v>
       </c>
       <c r="AR33" t="s">
         <v>357</v>
@@ -11347,16 +11347,16 @@
         <v>749</v>
       </c>
       <c r="BA33" t="s">
+        <v>801</v>
+      </c>
+      <c r="BB33" t="s">
         <v>802</v>
       </c>
-      <c r="BB33" t="s">
-        <v>520</v>
-      </c>
       <c r="BC33">
-        <v>0.97764590548227914</v>
+        <v>0.99085132728755021</v>
       </c>
       <c r="BD33">
-        <v>409.8250661582149</v>
+        <v>167.72566639491282</v>
       </c>
     </row>
     <row r="34" spans="2:56">
@@ -11421,16 +11421,16 @@
         <v>406</v>
       </c>
       <c r="Y34" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="Z34" t="s">
         <v>502</v>
       </c>
       <c r="AA34">
-        <v>0.99627916803835959</v>
+        <v>0.9970215739199545</v>
       </c>
       <c r="AB34">
-        <v>68.215252630073479</v>
+        <v>54.604478134167074</v>
       </c>
       <c r="AD34" t="s">
         <v>357</v>
@@ -11457,16 +11457,16 @@
         <v>584</v>
       </c>
       <c r="AM34" t="s">
-        <v>669</v>
+        <v>667</v>
       </c>
       <c r="AN34" t="s">
-        <v>670</v>
+        <v>668</v>
       </c>
       <c r="AO34">
-        <v>0.99367595643491624</v>
+        <v>0.99549102504559717</v>
       </c>
       <c r="AP34">
-        <v>115.94079869320176</v>
+        <v>82.664540830717883</v>
       </c>
       <c r="AR34" t="s">
         <v>357</v>
@@ -11499,10 +11499,10 @@
         <v>804</v>
       </c>
       <c r="BC34">
-        <v>0.99603912935693217</v>
+        <v>0.98810956277351192</v>
       </c>
       <c r="BD34">
-        <v>72.615961789576843</v>
+        <v>217.99134915228177</v>
       </c>
     </row>
     <row r="35" spans="2:56">
@@ -11567,16 +11567,16 @@
         <v>408</v>
       </c>
       <c r="Y35" t="s">
-        <v>338</v>
+        <v>330</v>
       </c>
       <c r="Z35" t="s">
         <v>503</v>
       </c>
       <c r="AA35">
-        <v>0.99512875041881377</v>
+        <v>0.9963692742640502</v>
       </c>
       <c r="AB35">
-        <v>89.306242321746609</v>
+        <v>66.563305159080301</v>
       </c>
       <c r="AD35" t="s">
         <v>357</v>
@@ -11603,16 +11603,16 @@
         <v>586</v>
       </c>
       <c r="AM35" t="s">
-        <v>671</v>
+        <v>669</v>
       </c>
       <c r="AN35" t="s">
-        <v>672</v>
+        <v>501</v>
       </c>
       <c r="AO35">
-        <v>0.98007271259494255</v>
+        <v>0.99089429663374551</v>
       </c>
       <c r="AP35">
-        <v>365.33360242605363</v>
+        <v>166.93789504799881</v>
       </c>
       <c r="AR35" t="s">
         <v>357</v>
@@ -11645,10 +11645,10 @@
         <v>806</v>
       </c>
       <c r="BC35">
-        <v>0.99085132728755021</v>
+        <v>0.976919795397307</v>
       </c>
       <c r="BD35">
-        <v>167.72566639491282</v>
+        <v>423.13708438270464</v>
       </c>
     </row>
     <row r="36" spans="2:56">
@@ -11713,16 +11713,16 @@
         <v>410</v>
       </c>
       <c r="Y36" t="s">
-        <v>299</v>
+        <v>319</v>
       </c>
       <c r="Z36" t="s">
         <v>504</v>
       </c>
       <c r="AA36">
-        <v>0.97936066022114188</v>
+        <v>0.99312342621982508</v>
       </c>
       <c r="AB36">
-        <v>378.38789594573325</v>
+        <v>126.07051930320748</v>
       </c>
       <c r="AD36" t="s">
         <v>357</v>
@@ -11749,16 +11749,16 @@
         <v>588</v>
       </c>
       <c r="AM36" t="s">
-        <v>673</v>
+        <v>670</v>
       </c>
       <c r="AN36" t="s">
-        <v>480</v>
+        <v>671</v>
       </c>
       <c r="AO36">
-        <v>0.99276484208013105</v>
+        <v>0.99724587877560378</v>
       </c>
       <c r="AP36">
-        <v>132.64456186426332</v>
+        <v>50.492222447263664</v>
       </c>
       <c r="AR36" t="s">
         <v>357</v>
@@ -11791,10 +11791,10 @@
         <v>808</v>
       </c>
       <c r="BC36">
-        <v>0.93550473459950212</v>
+        <v>0.99088318071669168</v>
       </c>
       <c r="BD36">
-        <v>1182.4131990091278</v>
+        <v>167.14168686065315</v>
       </c>
     </row>
     <row r="37" spans="2:56">
@@ -11859,16 +11859,16 @@
         <v>412</v>
       </c>
       <c r="Y37" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="Z37" t="s">
         <v>505</v>
       </c>
       <c r="AA37">
-        <v>0.9979650023251263</v>
+        <v>0.99752287241357906</v>
       </c>
       <c r="AB37">
-        <v>37.308290706018212</v>
+        <v>45.414005751051391</v>
       </c>
       <c r="AD37" t="s">
         <v>357</v>
@@ -11895,16 +11895,16 @@
         <v>590</v>
       </c>
       <c r="AM37" t="s">
-        <v>674</v>
+        <v>672</v>
       </c>
       <c r="AN37" t="s">
-        <v>501</v>
+        <v>673</v>
       </c>
       <c r="AO37">
-        <v>0.9953231779810513</v>
+        <v>0.99687395765771536</v>
       </c>
       <c r="AP37">
-        <v>85.741737014060448</v>
+        <v>57.310776275218892</v>
       </c>
       <c r="AR37" t="s">
         <v>357</v>
@@ -11934,13 +11934,13 @@
         <v>809</v>
       </c>
       <c r="BB37" t="s">
-        <v>664</v>
+        <v>810</v>
       </c>
       <c r="BC37">
-        <v>0.99006235484112581</v>
+        <v>0.99267872653249711</v>
       </c>
       <c r="BD37">
-        <v>182.19016124602703</v>
+        <v>134.22334690422022</v>
       </c>
     </row>
     <row r="38" spans="2:56">
@@ -12005,16 +12005,16 @@
         <v>414</v>
       </c>
       <c r="Y38" t="s">
-        <v>332</v>
+        <v>321</v>
       </c>
       <c r="Z38" t="s">
         <v>506</v>
       </c>
       <c r="AA38">
-        <v>0.99672243529281113</v>
+        <v>0.99474921825793183</v>
       </c>
       <c r="AB38">
-        <v>60.088686298463386</v>
+        <v>96.264331937916907</v>
       </c>
       <c r="AD38" t="s">
         <v>357</v>
@@ -12041,16 +12041,16 @@
         <v>592</v>
       </c>
       <c r="AM38" t="s">
+        <v>674</v>
+      </c>
+      <c r="AN38" t="s">
         <v>675</v>
       </c>
-      <c r="AN38" t="s">
-        <v>676</v>
-      </c>
       <c r="AO38">
-        <v>0.99784973993426285</v>
+        <v>0.99410266459132846</v>
       </c>
       <c r="AP38">
-        <v>39.4214345385139</v>
+        <v>108.11781582564529</v>
       </c>
       <c r="AR38" t="s">
         <v>357</v>
@@ -12077,16 +12077,16 @@
         <v>759</v>
       </c>
       <c r="BA38" t="s">
-        <v>810</v>
+        <v>811</v>
       </c>
       <c r="BB38" t="s">
-        <v>811</v>
+        <v>812</v>
       </c>
       <c r="BC38">
-        <v>0.99266053819235223</v>
+        <v>0.99560935707608011</v>
       </c>
       <c r="BD38">
-        <v>134.55679980687663</v>
+        <v>80.495120271864536</v>
       </c>
     </row>
     <row r="39" spans="2:56">
@@ -12151,16 +12151,16 @@
         <v>416</v>
       </c>
       <c r="Y39" t="s">
-        <v>319</v>
+        <v>348</v>
       </c>
       <c r="Z39" t="s">
         <v>507</v>
       </c>
       <c r="AA39">
-        <v>0.99312342621982508</v>
+        <v>0.99496672523274499</v>
       </c>
       <c r="AB39">
-        <v>126.07051930320748</v>
+        <v>92.276704066342106</v>
       </c>
       <c r="AD39" t="s">
         <v>357</v>
@@ -12187,16 +12187,16 @@
         <v>594</v>
       </c>
       <c r="AM39" t="s">
+        <v>676</v>
+      </c>
+      <c r="AN39" t="s">
         <v>677</v>
       </c>
-      <c r="AN39" t="s">
-        <v>492</v>
-      </c>
       <c r="AO39">
-        <v>0.99089429663374551</v>
+        <v>0.99072079741836661</v>
       </c>
       <c r="AP39">
-        <v>166.93789504799881</v>
+        <v>170.11871399661308</v>
       </c>
       <c r="AR39" t="s">
         <v>357</v>
@@ -12223,16 +12223,16 @@
         <v>761</v>
       </c>
       <c r="BA39" t="s">
-        <v>812</v>
+        <v>813</v>
       </c>
       <c r="BB39" t="s">
-        <v>813</v>
+        <v>488</v>
       </c>
       <c r="BC39">
-        <v>0.976919795397307</v>
+        <v>0.97764590548227914</v>
       </c>
       <c r="BD39">
-        <v>423.13708438270464</v>
+        <v>409.8250661582149</v>
       </c>
     </row>
     <row r="40" spans="2:56">
@@ -12297,16 +12297,16 @@
         <v>418</v>
       </c>
       <c r="Y40" t="s">
-        <v>355</v>
+        <v>337</v>
       </c>
       <c r="Z40" t="s">
         <v>508</v>
       </c>
       <c r="AA40">
-        <v>0.99752287241357906</v>
+        <v>0.99600522283071102</v>
       </c>
       <c r="AB40">
-        <v>45.414005751051391</v>
+        <v>73.237581436964462</v>
       </c>
       <c r="AD40" t="s">
         <v>357</v>
@@ -12339,10 +12339,10 @@
         <v>679</v>
       </c>
       <c r="AO40">
-        <v>0.99724587877560378</v>
+        <v>0.99501643023888209</v>
       </c>
       <c r="AP40">
-        <v>50.492222447263664</v>
+        <v>91.36544562049427</v>
       </c>
       <c r="AR40" t="s">
         <v>357</v>
@@ -12375,10 +12375,10 @@
         <v>815</v>
       </c>
       <c r="BC40">
-        <v>0.99088318071669168</v>
+        <v>0.99603912935693217</v>
       </c>
       <c r="BD40">
-        <v>167.14168686065315</v>
+        <v>72.615961789576843</v>
       </c>
     </row>
     <row r="41" spans="2:56">
@@ -12443,16 +12443,16 @@
         <v>420</v>
       </c>
       <c r="Y41" t="s">
-        <v>344</v>
+        <v>303</v>
       </c>
       <c r="Z41" t="s">
         <v>509</v>
       </c>
       <c r="AA41">
-        <v>0.99634720436029245</v>
+        <v>0.98327228856468729</v>
       </c>
       <c r="AB41">
-        <v>66.967920061305705</v>
+        <v>306.67470964740028</v>
       </c>
       <c r="AD41" t="s">
         <v>357</v>
@@ -12485,10 +12485,10 @@
         <v>681</v>
       </c>
       <c r="AO41">
-        <v>0.99687395765771536</v>
+        <v>0.99367595643491624</v>
       </c>
       <c r="AP41">
-        <v>57.310776275218892</v>
+        <v>115.94079869320176</v>
       </c>
     </row>
     <row r="42" spans="2:56">
@@ -12553,16 +12553,16 @@
         <v>422</v>
       </c>
       <c r="Y42" t="s">
-        <v>324</v>
+        <v>311</v>
       </c>
       <c r="Z42" t="s">
         <v>510</v>
       </c>
       <c r="AA42">
-        <v>0.99690900069701904</v>
+        <v>0.99608527259090462</v>
       </c>
       <c r="AB42">
-        <v>56.668320554651658</v>
+        <v>71.770002500082597</v>
       </c>
       <c r="AD42" t="s">
         <v>357</v>
@@ -12592,13 +12592,13 @@
         <v>682</v>
       </c>
       <c r="AN42" t="s">
-        <v>501</v>
+        <v>683</v>
       </c>
       <c r="AO42">
-        <v>0.99336120165168273</v>
+        <v>0.99644445157760886</v>
       </c>
       <c r="AP42">
-        <v>121.71130305248386</v>
+        <v>65.185054410503341</v>
       </c>
     </row>
     <row r="43" spans="2:56">
@@ -12663,16 +12663,16 @@
         <v>424</v>
       </c>
       <c r="Y43" t="s">
-        <v>343</v>
+        <v>322</v>
       </c>
       <c r="Z43" t="s">
         <v>511</v>
       </c>
       <c r="AA43">
-        <v>0.98659243069702229</v>
+        <v>0.99688420747686357</v>
       </c>
       <c r="AB43">
-        <v>245.80543722125813</v>
+        <v>57.122862924167315</v>
       </c>
       <c r="AD43" t="s">
         <v>357</v>
@@ -12699,16 +12699,16 @@
         <v>602</v>
       </c>
       <c r="AM43" t="s">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="AN43" t="s">
-        <v>485</v>
+        <v>685</v>
       </c>
       <c r="AO43">
-        <v>0.99146458511356661</v>
+        <v>0.99593921525806983</v>
       </c>
       <c r="AP43">
-        <v>156.48260625127807</v>
+        <v>74.447720268718882</v>
       </c>
     </row>
     <row r="44" spans="2:56">
@@ -12809,16 +12809,16 @@
         <v>604</v>
       </c>
       <c r="AM44" t="s">
-        <v>684</v>
+        <v>686</v>
       </c>
       <c r="AN44" t="s">
-        <v>685</v>
+        <v>687</v>
       </c>
       <c r="AO44">
-        <v>0.99549102504559717</v>
+        <v>0.99516270130765094</v>
       </c>
       <c r="AP44">
-        <v>82.664540830717883</v>
+        <v>88.68380935973272</v>
       </c>
     </row>
     <row r="45" spans="2:56">
@@ -12919,16 +12919,16 @@
         <v>606</v>
       </c>
       <c r="AM45" t="s">
-        <v>686</v>
+        <v>688</v>
       </c>
       <c r="AN45" t="s">
-        <v>687</v>
+        <v>689</v>
       </c>
       <c r="AO45">
-        <v>0.99652238714397645</v>
+        <v>0.99373433598681304</v>
       </c>
       <c r="AP45">
-        <v>63.756235693765916</v>
+        <v>114.8705069084281</v>
       </c>
     </row>
     <row r="46" spans="2:56">
@@ -13029,16 +13029,16 @@
         <v>608</v>
       </c>
       <c r="AM46" t="s">
-        <v>688</v>
+        <v>690</v>
       </c>
       <c r="AN46" t="s">
-        <v>689</v>
+        <v>691</v>
       </c>
       <c r="AO46">
-        <v>0.99644445157760886</v>
+        <v>0.99674459930858406</v>
       </c>
       <c r="AP46">
-        <v>65.185054410503341</v>
+        <v>59.682346009292083</v>
       </c>
     </row>
     <row r="47" spans="2:56">
@@ -13103,16 +13103,16 @@
         <v>432</v>
       </c>
       <c r="Y47" t="s">
-        <v>306</v>
+        <v>302</v>
       </c>
       <c r="Z47" t="s">
         <v>515</v>
       </c>
       <c r="AA47">
-        <v>0.98362146023706842</v>
+        <v>0.98305355992983057</v>
       </c>
       <c r="AB47">
-        <v>300.27322898707882</v>
+        <v>310.68473461977231</v>
       </c>
       <c r="AD47" t="s">
         <v>357</v>
@@ -13139,16 +13139,16 @@
         <v>610</v>
       </c>
       <c r="AM47" t="s">
-        <v>690</v>
+        <v>692</v>
       </c>
       <c r="AN47" t="s">
-        <v>691</v>
+        <v>529</v>
       </c>
       <c r="AO47">
-        <v>0.99593921525806983</v>
+        <v>0.99159807557278401</v>
       </c>
       <c r="AP47">
-        <v>74.447720268718882</v>
+        <v>154.03528116562623</v>
       </c>
     </row>
     <row r="48" spans="2:56">
@@ -13213,16 +13213,16 @@
         <v>434</v>
       </c>
       <c r="Y48" t="s">
-        <v>309</v>
+        <v>341</v>
       </c>
       <c r="Z48" t="s">
         <v>516</v>
       </c>
       <c r="AA48">
-        <v>0.99264013999643841</v>
+        <v>0.99526736010661099</v>
       </c>
       <c r="AB48">
-        <v>134.93076673196322</v>
+        <v>86.765064712131235</v>
       </c>
       <c r="AD48" t="s">
         <v>357</v>
@@ -13249,16 +13249,16 @@
         <v>612</v>
       </c>
       <c r="AM48" t="s">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="AN48" t="s">
-        <v>693</v>
+        <v>481</v>
       </c>
       <c r="AO48">
-        <v>0.99516270130765094</v>
+        <v>0.98819864394083989</v>
       </c>
       <c r="AP48">
-        <v>88.68380935973272</v>
+        <v>216.35819441793581</v>
       </c>
     </row>
     <row r="49" spans="2:42">
@@ -13323,16 +13323,16 @@
         <v>436</v>
       </c>
       <c r="Y49" t="s">
-        <v>352</v>
+        <v>331</v>
       </c>
       <c r="Z49" t="s">
         <v>517</v>
       </c>
       <c r="AA49">
-        <v>0.99665443666269515</v>
+        <v>0.99536018066282017</v>
       </c>
       <c r="AB49">
-        <v>61.335327850588769</v>
+        <v>85.06335451496426</v>
       </c>
       <c r="AD49" t="s">
         <v>357</v>
@@ -13365,10 +13365,10 @@
         <v>695</v>
       </c>
       <c r="AO49">
-        <v>0.99373433598681304</v>
+        <v>0.99783515171992265</v>
       </c>
       <c r="AP49">
-        <v>114.8705069084281</v>
+        <v>39.688885134750748</v>
       </c>
     </row>
     <row r="50" spans="2:42">
@@ -13433,16 +13433,16 @@
         <v>438</v>
       </c>
       <c r="Y50" t="s">
-        <v>347</v>
+        <v>344</v>
       </c>
       <c r="Z50" t="s">
         <v>518</v>
       </c>
       <c r="AA50">
-        <v>0.99724701964333673</v>
+        <v>0.99634720436029245</v>
       </c>
       <c r="AB50">
-        <v>50.471306538827449</v>
+        <v>66.967920061305705</v>
       </c>
       <c r="AD50" t="s">
         <v>357</v>
@@ -13475,10 +13475,10 @@
         <v>697</v>
       </c>
       <c r="AO50">
-        <v>0.99674459930858406</v>
+        <v>0.99652238714397645</v>
       </c>
       <c r="AP50">
-        <v>59.682346009292083</v>
+        <v>63.756235693765916</v>
       </c>
     </row>
     <row r="51" spans="2:42">
@@ -13543,16 +13543,16 @@
         <v>440</v>
       </c>
       <c r="Y51" t="s">
-        <v>350</v>
+        <v>324</v>
       </c>
       <c r="Z51" t="s">
         <v>519</v>
       </c>
       <c r="AA51">
-        <v>0.99698341997506779</v>
+        <v>0.99690900069701904</v>
       </c>
       <c r="AB51">
-        <v>55.30396712375795</v>
+        <v>56.668320554651658</v>
       </c>
       <c r="AD51" t="s">
         <v>357</v>
@@ -13582,7 +13582,7 @@
         <v>698</v>
       </c>
       <c r="AN51" t="s">
-        <v>635</v>
+        <v>638</v>
       </c>
       <c r="AO51">
         <v>0.98296108964477757</v>
@@ -13653,16 +13653,16 @@
         <v>442</v>
       </c>
       <c r="Y52" t="s">
-        <v>300</v>
+        <v>343</v>
       </c>
       <c r="Z52" t="s">
         <v>520</v>
       </c>
       <c r="AA52">
-        <v>0.98292551835825892</v>
+        <v>0.98659243069702229</v>
       </c>
       <c r="AB52">
-        <v>313.03216343191991</v>
+        <v>245.80543722125813</v>
       </c>
       <c r="AD52" t="s">
         <v>357</v>
@@ -13763,16 +13763,16 @@
         <v>444</v>
       </c>
       <c r="Y53" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="Z53" t="s">
         <v>521</v>
       </c>
       <c r="AA53">
-        <v>0.99614153666719696</v>
+        <v>0.98362146023706842</v>
       </c>
       <c r="AB53">
-        <v>70.738494434723179</v>
+        <v>300.27322898707882</v>
       </c>
       <c r="AD53" t="s">
         <v>357</v>
@@ -13873,16 +13873,16 @@
         <v>446</v>
       </c>
       <c r="Y54" t="s">
-        <v>314</v>
+        <v>309</v>
       </c>
       <c r="Z54" t="s">
         <v>522</v>
       </c>
       <c r="AA54">
-        <v>0.98850654863880194</v>
+        <v>0.99264013999643841</v>
       </c>
       <c r="AB54">
-        <v>210.71327495529766</v>
+        <v>134.93076673196322</v>
       </c>
       <c r="AD54" t="s">
         <v>357</v>
@@ -13983,16 +13983,16 @@
         <v>448</v>
       </c>
       <c r="Y55" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="Z55" t="s">
         <v>523</v>
       </c>
       <c r="AA55">
-        <v>0.99485294245609246</v>
+        <v>0.99665443666269515</v>
       </c>
       <c r="AB55">
-        <v>94.362721638304791</v>
+        <v>61.335327850588769</v>
       </c>
     </row>
     <row r="56" spans="2:42">
@@ -14057,16 +14057,16 @@
         <v>450</v>
       </c>
       <c r="Y56" t="s">
-        <v>351</v>
+        <v>347</v>
       </c>
       <c r="Z56" t="s">
         <v>524</v>
       </c>
       <c r="AA56">
-        <v>0.99404600424580258</v>
+        <v>0.99724701964333673</v>
       </c>
       <c r="AB56">
-        <v>109.15658882695236</v>
+        <v>50.471306538827449</v>
       </c>
     </row>
     <row r="57" spans="2:42">
@@ -14131,16 +14131,16 @@
         <v>452</v>
       </c>
       <c r="Y57" t="s">
-        <v>325</v>
+        <v>350</v>
       </c>
       <c r="Z57" t="s">
         <v>525</v>
       </c>
       <c r="AA57">
-        <v>0.99781526983247337</v>
+        <v>0.99698341997506779</v>
       </c>
       <c r="AB57">
-        <v>40.053386404654447</v>
+        <v>55.30396712375795</v>
       </c>
     </row>
     <row r="58" spans="2:42">
@@ -14205,16 +14205,16 @@
         <v>454</v>
       </c>
       <c r="Y58" t="s">
-        <v>328</v>
+        <v>299</v>
       </c>
       <c r="Z58" t="s">
         <v>526</v>
       </c>
       <c r="AA58">
-        <v>0.98875969313918877</v>
+        <v>0.97936066022114188</v>
       </c>
       <c r="AB58">
-        <v>206.07229244820644</v>
+        <v>378.38789594573325</v>
       </c>
     </row>
     <row r="59" spans="2:42">
@@ -14279,16 +14279,16 @@
         <v>456</v>
       </c>
       <c r="Y59" t="s">
-        <v>349</v>
+        <v>354</v>
       </c>
       <c r="Z59" t="s">
         <v>527</v>
       </c>
       <c r="AA59">
-        <v>0.9962831220986742</v>
+        <v>0.9979650023251263</v>
       </c>
       <c r="AB59">
-        <v>68.14276152430682</v>
+        <v>37.308290706018212</v>
       </c>
     </row>
     <row r="60" spans="2:42">
@@ -14353,16 +14353,16 @@
         <v>458</v>
       </c>
       <c r="Y60" t="s">
-        <v>303</v>
+        <v>332</v>
       </c>
       <c r="Z60" t="s">
         <v>528</v>
       </c>
       <c r="AA60">
-        <v>0.98327228856468729</v>
+        <v>0.99672243529281113</v>
       </c>
       <c r="AB60">
-        <v>306.67470964740028</v>
+        <v>60.088686298463386</v>
       </c>
     </row>
     <row r="61" spans="2:42">
@@ -14427,16 +14427,16 @@
         <v>460</v>
       </c>
       <c r="Y61" t="s">
-        <v>311</v>
+        <v>308</v>
       </c>
       <c r="Z61" t="s">
         <v>529</v>
       </c>
       <c r="AA61">
-        <v>0.99608527259090462</v>
+        <v>0.99468188905612376</v>
       </c>
       <c r="AB61">
-        <v>71.770002500082597</v>
+        <v>97.498700637730266</v>
       </c>
     </row>
     <row r="62" spans="2:42">
@@ -14501,16 +14501,16 @@
         <v>462</v>
       </c>
       <c r="Y62" t="s">
-        <v>322</v>
+        <v>326</v>
       </c>
       <c r="Z62" t="s">
         <v>530</v>
       </c>
       <c r="AA62">
-        <v>0.99688420747686357</v>
+        <v>0.99798506730783287</v>
       </c>
       <c r="AB62">
-        <v>57.122862924167315</v>
+        <v>36.940432689730294</v>
       </c>
     </row>
     <row r="63" spans="2:42">
@@ -14575,16 +14575,16 @@
         <v>464</v>
       </c>
       <c r="Y63" t="s">
-        <v>308</v>
+        <v>333</v>
       </c>
       <c r="Z63" t="s">
         <v>531</v>
       </c>
       <c r="AA63">
-        <v>0.99468188905612376</v>
+        <v>0.99710009105712261</v>
       </c>
       <c r="AB63">
-        <v>97.498700637730266</v>
+        <v>53.164997286085928</v>
       </c>
     </row>
     <row r="64" spans="2:42">
@@ -14649,16 +14649,16 @@
         <v>466</v>
       </c>
       <c r="Y64" t="s">
-        <v>326</v>
+        <v>334</v>
       </c>
       <c r="Z64" t="s">
         <v>532</v>
       </c>
       <c r="AA64">
-        <v>0.99798506730783287</v>
+        <v>0.99687437062079542</v>
       </c>
       <c r="AB64">
-        <v>36.940432689730294</v>
+        <v>57.30320528541781</v>
       </c>
     </row>
     <row r="65" spans="2:28">
@@ -14723,16 +14723,16 @@
         <v>468</v>
       </c>
       <c r="Y65" t="s">
-        <v>333</v>
+        <v>349</v>
       </c>
       <c r="Z65" t="s">
         <v>533</v>
       </c>
       <c r="AA65">
-        <v>0.99710009105712261</v>
+        <v>0.9962831220986742</v>
       </c>
       <c r="AB65">
-        <v>53.164997286085928</v>
+        <v>68.14276152430682</v>
       </c>
     </row>
     <row r="66" spans="2:28">
@@ -14797,16 +14797,16 @@
         <v>470</v>
       </c>
       <c r="Y66" t="s">
-        <v>334</v>
+        <v>312</v>
       </c>
       <c r="Z66" t="s">
         <v>534</v>
       </c>
       <c r="AA66">
-        <v>0.99687437062079542</v>
+        <v>0.99092468152945157</v>
       </c>
       <c r="AB66">
-        <v>57.30320528541781</v>
+        <v>166.38083862672116</v>
       </c>
     </row>
     <row r="67" spans="2:28">
@@ -14871,16 +14871,16 @@
         <v>472</v>
       </c>
       <c r="Y67" t="s">
-        <v>321</v>
+        <v>313</v>
       </c>
       <c r="Z67" t="s">
         <v>535</v>
       </c>
       <c r="AA67">
-        <v>0.99474921825793183</v>
+        <v>0.99431419492629725</v>
       </c>
       <c r="AB67">
-        <v>96.264331937916907</v>
+        <v>104.23975968455018</v>
       </c>
     </row>
     <row r="68" spans="2:28">
@@ -14945,16 +14945,16 @@
         <v>474</v>
       </c>
       <c r="Y68" t="s">
-        <v>348</v>
+        <v>345</v>
       </c>
       <c r="Z68" t="s">
         <v>536</v>
       </c>
       <c r="AA68">
-        <v>0.99496672523274499</v>
+        <v>0.99627916803835959</v>
       </c>
       <c r="AB68">
-        <v>92.276704066342106</v>
+        <v>68.215252630073479</v>
       </c>
     </row>
     <row r="69" spans="2:28">
@@ -15019,16 +15019,16 @@
         <v>476</v>
       </c>
       <c r="Y69" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="Z69" t="s">
         <v>537</v>
       </c>
       <c r="AA69">
-        <v>0.99600522283071102</v>
+        <v>0.99512875041881377</v>
       </c>
       <c r="AB69">
-        <v>73.237581436964462</v>
+        <v>89.306242321746609</v>
       </c>
     </row>
   </sheetData>
@@ -15037,7 +15037,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{27F58468-D39C-41E2-915C-5D685B1ECEDE}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1D1AFA7B-E7CF-49E9-AF7F-1421661A36E9}">
   <dimension ref="B9:Z54"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -15149,7 +15149,7 @@
         <v>816</v>
       </c>
       <c r="K11" t="s">
-        <v>684</v>
+        <v>667</v>
       </c>
       <c r="L11">
         <v>2.8233593407936151</v>
@@ -15182,7 +15182,7 @@
         <v>904</v>
       </c>
       <c r="X11" t="s">
-        <v>772</v>
+        <v>795</v>
       </c>
       <c r="Y11">
         <v>3.4740000000000002</v>
@@ -15217,7 +15217,7 @@
         <v>818</v>
       </c>
       <c r="K12" t="s">
-        <v>636</v>
+        <v>639</v>
       </c>
       <c r="L12">
         <v>3.8142378644522381</v>
@@ -15250,7 +15250,7 @@
         <v>906</v>
       </c>
       <c r="X12" t="s">
-        <v>782</v>
+        <v>773</v>
       </c>
       <c r="Y12">
         <v>8.5649999999999995</v>
@@ -15285,7 +15285,7 @@
         <v>820</v>
       </c>
       <c r="K13" t="s">
-        <v>650</v>
+        <v>692</v>
       </c>
       <c r="L13">
         <v>9.4269786267192082</v>
@@ -15318,7 +15318,7 @@
         <v>908</v>
       </c>
       <c r="X13" t="s">
-        <v>783</v>
+        <v>774</v>
       </c>
       <c r="Y13">
         <v>1.0125</v>
@@ -15353,7 +15353,7 @@
         <v>822</v>
       </c>
       <c r="K14" t="s">
-        <v>682</v>
+        <v>647</v>
       </c>
       <c r="L14">
         <v>7.6140112878139474</v>
@@ -15386,7 +15386,7 @@
         <v>910</v>
       </c>
       <c r="X14" t="s">
-        <v>802</v>
+        <v>813</v>
       </c>
       <c r="Y14">
         <v>23.480250000000002</v>
@@ -15421,7 +15421,7 @@
         <v>824</v>
       </c>
       <c r="K15" t="s">
-        <v>644</v>
+        <v>652</v>
       </c>
       <c r="L15">
         <v>0.94579509370884995</v>
@@ -15454,7 +15454,7 @@
         <v>912</v>
       </c>
       <c r="X15" t="s">
-        <v>812</v>
+        <v>805</v>
       </c>
       <c r="Y15">
         <v>39.333750000000002</v>
@@ -15489,7 +15489,7 @@
         <v>826</v>
       </c>
       <c r="K16" t="s">
-        <v>651</v>
+        <v>693</v>
       </c>
       <c r="L16">
         <v>11.144960581876036</v>
@@ -15522,7 +15522,7 @@
         <v>914</v>
       </c>
       <c r="X16" t="s">
-        <v>801</v>
+        <v>765</v>
       </c>
       <c r="Y16">
         <v>38.395499999999998</v>
@@ -15557,7 +15557,7 @@
         <v>828</v>
       </c>
       <c r="K17" t="s">
-        <v>683</v>
+        <v>666</v>
       </c>
       <c r="L17">
         <v>33.533313348973216</v>
@@ -15590,7 +15590,7 @@
         <v>916</v>
       </c>
       <c r="X17" t="s">
-        <v>774</v>
+        <v>797</v>
       </c>
       <c r="Y17">
         <v>37.595999999999997</v>
@@ -15625,7 +15625,7 @@
         <v>830</v>
       </c>
       <c r="K18" t="s">
-        <v>655</v>
+        <v>627</v>
       </c>
       <c r="L18">
         <v>11.453245383033059</v>
@@ -15658,7 +15658,7 @@
         <v>918</v>
       </c>
       <c r="X18" t="s">
-        <v>773</v>
+        <v>796</v>
       </c>
       <c r="Y18">
         <v>14.10375</v>
@@ -15693,7 +15693,7 @@
         <v>832</v>
       </c>
       <c r="K19" t="s">
-        <v>674</v>
+        <v>661</v>
       </c>
       <c r="L19">
         <v>6.1833350114404624</v>
@@ -15726,7 +15726,7 @@
         <v>920</v>
       </c>
       <c r="X19" t="s">
-        <v>779</v>
+        <v>788</v>
       </c>
       <c r="Y19">
         <v>26.091750000000001</v>
@@ -15794,7 +15794,7 @@
         <v>922</v>
       </c>
       <c r="X20" t="s">
-        <v>778</v>
+        <v>787</v>
       </c>
       <c r="Y20">
         <v>12.781499999999999</v>
@@ -15829,7 +15829,7 @@
         <v>836</v>
       </c>
       <c r="K21" t="s">
-        <v>654</v>
+        <v>626</v>
       </c>
       <c r="L21">
         <v>20.286141920134732</v>
@@ -15862,7 +15862,7 @@
         <v>924</v>
       </c>
       <c r="X21" t="s">
-        <v>771</v>
+        <v>777</v>
       </c>
       <c r="Y21">
         <v>14.436</v>
@@ -15897,7 +15897,7 @@
         <v>838</v>
       </c>
       <c r="K22" t="s">
-        <v>665</v>
+        <v>676</v>
       </c>
       <c r="L22">
         <v>32.012227177722089</v>
@@ -15930,7 +15930,7 @@
         <v>926</v>
       </c>
       <c r="X22" t="s">
-        <v>787</v>
+        <v>769</v>
       </c>
       <c r="Y22">
         <v>15.56025</v>
@@ -15965,7 +15965,7 @@
         <v>840</v>
       </c>
       <c r="K23" t="s">
-        <v>688</v>
+        <v>682</v>
       </c>
       <c r="L23">
         <v>7.7073299979921162</v>
@@ -15998,7 +15998,7 @@
         <v>928</v>
       </c>
       <c r="X23" t="s">
-        <v>809</v>
+        <v>784</v>
       </c>
       <c r="Y23">
         <v>19.391999999999999</v>
@@ -16033,7 +16033,7 @@
         <v>842</v>
       </c>
       <c r="K24" t="s">
-        <v>657</v>
+        <v>629</v>
       </c>
       <c r="L24">
         <v>10.94212775371234</v>
@@ -16066,7 +16066,7 @@
         <v>930</v>
       </c>
       <c r="X24" t="s">
-        <v>765</v>
+        <v>809</v>
       </c>
       <c r="Y24">
         <v>11.877750000000001</v>
@@ -16101,7 +16101,7 @@
         <v>844</v>
       </c>
       <c r="K25" t="s">
-        <v>630</v>
+        <v>664</v>
       </c>
       <c r="L25">
         <v>17.017572468804527</v>
@@ -16134,7 +16134,7 @@
         <v>932</v>
       </c>
       <c r="X25" t="s">
-        <v>769</v>
+        <v>803</v>
       </c>
       <c r="Y25">
         <v>58.667999999999999</v>
@@ -16169,7 +16169,7 @@
         <v>846</v>
       </c>
       <c r="K26" t="s">
-        <v>690</v>
+        <v>684</v>
       </c>
       <c r="L26">
         <v>10.044304280614389</v>
@@ -16202,7 +16202,7 @@
         <v>934</v>
       </c>
       <c r="X26" t="s">
-        <v>805</v>
+        <v>801</v>
       </c>
       <c r="Y26">
         <v>23.315249999999999</v>
@@ -16270,7 +16270,7 @@
         <v>936</v>
       </c>
       <c r="X27" t="s">
-        <v>795</v>
+        <v>780</v>
       </c>
       <c r="Y27">
         <v>10.53525</v>
@@ -16305,7 +16305,7 @@
         <v>850</v>
       </c>
       <c r="K28" t="s">
-        <v>686</v>
+        <v>696</v>
       </c>
       <c r="L28">
         <v>21.882724350441411</v>
@@ -16338,7 +16338,7 @@
         <v>938</v>
       </c>
       <c r="X28" t="s">
-        <v>799</v>
+        <v>793</v>
       </c>
       <c r="Y28">
         <v>43.472250000000003</v>
@@ -16373,7 +16373,7 @@
         <v>852</v>
       </c>
       <c r="K29" t="s">
-        <v>652</v>
+        <v>694</v>
       </c>
       <c r="L29">
         <v>4.5283086408379516</v>
@@ -16406,7 +16406,7 @@
         <v>940</v>
       </c>
       <c r="X29" t="s">
-        <v>789</v>
+        <v>771</v>
       </c>
       <c r="Y29">
         <v>60.665999999999997</v>
@@ -16441,7 +16441,7 @@
         <v>854</v>
       </c>
       <c r="K30" t="s">
-        <v>638</v>
+        <v>641</v>
       </c>
       <c r="L30">
         <v>10.193964319177619</v>
@@ -16474,7 +16474,7 @@
         <v>942</v>
       </c>
       <c r="X30" t="s">
-        <v>791</v>
+        <v>767</v>
       </c>
       <c r="Y30">
         <v>38.461500000000001</v>
@@ -16509,7 +16509,7 @@
         <v>856</v>
       </c>
       <c r="K31" t="s">
-        <v>659</v>
+        <v>631</v>
       </c>
       <c r="L31">
         <v>4.0796933380077434</v>
@@ -16542,7 +16542,7 @@
         <v>944</v>
       </c>
       <c r="X31" t="s">
-        <v>780</v>
+        <v>789</v>
       </c>
       <c r="Y31">
         <v>29.377500000000001</v>
@@ -16577,7 +16577,7 @@
         <v>858</v>
       </c>
       <c r="K32" t="s">
-        <v>642</v>
+        <v>650</v>
       </c>
       <c r="L32">
         <v>12.26323880416394</v>
@@ -16610,7 +16610,7 @@
         <v>946</v>
       </c>
       <c r="X32" t="s">
-        <v>767</v>
+        <v>811</v>
       </c>
       <c r="Y32">
         <v>8.5395000000000003</v>
@@ -16645,7 +16645,7 @@
         <v>860</v>
       </c>
       <c r="K33" t="s">
-        <v>663</v>
+        <v>674</v>
       </c>
       <c r="L33">
         <v>0.6739114575585754</v>
@@ -16678,7 +16678,7 @@
         <v>948</v>
       </c>
       <c r="X33" t="s">
-        <v>803</v>
+        <v>814</v>
       </c>
       <c r="Y33">
         <v>22.296749999999999</v>
@@ -16746,7 +16746,7 @@
         <v>950</v>
       </c>
       <c r="X34" t="s">
-        <v>807</v>
+        <v>782</v>
       </c>
       <c r="Y34">
         <v>0.45450000000000002</v>
@@ -16781,7 +16781,7 @@
         <v>864</v>
       </c>
       <c r="K35" t="s">
-        <v>677</v>
+        <v>669</v>
       </c>
       <c r="L35">
         <v>8.2027093455463351</v>
@@ -16814,7 +16814,7 @@
         <v>952</v>
       </c>
       <c r="X35" t="s">
-        <v>810</v>
+        <v>785</v>
       </c>
       <c r="Y35">
         <v>1.9215</v>
@@ -16849,7 +16849,7 @@
         <v>866</v>
       </c>
       <c r="K36" t="s">
-        <v>673</v>
+        <v>660</v>
       </c>
       <c r="L36">
         <v>14.077964934917114</v>
@@ -16882,7 +16882,7 @@
         <v>954</v>
       </c>
       <c r="X36" t="s">
-        <v>785</v>
+        <v>775</v>
       </c>
       <c r="Y36">
         <v>66.086250000000007</v>
@@ -16917,7 +16917,7 @@
         <v>868</v>
       </c>
       <c r="K37" t="s">
-        <v>626</v>
+        <v>643</v>
       </c>
       <c r="L37">
         <v>30.634386080822491</v>
@@ -16950,7 +16950,7 @@
         <v>956</v>
       </c>
       <c r="X37" t="s">
-        <v>793</v>
+        <v>778</v>
       </c>
       <c r="Y37">
         <v>17.88</v>
@@ -16985,7 +16985,7 @@
         <v>870</v>
       </c>
       <c r="K38" t="s">
-        <v>634</v>
+        <v>637</v>
       </c>
       <c r="L38">
         <v>5.7746901396817503</v>
@@ -17018,7 +17018,7 @@
         <v>958</v>
       </c>
       <c r="X38" t="s">
-        <v>814</v>
+        <v>807</v>
       </c>
       <c r="Y38">
         <v>15.9975</v>
@@ -17053,7 +17053,7 @@
         <v>872</v>
       </c>
       <c r="K39" t="s">
-        <v>640</v>
+        <v>648</v>
       </c>
       <c r="L39">
         <v>0.31034972419242446</v>
@@ -17086,7 +17086,7 @@
         <v>960</v>
       </c>
       <c r="X39" t="s">
-        <v>776</v>
+        <v>799</v>
       </c>
       <c r="Y39">
         <v>13.328250000000001</v>
@@ -17121,7 +17121,7 @@
         <v>874</v>
       </c>
       <c r="K40" t="s">
-        <v>628</v>
+        <v>645</v>
       </c>
       <c r="L40">
         <v>6.8374865443011785</v>
@@ -17154,7 +17154,7 @@
         <v>962</v>
       </c>
       <c r="X40" t="s">
-        <v>797</v>
+        <v>791</v>
       </c>
       <c r="Y40">
         <v>20.887499999999999</v>
@@ -17224,7 +17224,7 @@
         <v>878</v>
       </c>
       <c r="K42" t="s">
-        <v>632</v>
+        <v>635</v>
       </c>
       <c r="L42">
         <v>1.2064770882628508</v>
@@ -17259,7 +17259,7 @@
         <v>880</v>
       </c>
       <c r="K43" t="s">
-        <v>671</v>
+        <v>658</v>
       </c>
       <c r="L43">
         <v>18.8349545412255</v>
@@ -17294,7 +17294,7 @@
         <v>882</v>
       </c>
       <c r="K44" t="s">
-        <v>692</v>
+        <v>686</v>
       </c>
       <c r="L44">
         <v>58.145469176630144</v>
@@ -17329,7 +17329,7 @@
         <v>884</v>
       </c>
       <c r="K45" t="s">
-        <v>646</v>
+        <v>654</v>
       </c>
       <c r="L45">
         <v>21.047598854439691</v>
@@ -17364,7 +17364,7 @@
         <v>886</v>
       </c>
       <c r="K46" t="s">
-        <v>667</v>
+        <v>678</v>
       </c>
       <c r="L46">
         <v>6.0945869574590601</v>
@@ -17399,7 +17399,7 @@
         <v>888</v>
       </c>
       <c r="K47" t="s">
-        <v>696</v>
+        <v>690</v>
       </c>
       <c r="L47">
         <v>0.52378718950160097</v>
@@ -17434,7 +17434,7 @@
         <v>890</v>
       </c>
       <c r="K48" t="s">
-        <v>669</v>
+        <v>680</v>
       </c>
       <c r="L48">
         <v>0.74417561246386832</v>
@@ -17469,7 +17469,7 @@
         <v>892</v>
       </c>
       <c r="K49" t="s">
-        <v>694</v>
+        <v>688</v>
       </c>
       <c r="L49">
         <v>1.2742474813759068</v>
@@ -17504,7 +17504,7 @@
         <v>894</v>
       </c>
       <c r="K50" t="s">
-        <v>680</v>
+        <v>672</v>
       </c>
       <c r="L50">
         <v>0.78634982125966435</v>
@@ -17539,7 +17539,7 @@
         <v>896</v>
       </c>
       <c r="K51" t="s">
-        <v>678</v>
+        <v>670</v>
       </c>
       <c r="L51">
         <v>2.1288097562409964</v>
@@ -17574,7 +17574,7 @@
         <v>898</v>
       </c>
       <c r="K52" t="s">
-        <v>675</v>
+        <v>662</v>
       </c>
       <c r="L52">
         <v>3.1509090152495176</v>
@@ -17609,7 +17609,7 @@
         <v>900</v>
       </c>
       <c r="K53" t="s">
-        <v>661</v>
+        <v>633</v>
       </c>
       <c r="L53">
         <v>1.0579993988849852</v>
@@ -17644,7 +17644,7 @@
         <v>902</v>
       </c>
       <c r="K54" t="s">
-        <v>648</v>
+        <v>656</v>
       </c>
       <c r="L54">
         <v>0.12383426416706249</v>
@@ -17659,7 +17659,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{30762AB5-3FB5-41C9-8E3B-6313BA37FB94}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E316BE10-2A10-49B4-90BE-C6FC965A9961}">
   <dimension ref="B9:P73"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
